--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\GG\Jeronimo\Assets\StreamingAssets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E445202E-5FC4-45C1-BEC8-71C3731B5C3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBCC828-5B8B-4FA2-B90C-3E372AF407BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="9" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7382" uniqueCount="1736">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7277" uniqueCount="1737">
   <si>
     <t>NAME</t>
   </si>
@@ -5392,6 +5392,9 @@
   </si>
   <si>
     <t>kill,insect,2,&gt;=</t>
+  </si>
+  <si>
+    <t>s,battle6</t>
   </si>
 </sst>
 </file>
@@ -30961,7 +30964,7 @@
         <v>1722</v>
       </c>
       <c r="B64">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C64" t="s">
         <v>1723</v>
@@ -39243,46 +39246,46 @@
       <c r="L1" s="48"/>
     </row>
     <row r="2" spans="1:26" ht="12.5">
-      <c r="A2" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="B2" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="C2" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="D2" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="E2" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="F2" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="H2" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="J2" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="K2" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="L2" s="51" t="s">
-        <v>36</v>
+      <c r="A2" s="51">
+        <v>1</v>
+      </c>
+      <c r="B2" s="51">
+        <v>1</v>
+      </c>
+      <c r="C2" s="51">
+        <v>1</v>
+      </c>
+      <c r="D2" s="51">
+        <v>1</v>
+      </c>
+      <c r="E2" s="51">
+        <v>1</v>
+      </c>
+      <c r="F2" s="51">
+        <v>1</v>
+      </c>
+      <c r="G2" s="51">
+        <v>1</v>
+      </c>
+      <c r="H2" s="51">
+        <v>1</v>
+      </c>
+      <c r="I2" s="51">
+        <v>1</v>
+      </c>
+      <c r="J2" s="51">
+        <v>1</v>
+      </c>
+      <c r="K2" s="51">
+        <v>1</v>
+      </c>
+      <c r="L2" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:26" ht="12.5">
-      <c r="A3" s="51" t="s">
-        <v>36</v>
+      <c r="A3" s="51">
+        <v>1</v>
       </c>
       <c r="B3" s="51" t="s">
         <v>36</v>
@@ -39302,8 +39305,8 @@
       <c r="G3" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="H3" s="51" t="s">
-        <v>36</v>
+      <c r="H3" s="51">
+        <v>1</v>
       </c>
       <c r="I3" s="51" t="s">
         <v>36</v>
@@ -39314,13 +39317,13 @@
       <c r="K3" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L3" s="51" t="s">
-        <v>36</v>
+      <c r="L3" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:26" ht="12.5">
-      <c r="A4" s="51" t="s">
-        <v>36</v>
+      <c r="A4" s="51">
+        <v>1</v>
       </c>
       <c r="B4" s="51" t="s">
         <v>36</v>
@@ -39334,31 +39337,31 @@
       <c r="E4" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="51" t="s">
-        <v>36</v>
+      <c r="F4" s="51">
+        <v>1</v>
       </c>
       <c r="G4" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="H4" s="51" t="s">
-        <v>36</v>
+      <c r="H4" s="51">
+        <v>1</v>
       </c>
       <c r="I4" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J4" s="51" t="s">
-        <v>36</v>
+      <c r="J4" s="51">
+        <v>1</v>
       </c>
       <c r="K4" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L4" s="51" t="s">
-        <v>36</v>
+      <c r="L4" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:26" ht="12.5">
-      <c r="A5" s="51" t="s">
-        <v>36</v>
+      <c r="A5" s="51">
+        <v>1</v>
       </c>
       <c r="B5" s="51" t="s">
         <v>36</v>
@@ -39372,31 +39375,31 @@
       <c r="E5" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="51" t="s">
-        <v>36</v>
+      <c r="F5" s="51">
+        <v>1</v>
       </c>
       <c r="G5" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="H5" s="51" t="s">
-        <v>36</v>
+      <c r="H5" s="51">
+        <v>1</v>
       </c>
       <c r="I5" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J5" s="51" t="s">
-        <v>36</v>
+      <c r="J5" s="51">
+        <v>1</v>
       </c>
       <c r="K5" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L5" s="51" t="s">
-        <v>36</v>
+      <c r="L5" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:26" ht="12.5">
-      <c r="A6" s="51" t="s">
-        <v>36</v>
+      <c r="A6" s="51">
+        <v>1</v>
       </c>
       <c r="B6" s="51" t="s">
         <v>36</v>
@@ -39410,31 +39413,31 @@
       <c r="E6" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="F6" s="51" t="s">
-        <v>36</v>
+      <c r="F6" s="51">
+        <v>1</v>
       </c>
       <c r="G6" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="51" t="s">
-        <v>36</v>
+      <c r="H6" s="51">
+        <v>1</v>
       </c>
       <c r="I6" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J6" s="51" t="s">
-        <v>36</v>
+      <c r="J6" s="51">
+        <v>1</v>
       </c>
       <c r="K6" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="51" t="s">
-        <v>36</v>
+      <c r="L6" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:26" ht="12.5">
-      <c r="A7" s="51" t="s">
-        <v>36</v>
+      <c r="A7" s="51">
+        <v>1</v>
       </c>
       <c r="B7" s="51" t="s">
         <v>36</v>
@@ -39448,31 +39451,31 @@
       <c r="E7" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="F7" s="51" t="s">
-        <v>36</v>
+      <c r="F7" s="51">
+        <v>1</v>
       </c>
       <c r="G7" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="51" t="s">
-        <v>36</v>
+      <c r="H7" s="51">
+        <v>1</v>
       </c>
       <c r="I7" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J7" s="51" t="s">
-        <v>36</v>
+      <c r="J7" s="51">
+        <v>1</v>
       </c>
       <c r="K7" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L7" s="51" t="s">
-        <v>36</v>
+      <c r="L7" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:26" ht="12.5">
-      <c r="A8" s="51" t="s">
-        <v>36</v>
+      <c r="A8" s="51">
+        <v>1</v>
       </c>
       <c r="B8" s="51" t="s">
         <v>36</v>
@@ -39486,31 +39489,31 @@
       <c r="E8" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="51" t="s">
-        <v>36</v>
+      <c r="F8" s="51">
+        <v>1</v>
       </c>
       <c r="G8" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="H8" s="51" t="s">
-        <v>36</v>
+      <c r="H8" s="51">
+        <v>1</v>
       </c>
       <c r="I8" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J8" s="51" t="s">
-        <v>36</v>
+      <c r="J8" s="51">
+        <v>1</v>
       </c>
       <c r="K8" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L8" s="51" t="s">
-        <v>36</v>
+      <c r="L8" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:26" ht="12.5">
-      <c r="A9" s="51" t="s">
-        <v>36</v>
+      <c r="A9" s="51">
+        <v>1</v>
       </c>
       <c r="B9" s="51" t="s">
         <v>36</v>
@@ -39524,31 +39527,31 @@
       <c r="E9" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="51" t="s">
-        <v>36</v>
+      <c r="F9" s="51">
+        <v>1</v>
       </c>
       <c r="G9" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="H9" s="51" t="s">
-        <v>36</v>
+      <c r="H9" s="51">
+        <v>1</v>
       </c>
       <c r="I9" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J9" s="51" t="s">
-        <v>36</v>
+      <c r="J9" s="51">
+        <v>1</v>
       </c>
       <c r="K9" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L9" s="51" t="s">
-        <v>36</v>
+      <c r="L9" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:26" ht="12.5">
-      <c r="A10" s="51" t="s">
-        <v>36</v>
+      <c r="A10" s="51">
+        <v>1</v>
       </c>
       <c r="B10" s="51" t="s">
         <v>36</v>
@@ -39562,31 +39565,31 @@
       <c r="E10" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="F10" s="51" t="s">
-        <v>36</v>
+      <c r="F10" s="51">
+        <v>1</v>
       </c>
       <c r="G10" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="H10" s="51" t="s">
-        <v>36</v>
+      <c r="H10" s="51">
+        <v>1</v>
       </c>
       <c r="I10" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J10" s="51" t="s">
-        <v>36</v>
+      <c r="J10" s="51">
+        <v>1</v>
       </c>
       <c r="K10" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L10" s="51" t="s">
-        <v>36</v>
+      <c r="L10" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:26" ht="12.5">
-      <c r="A11" s="51" t="s">
-        <v>36</v>
+      <c r="A11" s="51">
+        <v>1</v>
       </c>
       <c r="B11" s="51" t="s">
         <v>36</v>
@@ -39600,31 +39603,31 @@
       <c r="E11" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="F11" s="51" t="s">
-        <v>36</v>
+      <c r="F11" s="51">
+        <v>1</v>
       </c>
       <c r="G11" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="H11" s="51" t="s">
-        <v>36</v>
+      <c r="H11" s="51">
+        <v>1</v>
       </c>
       <c r="I11" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J11" s="51" t="s">
-        <v>36</v>
+      <c r="J11" s="51">
+        <v>1</v>
       </c>
       <c r="K11" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L11" s="51" t="s">
-        <v>36</v>
+      <c r="L11" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:26" ht="12.5">
-      <c r="A12" s="51" t="s">
-        <v>36</v>
+      <c r="A12" s="51">
+        <v>1</v>
       </c>
       <c r="B12" s="51" t="s">
         <v>36</v>
@@ -39638,8 +39641,8 @@
       <c r="E12" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="F12" s="51" t="s">
-        <v>36</v>
+      <c r="F12" s="51">
+        <v>1</v>
       </c>
       <c r="G12" s="51" t="s">
         <v>36</v>
@@ -39650,52 +39653,52 @@
       <c r="I12" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="J12" s="51" t="s">
-        <v>36</v>
+      <c r="J12" s="51">
+        <v>1</v>
       </c>
       <c r="K12" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="L12" s="51" t="s">
-        <v>36</v>
+        <v>1736</v>
+      </c>
+      <c r="L12" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:26" ht="12.5">
-      <c r="A13" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="B13" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="D13" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="E13" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="F13" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="G13" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="H13" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="I13" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="J13" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="K13" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="L13" s="51" t="s">
-        <v>36</v>
+      <c r="A13" s="51">
+        <v>1</v>
+      </c>
+      <c r="B13" s="51">
+        <v>1</v>
+      </c>
+      <c r="C13" s="51">
+        <v>1</v>
+      </c>
+      <c r="D13" s="51">
+        <v>1</v>
+      </c>
+      <c r="E13" s="51">
+        <v>1</v>
+      </c>
+      <c r="F13" s="51">
+        <v>1</v>
+      </c>
+      <c r="G13" s="51">
+        <v>1</v>
+      </c>
+      <c r="H13" s="51">
+        <v>1</v>
+      </c>
+      <c r="I13" s="51">
+        <v>1</v>
+      </c>
+      <c r="J13" s="51">
+        <v>1</v>
+      </c>
+      <c r="K13" s="51">
+        <v>1</v>
+      </c>
+      <c r="L13" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:26" ht="12.5">
@@ -39757,41 +39760,41 @@
       <c r="Z16" s="28"/>
     </row>
     <row r="17" spans="1:26" ht="12.5">
-      <c r="A17" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="B17" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="D17" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="F17" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="I17" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="J17" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="K17" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="L17" s="51" t="s">
-        <v>36</v>
+      <c r="A17" s="51">
+        <v>1</v>
+      </c>
+      <c r="B17" s="51">
+        <v>1</v>
+      </c>
+      <c r="C17" s="51">
+        <v>1</v>
+      </c>
+      <c r="D17" s="51">
+        <v>1</v>
+      </c>
+      <c r="E17" s="51">
+        <v>1</v>
+      </c>
+      <c r="F17" s="51">
+        <v>1</v>
+      </c>
+      <c r="G17" s="51">
+        <v>1</v>
+      </c>
+      <c r="H17" s="51">
+        <v>1</v>
+      </c>
+      <c r="I17" s="51">
+        <v>1</v>
+      </c>
+      <c r="J17" s="51">
+        <v>1</v>
+      </c>
+      <c r="K17" s="51">
+        <v>1</v>
+      </c>
+      <c r="L17" s="51">
+        <v>1</v>
       </c>
       <c r="M17" s="28"/>
       <c r="N17" s="28"/>
@@ -39842,8 +39845,8 @@
       <c r="K18" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L18" s="51" t="s">
-        <v>36</v>
+      <c r="L18" s="51">
+        <v>1</v>
       </c>
       <c r="M18" s="28"/>
       <c r="N18" s="28"/>
@@ -39894,8 +39897,8 @@
       <c r="K19" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L19" s="51" t="s">
-        <v>36</v>
+      <c r="L19" s="51">
+        <v>1</v>
       </c>
       <c r="M19" s="28"/>
       <c r="N19" s="28"/>
@@ -39946,8 +39949,8 @@
       <c r="K20" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L20" s="51" t="s">
-        <v>36</v>
+      <c r="L20" s="51">
+        <v>1</v>
       </c>
       <c r="M20" s="28"/>
       <c r="N20" s="28"/>
@@ -39998,8 +40001,8 @@
       <c r="K21" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L21" s="51" t="s">
-        <v>36</v>
+      <c r="L21" s="51">
+        <v>1</v>
       </c>
       <c r="M21" s="28"/>
       <c r="N21" s="28"/>
@@ -40050,8 +40053,8 @@
       <c r="K22" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L22" s="51" t="s">
-        <v>36</v>
+      <c r="L22" s="51">
+        <v>1</v>
       </c>
       <c r="M22" s="28"/>
       <c r="N22" s="28"/>
@@ -40102,8 +40105,8 @@
       <c r="K23" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L23" s="51" t="s">
-        <v>36</v>
+      <c r="L23" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="24" spans="1:26" ht="12.5">
@@ -40140,8 +40143,8 @@
       <c r="K24" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L24" s="51" t="s">
-        <v>36</v>
+      <c r="L24" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="25" spans="1:26" ht="12.5">
@@ -40178,8 +40181,8 @@
       <c r="K25" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L25" s="51" t="s">
-        <v>36</v>
+      <c r="L25" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="26" spans="1:26" ht="12.5">
@@ -40211,13 +40214,13 @@
         <v>36</v>
       </c>
       <c r="J26" s="51" t="s">
-        <v>36</v>
+        <v>1414</v>
       </c>
       <c r="K26" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L26" s="51" t="s">
-        <v>36</v>
+      <c r="L26" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:26" ht="12.5">
@@ -40254,46 +40257,46 @@
       <c r="K27" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="L27" s="51" t="s">
-        <v>36</v>
+      <c r="L27" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:26" ht="12.5">
-      <c r="A28" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="B28" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="C28" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="D28" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="E28" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="F28" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="G28" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="H28" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="I28" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="J28" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="K28" s="51" t="s">
-        <v>36</v>
-      </c>
-      <c r="L28" s="51" t="s">
-        <v>36</v>
+      <c r="A28" s="51">
+        <v>1</v>
+      </c>
+      <c r="B28" s="51">
+        <v>1</v>
+      </c>
+      <c r="C28" s="51">
+        <v>1</v>
+      </c>
+      <c r="D28" s="51">
+        <v>1</v>
+      </c>
+      <c r="E28" s="51">
+        <v>1</v>
+      </c>
+      <c r="F28" s="51">
+        <v>1</v>
+      </c>
+      <c r="G28" s="51">
+        <v>1</v>
+      </c>
+      <c r="H28" s="51">
+        <v>1</v>
+      </c>
+      <c r="I28" s="51">
+        <v>1</v>
+      </c>
+      <c r="J28" s="51">
+        <v>1</v>
+      </c>
+      <c r="K28" s="51">
+        <v>1</v>
+      </c>
+      <c r="L28" s="51">
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:26" ht="12.5">

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADBCC828-5B8B-4FA2-B90C-3E372AF407BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1B935B-DC7A-476A-A494-B82F4634C0E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -5725,7 +5725,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6502,7 +6504,7 @@
         <v>33</v>
       </c>
       <c r="S4" s="40" t="s">
-        <v>1619</v>
+        <v>36</v>
       </c>
       <c r="T4" s="40" t="s">
         <v>35</v>
@@ -40048,7 +40050,7 @@
         <v>36</v>
       </c>
       <c r="J22" s="51" t="s">
-        <v>36</v>
+        <v>1416</v>
       </c>
       <c r="K22" s="51" t="s">
         <v>36</v>
@@ -40100,7 +40102,7 @@
         <v>36</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>36</v>
+        <v>1416</v>
       </c>
       <c r="K23" s="51" t="s">
         <v>36</v>
@@ -40214,7 +40216,7 @@
         <v>36</v>
       </c>
       <c r="J26" s="51" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="K26" s="51" t="s">
         <v>36</v>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A1B935B-DC7A-476A-A494-B82F4634C0E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F20790-F5D4-4806-AB18-5F200CC816E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="14" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7277" uniqueCount="1737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7336" uniqueCount="1738">
   <si>
     <t>NAME</t>
   </si>
@@ -5395,6 +5395,9 @@
   </si>
   <si>
     <t>s,battle6</t>
+  </si>
+  <si>
+    <t>STATS_EXACT</t>
   </si>
 </sst>
 </file>
@@ -35159,29 +35162,30 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87945C49-375A-40BB-B037-1C50621D6D44}">
-  <dimension ref="A1:V73"/>
+  <dimension ref="A1:W73"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="17.08984375" customWidth="1"/>
     <col min="2" max="3" width="15.81640625" customWidth="1"/>
     <col min="4" max="4" width="28.81640625" customWidth="1"/>
-    <col min="5" max="5" width="27.6328125" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" customWidth="1"/>
-    <col min="7" max="9" width="17.54296875" customWidth="1"/>
-    <col min="10" max="10" width="19.7265625" customWidth="1"/>
-    <col min="11" max="11" width="14.90625" customWidth="1"/>
-    <col min="12" max="12" width="18.6328125" customWidth="1"/>
-    <col min="13" max="13" width="14.08984375" customWidth="1"/>
-    <col min="14" max="15" width="21.453125" customWidth="1"/>
-    <col min="16" max="16" width="16.1796875" customWidth="1"/>
-    <col min="17" max="18" width="13.81640625" customWidth="1"/>
-    <col min="19" max="19" width="10.453125" customWidth="1"/>
-    <col min="20" max="20" width="11" customWidth="1"/>
-    <col min="21" max="21" width="7.1796875" customWidth="1"/>
-    <col min="22" max="22" width="13.81640625" customWidth="1"/>
+    <col min="5" max="5" width="22.7265625" customWidth="1"/>
+    <col min="6" max="6" width="27.6328125" customWidth="1"/>
+    <col min="7" max="7" width="13.453125" customWidth="1"/>
+    <col min="8" max="10" width="17.54296875" customWidth="1"/>
+    <col min="11" max="11" width="19.7265625" customWidth="1"/>
+    <col min="12" max="12" width="14.90625" customWidth="1"/>
+    <col min="13" max="13" width="18.6328125" customWidth="1"/>
+    <col min="14" max="14" width="14.08984375" customWidth="1"/>
+    <col min="15" max="16" width="21.453125" customWidth="1"/>
+    <col min="17" max="17" width="16.1796875" customWidth="1"/>
+    <col min="18" max="19" width="13.81640625" customWidth="1"/>
+    <col min="20" max="20" width="10.453125" customWidth="1"/>
+    <col min="21" max="21" width="11" customWidth="1"/>
+    <col min="22" max="22" width="7.1796875" customWidth="1"/>
+    <col min="23" max="23" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" ht="13">
+    <row r="1" spans="1:23" ht="13">
       <c r="A1" s="45" t="s">
         <v>1102</v>
       </c>
@@ -35195,61 +35199,64 @@
         <v>1419</v>
       </c>
       <c r="E1" s="45" t="s">
+        <v>1737</v>
+      </c>
+      <c r="F1" s="45" t="s">
         <v>1420</v>
       </c>
-      <c r="F1" s="45" t="s">
+      <c r="G1" s="45" t="s">
         <v>1563</v>
       </c>
-      <c r="G1" s="45" t="s">
+      <c r="H1" s="45" t="s">
         <v>1637</v>
       </c>
-      <c r="H1" s="45" t="s">
+      <c r="I1" s="45" t="s">
         <v>83</v>
       </c>
-      <c r="I1" s="45" t="s">
+      <c r="J1" s="45" t="s">
         <v>1421</v>
       </c>
-      <c r="J1" s="45" t="s">
+      <c r="K1" s="45" t="s">
         <v>1434</v>
       </c>
-      <c r="K1" s="45" t="s">
+      <c r="L1" s="45" t="s">
         <v>1526</v>
       </c>
-      <c r="L1" s="45" t="s">
+      <c r="M1" s="45" t="s">
         <v>1711</v>
       </c>
-      <c r="M1" s="45" t="s">
+      <c r="N1" s="45" t="s">
         <v>1437</v>
       </c>
-      <c r="N1" s="45" t="s">
+      <c r="O1" s="45" t="s">
         <v>1454</v>
       </c>
-      <c r="O1" s="45" t="s">
+      <c r="P1" s="45" t="s">
         <v>1554</v>
       </c>
-      <c r="P1" s="45" t="s">
+      <c r="Q1" s="45" t="s">
         <v>1462</v>
       </c>
-      <c r="Q1" s="45" t="s">
+      <c r="R1" s="45" t="s">
         <v>1463</v>
       </c>
-      <c r="R1" s="45" t="s">
+      <c r="S1" s="45" t="s">
         <v>1565</v>
       </c>
-      <c r="S1" s="45" t="s">
+      <c r="T1" s="45" t="s">
         <v>1525</v>
       </c>
-      <c r="T1" s="45" t="s">
+      <c r="U1" s="45" t="s">
         <v>1527</v>
       </c>
-      <c r="U1" s="45" t="s">
+      <c r="V1" s="45" t="s">
         <v>1644</v>
       </c>
-      <c r="V1" s="45" t="s">
+      <c r="W1" s="45" t="s">
         <v>1411</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:23">
       <c r="A2" s="46" t="s">
         <v>1424</v>
       </c>
@@ -35301,23 +35308,26 @@
       <c r="Q2" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R2" s="46">
+      <c r="R2" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S2" s="46">
         <v>-1</v>
       </c>
-      <c r="S2" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T2" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U2" s="46">
-        <v>0</v>
+      <c r="U2" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V2" s="46">
+        <v>0</v>
+      </c>
+      <c r="W2" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:23">
       <c r="A3" s="46" t="s">
         <v>1426</v>
       </c>
@@ -35369,23 +35379,26 @@
       <c r="Q3" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R3" s="46">
+      <c r="R3" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S3" s="46">
         <v>-1</v>
       </c>
-      <c r="S3" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T3" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U3" s="46">
-        <v>0</v>
+      <c r="U3" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V3" s="46">
+        <v>0</v>
+      </c>
+      <c r="W3" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:23">
       <c r="A4" s="46" t="s">
         <v>1427</v>
       </c>
@@ -35437,23 +35450,26 @@
       <c r="Q4" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R4" s="46">
+      <c r="R4" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S4" s="46">
         <v>-1</v>
       </c>
-      <c r="S4" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T4" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U4" s="46">
-        <v>0</v>
+      <c r="U4" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V4" s="46">
+        <v>0</v>
+      </c>
+      <c r="W4" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:23">
       <c r="A5" s="46" t="s">
         <v>1428</v>
       </c>
@@ -35505,23 +35521,26 @@
       <c r="Q5" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R5" s="46">
+      <c r="R5" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S5" s="46">
         <v>-1</v>
       </c>
-      <c r="S5" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T5" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U5" s="46">
-        <v>0</v>
+      <c r="U5" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V5" s="46">
+        <v>0</v>
+      </c>
+      <c r="W5" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:23">
       <c r="A6" s="46" t="s">
         <v>1430</v>
       </c>
@@ -35573,23 +35592,26 @@
       <c r="Q6" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R6" s="46">
+      <c r="R6" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S6" s="46">
         <v>-1</v>
       </c>
-      <c r="S6" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T6" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U6" s="46">
-        <v>0</v>
+      <c r="U6" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V6" s="46">
+        <v>0</v>
+      </c>
+      <c r="W6" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:23">
       <c r="A7" s="46" t="s">
         <v>1431</v>
       </c>
@@ -35641,23 +35663,26 @@
       <c r="Q7" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R7" s="46">
+      <c r="R7" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S7" s="46">
         <v>-1</v>
       </c>
-      <c r="S7" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T7" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U7" s="46">
-        <v>0</v>
+      <c r="U7" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V7" s="46">
+        <v>0</v>
+      </c>
+      <c r="W7" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
+    <row r="8" spans="1:23">
       <c r="A8" s="46" t="s">
         <v>1435</v>
       </c>
@@ -35686,11 +35711,11 @@
         <v>36</v>
       </c>
       <c r="J8" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="46" t="s">
         <v>1501</v>
       </c>
-      <c r="K8" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="L8" s="46" t="s">
         <v>36</v>
       </c>
@@ -35709,23 +35734,26 @@
       <c r="Q8" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R8" s="46">
+      <c r="R8" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S8" s="46">
         <v>-1</v>
       </c>
-      <c r="S8" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T8" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U8" s="46">
-        <v>0</v>
+      <c r="U8" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V8" s="46">
+        <v>0</v>
+      </c>
+      <c r="W8" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:23">
       <c r="A9" s="46" t="s">
         <v>1436</v>
       </c>
@@ -35754,11 +35782,11 @@
         <v>36</v>
       </c>
       <c r="J9" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" s="46" t="s">
         <v>1439</v>
       </c>
-      <c r="K9" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="L9" s="46" t="s">
         <v>36</v>
       </c>
@@ -35777,23 +35805,26 @@
       <c r="Q9" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R9" s="46">
+      <c r="R9" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S9" s="46">
         <v>-1</v>
       </c>
-      <c r="S9" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T9" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U9" s="46">
-        <v>0</v>
+      <c r="U9" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V9" s="46">
+        <v>0</v>
+      </c>
+      <c r="W9" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:23">
       <c r="A10" s="46" t="s">
         <v>1440</v>
       </c>
@@ -35822,11 +35853,11 @@
         <v>36</v>
       </c>
       <c r="J10" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" s="46" t="s">
         <v>1441</v>
       </c>
-      <c r="K10" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="L10" s="46" t="s">
         <v>36</v>
       </c>
@@ -35845,23 +35876,26 @@
       <c r="Q10" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R10" s="46">
+      <c r="R10" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S10" s="46">
         <v>-1</v>
       </c>
-      <c r="S10" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T10" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U10" s="46">
-        <v>0</v>
+      <c r="U10" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V10" s="46">
+        <v>0</v>
+      </c>
+      <c r="W10" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:23">
       <c r="A11" s="46" t="s">
         <v>1442</v>
       </c>
@@ -35913,23 +35947,26 @@
       <c r="Q11" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R11" s="46">
+      <c r="R11" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S11" s="46">
         <v>-1</v>
       </c>
-      <c r="S11" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T11" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U11" s="46">
-        <v>0</v>
+      <c r="U11" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V11" s="46">
+        <v>0</v>
+      </c>
+      <c r="W11" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:22">
+    <row r="12" spans="1:23">
       <c r="A12" s="46" t="s">
         <v>1443</v>
       </c>
@@ -35981,23 +36018,26 @@
       <c r="Q12" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R12" s="46">
+      <c r="R12" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S12" s="46">
         <v>-1</v>
       </c>
-      <c r="S12" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T12" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U12" s="46">
-        <v>0</v>
+      <c r="U12" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V12" s="46">
+        <v>0</v>
+      </c>
+      <c r="W12" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:22">
+    <row r="13" spans="1:23">
       <c r="A13" s="46" t="s">
         <v>1445</v>
       </c>
@@ -36049,23 +36089,26 @@
       <c r="Q13" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R13" s="46">
+      <c r="R13" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S13" s="46">
         <v>-1</v>
       </c>
-      <c r="S13" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T13" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U13" s="46">
-        <v>0</v>
+      <c r="U13" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V13" s="46">
+        <v>0</v>
+      </c>
+      <c r="W13" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="14" spans="1:22">
+    <row r="14" spans="1:23">
       <c r="A14" s="46" t="s">
         <v>1446</v>
       </c>
@@ -36117,23 +36160,26 @@
       <c r="Q14" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R14" s="46">
+      <c r="R14" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S14" s="46">
         <v>-1</v>
       </c>
-      <c r="S14" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T14" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U14" s="46">
-        <v>0</v>
+      <c r="U14" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V14" s="46">
+        <v>0</v>
+      </c>
+      <c r="W14" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:22">
+    <row r="15" spans="1:23">
       <c r="A15" s="46" t="s">
         <v>1447</v>
       </c>
@@ -36185,23 +36231,26 @@
       <c r="Q15" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R15" s="46">
+      <c r="R15" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S15" s="46">
         <v>-1</v>
       </c>
-      <c r="S15" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T15" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U15" s="46">
-        <v>0</v>
+      <c r="U15" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V15" s="46">
+        <v>0</v>
+      </c>
+      <c r="W15" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="16" spans="1:22">
+    <row r="16" spans="1:23">
       <c r="A16" s="46" t="s">
         <v>1448</v>
       </c>
@@ -36253,23 +36302,26 @@
       <c r="Q16" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R16" s="46">
+      <c r="R16" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S16" s="46">
         <v>-1</v>
       </c>
-      <c r="S16" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T16" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U16" s="46">
-        <v>0</v>
+      <c r="U16" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V16" s="46">
+        <v>0</v>
+      </c>
+      <c r="W16" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:22">
+    <row r="17" spans="1:23">
       <c r="A17" s="46" t="s">
         <v>1450</v>
       </c>
@@ -36310,34 +36362,37 @@
         <v>36</v>
       </c>
       <c r="N17" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="O17" s="46" t="s">
         <v>1456</v>
       </c>
-      <c r="O17" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="P17" s="46" t="s">
         <v>36</v>
       </c>
       <c r="Q17" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R17" s="46">
+      <c r="R17" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S17" s="46">
         <v>-1</v>
       </c>
-      <c r="S17" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T17" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U17" s="46">
-        <v>0</v>
+      <c r="U17" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V17" s="46">
+        <v>0</v>
+      </c>
+      <c r="W17" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="18" spans="1:22">
+    <row r="18" spans="1:23">
       <c r="A18" s="46" t="s">
         <v>1451</v>
       </c>
@@ -36378,34 +36433,37 @@
         <v>36</v>
       </c>
       <c r="N18" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="O18" s="46" t="s">
         <v>1531</v>
       </c>
-      <c r="O18" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="P18" s="46" t="s">
         <v>36</v>
       </c>
       <c r="Q18" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R18" s="46">
+      <c r="R18" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S18" s="46">
         <v>-1</v>
       </c>
-      <c r="S18" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T18" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U18" s="46">
-        <v>0</v>
+      <c r="U18" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V18" s="46">
+        <v>0</v>
+      </c>
+      <c r="W18" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="1:22">
+    <row r="19" spans="1:23">
       <c r="A19" s="46" t="s">
         <v>1452</v>
       </c>
@@ -36446,34 +36504,37 @@
         <v>36</v>
       </c>
       <c r="N19" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="O19" s="46" t="s">
         <v>1457</v>
       </c>
-      <c r="O19" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="P19" s="46" t="s">
         <v>36</v>
       </c>
       <c r="Q19" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R19" s="46">
+      <c r="R19" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S19" s="46">
         <v>-1</v>
       </c>
-      <c r="S19" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T19" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U19" s="46">
-        <v>0</v>
+      <c r="U19" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V19" s="46">
+        <v>0</v>
+      </c>
+      <c r="W19" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="20" spans="1:22">
+    <row r="20" spans="1:23">
       <c r="A20" s="46" t="s">
         <v>1458</v>
       </c>
@@ -36502,11 +36563,11 @@
         <v>36</v>
       </c>
       <c r="J20" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="K20" s="46" t="s">
         <v>1491</v>
       </c>
-      <c r="K20" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="L20" s="46" t="s">
         <v>36</v>
       </c>
@@ -36525,23 +36586,26 @@
       <c r="Q20" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R20" s="46">
+      <c r="R20" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S20" s="46">
         <v>-1</v>
       </c>
-      <c r="S20" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T20" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U20" s="46">
-        <v>0</v>
+      <c r="U20" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V20" s="46">
+        <v>0</v>
+      </c>
+      <c r="W20" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="1:22">
+    <row r="21" spans="1:23">
       <c r="A21" s="46" t="s">
         <v>1459</v>
       </c>
@@ -36593,23 +36657,26 @@
       <c r="Q21" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R21" s="46">
+      <c r="R21" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S21" s="46">
         <v>-1</v>
       </c>
-      <c r="S21" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T21" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U21" s="46">
-        <v>0</v>
+      <c r="U21" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V21" s="46">
+        <v>0</v>
+      </c>
+      <c r="W21" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:22">
+    <row r="22" spans="1:23">
       <c r="A22" s="46" t="s">
         <v>1460</v>
       </c>
@@ -36661,23 +36728,26 @@
       <c r="Q22" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R22" s="46">
+      <c r="R22" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S22" s="46">
         <v>-1</v>
       </c>
-      <c r="S22" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T22" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U22" s="46">
-        <v>0</v>
+      <c r="U22" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V22" s="46">
+        <v>0</v>
+      </c>
+      <c r="W22" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="23" spans="1:22">
+    <row r="23" spans="1:23">
       <c r="A23" s="46" t="s">
         <v>1470</v>
       </c>
@@ -36718,34 +36788,37 @@
         <v>36</v>
       </c>
       <c r="N23" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="O23" s="46" t="s">
         <v>1498</v>
       </c>
-      <c r="O23" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="P23" s="46" t="s">
         <v>36</v>
       </c>
       <c r="Q23" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R23" s="46">
+      <c r="R23" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S23" s="46">
         <v>-1</v>
       </c>
-      <c r="S23" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T23" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U23" s="46">
-        <v>0</v>
+      <c r="U23" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V23" s="46">
+        <v>0</v>
+      </c>
+      <c r="W23" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:23">
       <c r="A24" s="46" t="s">
         <v>1471</v>
       </c>
@@ -36797,23 +36870,26 @@
       <c r="Q24" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R24" s="46">
+      <c r="R24" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S24" s="46">
         <v>-1</v>
       </c>
-      <c r="S24" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T24" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U24" s="46">
-        <v>0</v>
+      <c r="U24" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V24" s="46">
+        <v>0</v>
+      </c>
+      <c r="W24" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:23">
       <c r="A25" s="46" t="s">
         <v>1472</v>
       </c>
@@ -36865,23 +36941,26 @@
       <c r="Q25" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R25" s="46">
+      <c r="R25" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S25" s="46">
         <v>-1</v>
       </c>
-      <c r="S25" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T25" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U25" s="46">
-        <v>0</v>
+      <c r="U25" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V25" s="46">
+        <v>0</v>
+      </c>
+      <c r="W25" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
+    <row r="26" spans="1:23">
       <c r="A26" s="46"/>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -36904,8 +36983,9 @@
       <c r="T26" s="46"/>
       <c r="U26" s="46"/>
       <c r="V26" s="46"/>
-    </row>
-    <row r="27" spans="1:22">
+      <c r="W26" s="46"/>
+    </row>
+    <row r="27" spans="1:23">
       <c r="A27" s="46" t="s">
         <v>1555</v>
       </c>
@@ -36919,14 +36999,14 @@
         <v>36</v>
       </c>
       <c r="E27" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F27" s="46" t="s">
         <v>1556</v>
       </c>
-      <c r="F27" s="46" t="s">
+      <c r="G27" s="46" t="s">
         <v>1564</v>
       </c>
-      <c r="G27" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="H27" s="46" t="s">
         <v>36</v>
       </c>
@@ -36949,31 +37029,34 @@
         <v>36</v>
       </c>
       <c r="O27" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="P27" s="46" t="s">
         <v>1555</v>
       </c>
-      <c r="P27" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="Q27" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R27" s="46">
+      <c r="R27" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S27" s="46">
         <v>-1</v>
       </c>
-      <c r="S27" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T27" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U27" s="46">
-        <v>0</v>
+      <c r="U27" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V27" s="46">
+        <v>0</v>
+      </c>
+      <c r="W27" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:23">
       <c r="A28" s="46" t="s">
         <v>1566</v>
       </c>
@@ -36987,14 +37070,14 @@
         <v>36</v>
       </c>
       <c r="E28" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F28" s="46" t="s">
         <v>1567</v>
       </c>
-      <c r="F28" s="46" t="s">
+      <c r="G28" s="46" t="s">
         <v>1568</v>
       </c>
-      <c r="G28" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="H28" s="46" t="s">
         <v>36</v>
       </c>
@@ -37017,31 +37100,34 @@
         <v>36</v>
       </c>
       <c r="O28" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="P28" s="46" t="s">
         <v>1566</v>
       </c>
-      <c r="P28" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="Q28" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R28" s="46">
+      <c r="R28" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S28" s="46">
         <v>-1</v>
       </c>
-      <c r="S28" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T28" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U28" s="46">
-        <v>0</v>
+      <c r="U28" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V28" s="46">
+        <v>0</v>
+      </c>
+      <c r="W28" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:23">
       <c r="A31" s="46" t="s">
         <v>1542</v>
       </c>
@@ -37093,23 +37179,26 @@
       <c r="Q31" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R31" s="46">
+      <c r="R31" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S31" s="46">
         <v>-1</v>
       </c>
-      <c r="S31" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T31" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U31" s="46">
-        <v>0</v>
+      <c r="U31" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V31" s="46">
+        <v>0</v>
+      </c>
+      <c r="W31" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:23">
       <c r="A32" s="46" t="s">
         <v>1541</v>
       </c>
@@ -37161,23 +37250,26 @@
       <c r="Q32" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R32" s="46">
+      <c r="R32" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S32" s="46">
         <v>-1</v>
       </c>
-      <c r="S32" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T32" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U32" s="46">
-        <v>0</v>
+      <c r="U32" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V32" s="46">
+        <v>0</v>
+      </c>
+      <c r="W32" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="1:22">
+    <row r="35" spans="1:23">
       <c r="A35" s="46" t="s">
         <v>1543</v>
       </c>
@@ -37229,23 +37321,26 @@
       <c r="Q35" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R35" s="46">
+      <c r="R35" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S35" s="46">
         <v>-1</v>
       </c>
-      <c r="S35" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T35" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U35" s="46">
-        <v>0</v>
+      <c r="U35" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V35" s="46">
+        <v>0</v>
+      </c>
+      <c r="W35" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="1:22">
+    <row r="36" spans="1:23">
       <c r="A36" s="46" t="s">
         <v>1544</v>
       </c>
@@ -37297,23 +37392,26 @@
       <c r="Q36" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R36" s="46">
+      <c r="R36" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S36" s="46">
         <v>-1</v>
       </c>
-      <c r="S36" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T36" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U36" s="46">
-        <v>0</v>
+      <c r="U36" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V36" s="46">
+        <v>0</v>
+      </c>
+      <c r="W36" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="39" spans="1:22">
+    <row r="39" spans="1:23">
       <c r="A39" s="46" t="s">
         <v>1545</v>
       </c>
@@ -37365,23 +37463,26 @@
       <c r="Q39" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R39" s="46">
+      <c r="R39" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S39" s="46">
         <v>-1</v>
       </c>
-      <c r="S39" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T39" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U39" s="46">
-        <v>0</v>
+      <c r="U39" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V39" s="46">
+        <v>0</v>
+      </c>
+      <c r="W39" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="40" spans="1:22">
+    <row r="40" spans="1:23">
       <c r="A40" s="46" t="s">
         <v>1546</v>
       </c>
@@ -37433,23 +37534,26 @@
       <c r="Q40" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R40" s="46">
+      <c r="R40" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S40" s="46">
         <v>-1</v>
       </c>
-      <c r="S40" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T40" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U40" s="46">
-        <v>0</v>
+      <c r="U40" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V40" s="46">
+        <v>0</v>
+      </c>
+      <c r="W40" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="45" spans="1:22">
+    <row r="45" spans="1:23">
       <c r="A45" s="46" t="s">
         <v>1571</v>
       </c>
@@ -37501,23 +37605,26 @@
       <c r="Q45" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R45" s="46">
+      <c r="R45" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S45" s="46">
         <v>-1</v>
       </c>
-      <c r="S45" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T45" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U45" s="46">
-        <v>0</v>
+      <c r="U45" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V45" s="46">
+        <v>0</v>
+      </c>
+      <c r="W45" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="46" spans="1:22">
+    <row r="46" spans="1:23">
       <c r="A46" s="46" t="s">
         <v>1572</v>
       </c>
@@ -37569,23 +37676,26 @@
       <c r="Q46" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R46" s="46">
+      <c r="R46" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S46" s="46">
         <v>-1</v>
       </c>
-      <c r="S46" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T46" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U46" s="46">
-        <v>0</v>
+      <c r="U46" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V46" s="46">
+        <v>0</v>
+      </c>
+      <c r="W46" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="47" spans="1:22">
+    <row r="47" spans="1:23">
       <c r="A47" s="46" t="s">
         <v>1573</v>
       </c>
@@ -37637,23 +37747,26 @@
       <c r="Q47" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R47" s="46">
+      <c r="R47" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S47" s="46">
         <v>-1</v>
       </c>
-      <c r="S47" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T47" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U47" s="46">
-        <v>0</v>
+      <c r="U47" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V47" s="46">
+        <v>0</v>
+      </c>
+      <c r="W47" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="48" spans="1:22">
+    <row r="48" spans="1:23">
       <c r="A48" s="46" t="s">
         <v>1589</v>
       </c>
@@ -37705,23 +37818,26 @@
       <c r="Q48" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R48" s="46">
+      <c r="R48" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S48" s="46">
         <v>-1</v>
       </c>
-      <c r="S48" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T48" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U48" s="46">
-        <v>0</v>
+      <c r="U48" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V48" s="46">
+        <v>0</v>
+      </c>
+      <c r="W48" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="49" spans="1:22">
+    <row r="49" spans="1:23">
       <c r="A49" s="46" t="s">
         <v>1574</v>
       </c>
@@ -37773,23 +37889,26 @@
       <c r="Q49" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R49" s="46">
+      <c r="R49" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S49" s="46">
         <v>-1</v>
       </c>
-      <c r="S49" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T49" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U49" s="46">
-        <v>0</v>
+      <c r="U49" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V49" s="46">
+        <v>0</v>
+      </c>
+      <c r="W49" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="50" spans="1:22">
+    <row r="50" spans="1:23">
       <c r="A50" s="46" t="s">
         <v>1575</v>
       </c>
@@ -37841,23 +37960,26 @@
       <c r="Q50" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R50" s="46">
+      <c r="R50" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S50" s="46">
         <v>-1</v>
       </c>
-      <c r="S50" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T50" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U50" s="46">
-        <v>0</v>
+      <c r="U50" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V50" s="46">
+        <v>0</v>
+      </c>
+      <c r="W50" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="51" spans="1:22">
+    <row r="51" spans="1:23">
       <c r="A51" s="46" t="s">
         <v>1576</v>
       </c>
@@ -37909,23 +38031,26 @@
       <c r="Q51" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R51" s="46">
+      <c r="R51" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S51" s="46">
         <v>-1</v>
       </c>
-      <c r="S51" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T51" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U51" s="46">
-        <v>0</v>
+      <c r="U51" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V51" s="46">
+        <v>0</v>
+      </c>
+      <c r="W51" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="52" spans="1:22">
+    <row r="52" spans="1:23">
       <c r="A52" s="46" t="s">
         <v>1590</v>
       </c>
@@ -37977,23 +38102,26 @@
       <c r="Q52" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R52" s="46">
+      <c r="R52" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S52" s="46">
         <v>-1</v>
       </c>
-      <c r="S52" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T52" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U52" s="46">
-        <v>0</v>
+      <c r="U52" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V52" s="46">
+        <v>0</v>
+      </c>
+      <c r="W52" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="53" spans="1:22">
+    <row r="53" spans="1:23">
       <c r="A53" s="46" t="s">
         <v>1577</v>
       </c>
@@ -38045,23 +38173,26 @@
       <c r="Q53" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R53" s="46">
+      <c r="R53" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S53" s="46">
         <v>-1</v>
       </c>
-      <c r="S53" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T53" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U53" s="46">
-        <v>0</v>
+      <c r="U53" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V53" s="46">
+        <v>0</v>
+      </c>
+      <c r="W53" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="54" spans="1:22">
+    <row r="54" spans="1:23">
       <c r="A54" s="46" t="s">
         <v>1578</v>
       </c>
@@ -38113,23 +38244,26 @@
       <c r="Q54" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R54" s="46">
+      <c r="R54" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S54" s="46">
         <v>-1</v>
       </c>
-      <c r="S54" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T54" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U54" s="46">
-        <v>0</v>
+      <c r="U54" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V54" s="46">
+        <v>0</v>
+      </c>
+      <c r="W54" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="55" spans="1:22">
+    <row r="55" spans="1:23">
       <c r="A55" s="46" t="s">
         <v>1579</v>
       </c>
@@ -38181,23 +38315,26 @@
       <c r="Q55" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R55" s="46">
+      <c r="R55" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S55" s="46">
         <v>-1</v>
       </c>
-      <c r="S55" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T55" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U55" s="46">
-        <v>0</v>
+      <c r="U55" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V55" s="46">
+        <v>0</v>
+      </c>
+      <c r="W55" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="56" spans="1:22">
+    <row r="56" spans="1:23">
       <c r="A56" s="46" t="s">
         <v>1591</v>
       </c>
@@ -38249,23 +38386,26 @@
       <c r="Q56" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R56" s="46">
+      <c r="R56" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S56" s="46">
         <v>-1</v>
       </c>
-      <c r="S56" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T56" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U56" s="46">
-        <v>0</v>
+      <c r="U56" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V56" s="46">
+        <v>0</v>
+      </c>
+      <c r="W56" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="57" spans="1:22">
+    <row r="57" spans="1:23">
       <c r="A57" s="46" t="s">
         <v>1580</v>
       </c>
@@ -38317,23 +38457,26 @@
       <c r="Q57" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R57" s="46">
+      <c r="R57" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S57" s="46">
         <v>-1</v>
       </c>
-      <c r="S57" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T57" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U57" s="46">
-        <v>0</v>
+      <c r="U57" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V57" s="46">
+        <v>0</v>
+      </c>
+      <c r="W57" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="58" spans="1:22">
+    <row r="58" spans="1:23">
       <c r="A58" s="46" t="s">
         <v>1581</v>
       </c>
@@ -38385,23 +38528,26 @@
       <c r="Q58" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R58" s="46">
+      <c r="R58" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S58" s="46">
         <v>-1</v>
       </c>
-      <c r="S58" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T58" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U58" s="46">
-        <v>0</v>
+      <c r="U58" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V58" s="46">
+        <v>0</v>
+      </c>
+      <c r="W58" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="59" spans="1:22">
+    <row r="59" spans="1:23">
       <c r="A59" s="46" t="s">
         <v>1582</v>
       </c>
@@ -38453,23 +38599,26 @@
       <c r="Q59" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R59" s="46">
+      <c r="R59" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S59" s="46">
         <v>-1</v>
       </c>
-      <c r="S59" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T59" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U59" s="46">
-        <v>0</v>
+      <c r="U59" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V59" s="46">
+        <v>0</v>
+      </c>
+      <c r="W59" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="60" spans="1:22">
+    <row r="60" spans="1:23">
       <c r="A60" s="46" t="s">
         <v>1592</v>
       </c>
@@ -38521,23 +38670,26 @@
       <c r="Q60" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R60" s="46">
+      <c r="R60" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S60" s="46">
         <v>-1</v>
       </c>
-      <c r="S60" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T60" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U60" s="46">
-        <v>0</v>
+      <c r="U60" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V60" s="46">
+        <v>0</v>
+      </c>
+      <c r="W60" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="61" spans="1:22">
+    <row r="61" spans="1:23">
       <c r="A61" s="46" t="s">
         <v>1583</v>
       </c>
@@ -38589,23 +38741,26 @@
       <c r="Q61" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R61" s="46">
+      <c r="R61" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S61" s="46">
         <v>-1</v>
       </c>
-      <c r="S61" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T61" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U61" s="46">
-        <v>0</v>
+      <c r="U61" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V61" s="46">
+        <v>0</v>
+      </c>
+      <c r="W61" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="62" spans="1:22">
+    <row r="62" spans="1:23">
       <c r="A62" s="46" t="s">
         <v>1584</v>
       </c>
@@ -38657,23 +38812,26 @@
       <c r="Q62" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R62" s="46">
+      <c r="R62" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S62" s="46">
         <v>-1</v>
       </c>
-      <c r="S62" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T62" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U62" s="46">
-        <v>0</v>
+      <c r="U62" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V62" s="46">
+        <v>0</v>
+      </c>
+      <c r="W62" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="63" spans="1:22">
+    <row r="63" spans="1:23">
       <c r="A63" s="46" t="s">
         <v>1585</v>
       </c>
@@ -38725,23 +38883,26 @@
       <c r="Q63" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R63" s="46">
+      <c r="R63" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S63" s="46">
         <v>-1</v>
       </c>
-      <c r="S63" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T63" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U63" s="46">
-        <v>0</v>
+      <c r="U63" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V63" s="46">
+        <v>0</v>
+      </c>
+      <c r="W63" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="64" spans="1:22">
+    <row r="64" spans="1:23">
       <c r="A64" s="46" t="s">
         <v>1593</v>
       </c>
@@ -38793,23 +38954,26 @@
       <c r="Q64" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R64" s="46">
+      <c r="R64" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S64" s="46">
         <v>-1</v>
       </c>
-      <c r="S64" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T64" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U64" s="46">
-        <v>0</v>
+      <c r="U64" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V64" s="46">
+        <v>0</v>
+      </c>
+      <c r="W64" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="66" spans="1:22">
+    <row r="66" spans="1:23">
       <c r="A66" s="46" t="s">
         <v>1659</v>
       </c>
@@ -38823,14 +38987,14 @@
         <v>1658</v>
       </c>
       <c r="E66" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F66" s="46" t="s">
         <v>1556</v>
       </c>
-      <c r="F66" s="46" t="s">
+      <c r="G66" s="46" t="s">
         <v>1564</v>
       </c>
-      <c r="G66" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="H66" s="46" t="s">
         <v>36</v>
       </c>
@@ -38853,31 +39017,34 @@
         <v>36</v>
       </c>
       <c r="O66" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="P66" s="46" t="s">
         <v>1555</v>
       </c>
-      <c r="P66" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="Q66" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R66" s="46">
+      <c r="R66" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S66" s="46">
         <v>-1</v>
       </c>
-      <c r="S66" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T66" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U66" s="46">
-        <v>0</v>
+      <c r="U66" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V66" s="46">
+        <v>0</v>
+      </c>
+      <c r="W66" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="68" spans="1:22">
+    <row r="68" spans="1:23">
       <c r="A68" s="46" t="s">
         <v>1710</v>
       </c>
@@ -38924,28 +39091,31 @@
         <v>36</v>
       </c>
       <c r="P68" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q68" s="46" t="s">
         <v>1697</v>
       </c>
-      <c r="Q68" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="R68" s="46">
+      <c r="R68" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S68" s="46">
         <v>-1</v>
       </c>
-      <c r="S68" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T68" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="U68" s="46" t="s">
         <v>1720</v>
       </c>
-      <c r="U68" s="46">
-        <v>1</v>
-      </c>
       <c r="V68" s="46">
+        <v>1</v>
+      </c>
+      <c r="W68" s="46">
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:22">
+    <row r="70" spans="1:23">
       <c r="A70" s="46" t="s">
         <v>1712</v>
       </c>
@@ -38959,11 +39129,11 @@
         <v>36</v>
       </c>
       <c r="E70" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F70" s="46" t="s">
         <v>1716</v>
       </c>
-      <c r="F70" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="G70" s="46" t="s">
         <v>36</v>
       </c>
@@ -38997,23 +39167,26 @@
       <c r="Q70" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R70" s="46">
+      <c r="R70" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S70" s="46">
         <v>-1</v>
       </c>
-      <c r="S70" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T70" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U70" s="46">
-        <v>1</v>
+      <c r="U70" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V70" s="46">
+        <v>1</v>
+      </c>
+      <c r="W70" s="46">
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:22">
+    <row r="71" spans="1:23">
       <c r="A71" s="46" t="s">
         <v>1713</v>
       </c>
@@ -39027,11 +39200,11 @@
         <v>36</v>
       </c>
       <c r="E71" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F71" s="46" t="s">
         <v>1717</v>
       </c>
-      <c r="F71" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="G71" s="46" t="s">
         <v>36</v>
       </c>
@@ -39065,23 +39238,26 @@
       <c r="Q71" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R71" s="46">
+      <c r="R71" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S71" s="46">
         <v>-1</v>
       </c>
-      <c r="S71" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T71" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U71" s="46">
-        <v>1</v>
+      <c r="U71" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V71" s="46">
+        <v>1</v>
+      </c>
+      <c r="W71" s="46">
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:22">
+    <row r="72" spans="1:23">
       <c r="A72" s="46" t="s">
         <v>1714</v>
       </c>
@@ -39095,11 +39271,11 @@
         <v>36</v>
       </c>
       <c r="E72" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F72" s="46" t="s">
         <v>1718</v>
       </c>
-      <c r="F72" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="G72" s="46" t="s">
         <v>36</v>
       </c>
@@ -39133,23 +39309,26 @@
       <c r="Q72" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R72" s="46">
+      <c r="R72" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S72" s="46">
         <v>-1</v>
       </c>
-      <c r="S72" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T72" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U72" s="46">
-        <v>1</v>
+      <c r="U72" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V72" s="46">
+        <v>1</v>
+      </c>
+      <c r="W72" s="46">
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:22">
+    <row r="73" spans="1:23">
       <c r="A73" s="46" t="s">
         <v>1715</v>
       </c>
@@ -39163,11 +39342,11 @@
         <v>36</v>
       </c>
       <c r="E73" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F73" s="46" t="s">
         <v>1719</v>
       </c>
-      <c r="F73" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="G73" s="46" t="s">
         <v>36</v>
       </c>
@@ -39201,19 +39380,22 @@
       <c r="Q73" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="R73" s="46">
+      <c r="R73" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="S73" s="46">
         <v>-1</v>
       </c>
-      <c r="S73" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="T73" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="U73" s="46">
-        <v>1</v>
+      <c r="U73" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="V73" s="46">
+        <v>1</v>
+      </c>
+      <c r="W73" s="46">
         <v>10</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77F20790-F5D4-4806-AB18-5F200CC816E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE38DD0B-5B23-4337-A8F8-8064ED4FA16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="14" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7336" uniqueCount="1738">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7341" uniqueCount="1739">
   <si>
     <t>NAME</t>
   </si>
@@ -5398,6 +5398,9 @@
   </si>
   <si>
     <t>STATS_EXACT</t>
+  </si>
+  <si>
+    <t>shard</t>
   </si>
 </sst>
 </file>
@@ -41450,7 +41453,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4267B9-6C50-42DE-8EEA-ACDE778B1226}">
-  <dimension ref="A1:U23"/>
+  <dimension ref="A1:U24"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="15.26953125" customWidth="1"/>
@@ -42952,6 +42955,71 @@
         <v>11</v>
       </c>
       <c r="U23" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21">
+      <c r="A24" s="44" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B24">
+        <v>0</v>
+      </c>
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24">
+        <v>0</v>
+      </c>
+      <c r="E24">
+        <v>0</v>
+      </c>
+      <c r="F24">
+        <v>0</v>
+      </c>
+      <c r="G24">
+        <v>0</v>
+      </c>
+      <c r="H24">
+        <v>0</v>
+      </c>
+      <c r="I24">
+        <v>0</v>
+      </c>
+      <c r="J24">
+        <v>0</v>
+      </c>
+      <c r="K24">
+        <v>0</v>
+      </c>
+      <c r="L24">
+        <v>0</v>
+      </c>
+      <c r="M24">
+        <v>0</v>
+      </c>
+      <c r="N24">
+        <v>10</v>
+      </c>
+      <c r="O24" s="44" t="s">
+        <v>1376</v>
+      </c>
+      <c r="P24">
+        <v>0</v>
+      </c>
+      <c r="Q24">
+        <v>1</v>
+      </c>
+      <c r="R24" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="S24" t="s">
+        <v>36</v>
+      </c>
+      <c r="T24">
+        <v>11</v>
+      </c>
+      <c r="U24" t="s">
         <v>1666</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE38DD0B-5B23-4337-A8F8-8064ED4FA16E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF48447-6FAB-4A7E-BB9E-E4952037D25F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42497,7 +42497,7 @@
         <v>1624</v>
       </c>
       <c r="T16">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="U16" t="s">
         <v>1679</v>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FF48447-6FAB-4A7E-BB9E-E4952037D25F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580A8A56-B507-4566-9E08-7665C983E5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="14" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7341" uniqueCount="1739">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7461" uniqueCount="1745">
   <si>
     <t>NAME</t>
   </si>
@@ -5401,6 +5401,24 @@
   </si>
   <si>
     <t>shard</t>
+  </si>
+  <si>
+    <t>sphere_draw</t>
+  </si>
+  <si>
+    <t>draw_skl</t>
+  </si>
+  <si>
+    <t>draw_ten_skl</t>
+  </si>
+  <si>
+    <t>skl_draw1</t>
+  </si>
+  <si>
+    <t>itm_draw1</t>
+  </si>
+  <si>
+    <t>EVENT_NUM</t>
   </si>
 </sst>
 </file>
@@ -30986,7 +31004,7 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:G41"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="3" max="3" width="10.36328125" customWidth="1"/>
@@ -31612,6 +31630,190 @@
         <v>1728</v>
       </c>
       <c r="G41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7">
+      <c r="A43" t="s">
+        <v>1742</v>
+      </c>
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>25</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="E43">
+        <v>1</v>
+      </c>
+      <c r="F43" t="s">
+        <v>35</v>
+      </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" t="s">
+        <v>36</v>
+      </c>
+      <c r="B44">
+        <v>0</v>
+      </c>
+      <c r="C44">
+        <v>25</v>
+      </c>
+      <c r="D44">
+        <v>1</v>
+      </c>
+      <c r="E44">
+        <v>1</v>
+      </c>
+      <c r="F44" t="s">
+        <v>42</v>
+      </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7">
+      <c r="A45" t="s">
+        <v>36</v>
+      </c>
+      <c r="B45">
+        <v>0</v>
+      </c>
+      <c r="C45">
+        <v>25</v>
+      </c>
+      <c r="D45">
+        <v>1</v>
+      </c>
+      <c r="E45">
+        <v>1</v>
+      </c>
+      <c r="F45" t="s">
+        <v>1477</v>
+      </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7">
+      <c r="A46" t="s">
+        <v>36</v>
+      </c>
+      <c r="B46">
+        <v>0</v>
+      </c>
+      <c r="C46">
+        <v>25</v>
+      </c>
+      <c r="D46">
+        <v>1</v>
+      </c>
+      <c r="E46">
+        <v>1</v>
+      </c>
+      <c r="F46" t="s">
+        <v>1493</v>
+      </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" t="s">
+        <v>1743</v>
+      </c>
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
+        <v>25</v>
+      </c>
+      <c r="D48">
+        <v>1</v>
+      </c>
+      <c r="E48">
+        <v>1</v>
+      </c>
+      <c r="F48" t="s">
+        <v>1375</v>
+      </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7">
+      <c r="A49" t="s">
+        <v>36</v>
+      </c>
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>25</v>
+      </c>
+      <c r="D49">
+        <v>1</v>
+      </c>
+      <c r="E49">
+        <v>1</v>
+      </c>
+      <c r="F49" t="s">
+        <v>1374</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" t="s">
+        <v>36</v>
+      </c>
+      <c r="B50">
+        <v>0</v>
+      </c>
+      <c r="C50">
+        <v>25</v>
+      </c>
+      <c r="D50">
+        <v>1</v>
+      </c>
+      <c r="E50">
+        <v>1</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1228</v>
+      </c>
+      <c r="G50">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" t="s">
+        <v>36</v>
+      </c>
+      <c r="B51">
+        <v>0</v>
+      </c>
+      <c r="C51">
+        <v>25</v>
+      </c>
+      <c r="D51">
+        <v>1</v>
+      </c>
+      <c r="E51">
+        <v>1</v>
+      </c>
+      <c r="F51" t="s">
+        <v>1235</v>
+      </c>
+      <c r="G51">
         <v>0</v>
       </c>
     </row>
@@ -35165,7 +35367,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87945C49-375A-40BB-B037-1C50621D6D44}">
-  <dimension ref="A1:W73"/>
+  <dimension ref="A1:X76"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="17.08984375" customWidth="1"/>
@@ -35181,14 +35383,14 @@
     <col min="14" max="14" width="14.08984375" customWidth="1"/>
     <col min="15" max="16" width="21.453125" customWidth="1"/>
     <col min="17" max="17" width="16.1796875" customWidth="1"/>
-    <col min="18" max="19" width="13.81640625" customWidth="1"/>
-    <col min="20" max="20" width="10.453125" customWidth="1"/>
-    <col min="21" max="21" width="11" customWidth="1"/>
-    <col min="22" max="22" width="7.1796875" customWidth="1"/>
-    <col min="23" max="23" width="13.81640625" customWidth="1"/>
+    <col min="18" max="20" width="13.81640625" customWidth="1"/>
+    <col min="21" max="21" width="10.453125" customWidth="1"/>
+    <col min="22" max="22" width="11" customWidth="1"/>
+    <col min="23" max="23" width="7.1796875" customWidth="1"/>
+    <col min="24" max="24" width="13.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="13">
+    <row r="1" spans="1:24" ht="13">
       <c r="A1" s="45" t="s">
         <v>1102</v>
       </c>
@@ -35244,22 +35446,25 @@
         <v>1463</v>
       </c>
       <c r="S1" s="45" t="s">
+        <v>1744</v>
+      </c>
+      <c r="T1" s="45" t="s">
         <v>1565</v>
       </c>
-      <c r="T1" s="45" t="s">
+      <c r="U1" s="45" t="s">
         <v>1525</v>
       </c>
-      <c r="U1" s="45" t="s">
+      <c r="V1" s="45" t="s">
         <v>1527</v>
       </c>
-      <c r="V1" s="45" t="s">
+      <c r="W1" s="45" t="s">
         <v>1644</v>
       </c>
-      <c r="W1" s="45" t="s">
+      <c r="X1" s="45" t="s">
         <v>1411</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:24">
       <c r="A2" s="46" t="s">
         <v>1424</v>
       </c>
@@ -35314,23 +35519,26 @@
       <c r="R2" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S2" s="46">
+      <c r="S2" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T2" s="46">
         <v>-1</v>
       </c>
-      <c r="T2" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U2" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V2" s="46">
-        <v>0</v>
+      <c r="V2" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W2" s="46">
+        <v>0</v>
+      </c>
+      <c r="X2" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:24">
       <c r="A3" s="46" t="s">
         <v>1426</v>
       </c>
@@ -35385,23 +35593,26 @@
       <c r="R3" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S3" s="46">
+      <c r="S3" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T3" s="46">
         <v>-1</v>
       </c>
-      <c r="T3" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U3" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V3" s="46">
-        <v>0</v>
+      <c r="V3" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W3" s="46">
+        <v>0</v>
+      </c>
+      <c r="X3" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:24">
       <c r="A4" s="46" t="s">
         <v>1427</v>
       </c>
@@ -35456,23 +35667,26 @@
       <c r="R4" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S4" s="46">
+      <c r="S4" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T4" s="46">
         <v>-1</v>
       </c>
-      <c r="T4" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U4" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V4" s="46">
-        <v>0</v>
+      <c r="V4" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W4" s="46">
+        <v>0</v>
+      </c>
+      <c r="X4" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:24">
       <c r="A5" s="46" t="s">
         <v>1428</v>
       </c>
@@ -35527,23 +35741,26 @@
       <c r="R5" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S5" s="46">
+      <c r="S5" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T5" s="46">
         <v>-1</v>
       </c>
-      <c r="T5" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U5" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V5" s="46">
-        <v>0</v>
+      <c r="V5" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W5" s="46">
+        <v>0</v>
+      </c>
+      <c r="X5" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="6" spans="1:23">
+    <row r="6" spans="1:24">
       <c r="A6" s="46" t="s">
         <v>1430</v>
       </c>
@@ -35598,23 +35815,26 @@
       <c r="R6" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S6" s="46">
+      <c r="S6" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T6" s="46">
         <v>-1</v>
       </c>
-      <c r="T6" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U6" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V6" s="46">
-        <v>0</v>
+      <c r="V6" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W6" s="46">
+        <v>0</v>
+      </c>
+      <c r="X6" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:24">
       <c r="A7" s="46" t="s">
         <v>1431</v>
       </c>
@@ -35669,23 +35889,26 @@
       <c r="R7" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S7" s="46">
+      <c r="S7" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T7" s="46">
         <v>-1</v>
       </c>
-      <c r="T7" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U7" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V7" s="46">
-        <v>0</v>
+      <c r="V7" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W7" s="46">
+        <v>0</v>
+      </c>
+      <c r="X7" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:24">
       <c r="A8" s="46" t="s">
         <v>1435</v>
       </c>
@@ -35740,23 +35963,26 @@
       <c r="R8" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S8" s="46">
+      <c r="S8" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T8" s="46">
         <v>-1</v>
       </c>
-      <c r="T8" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U8" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V8" s="46">
-        <v>0</v>
+      <c r="V8" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W8" s="46">
+        <v>0</v>
+      </c>
+      <c r="X8" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:24">
       <c r="A9" s="46" t="s">
         <v>1436</v>
       </c>
@@ -35811,23 +36037,26 @@
       <c r="R9" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S9" s="46">
+      <c r="S9" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T9" s="46">
         <v>-1</v>
       </c>
-      <c r="T9" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U9" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V9" s="46">
-        <v>0</v>
+      <c r="V9" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W9" s="46">
+        <v>0</v>
+      </c>
+      <c r="X9" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:24">
       <c r="A10" s="46" t="s">
         <v>1440</v>
       </c>
@@ -35882,23 +36111,26 @@
       <c r="R10" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S10" s="46">
+      <c r="S10" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T10" s="46">
         <v>-1</v>
       </c>
-      <c r="T10" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U10" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V10" s="46">
-        <v>0</v>
+      <c r="V10" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W10" s="46">
+        <v>0</v>
+      </c>
+      <c r="X10" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:24">
       <c r="A11" s="46" t="s">
         <v>1442</v>
       </c>
@@ -35953,23 +36185,26 @@
       <c r="R11" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S11" s="46">
+      <c r="S11" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T11" s="46">
         <v>-1</v>
       </c>
-      <c r="T11" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U11" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V11" s="46">
-        <v>0</v>
+      <c r="V11" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W11" s="46">
+        <v>0</v>
+      </c>
+      <c r="X11" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:24">
       <c r="A12" s="46" t="s">
         <v>1443</v>
       </c>
@@ -36024,23 +36259,26 @@
       <c r="R12" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S12" s="46">
+      <c r="S12" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T12" s="46">
         <v>-1</v>
       </c>
-      <c r="T12" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U12" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V12" s="46">
-        <v>0</v>
+      <c r="V12" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W12" s="46">
+        <v>0</v>
+      </c>
+      <c r="X12" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:24">
       <c r="A13" s="46" t="s">
         <v>1445</v>
       </c>
@@ -36095,23 +36333,26 @@
       <c r="R13" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S13" s="46">
+      <c r="S13" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T13" s="46">
         <v>-1</v>
       </c>
-      <c r="T13" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U13" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V13" s="46">
-        <v>0</v>
+      <c r="V13" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W13" s="46">
+        <v>0</v>
+      </c>
+      <c r="X13" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:24">
       <c r="A14" s="46" t="s">
         <v>1446</v>
       </c>
@@ -36166,23 +36407,26 @@
       <c r="R14" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S14" s="46">
+      <c r="S14" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T14" s="46">
         <v>-1</v>
       </c>
-      <c r="T14" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U14" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V14" s="46">
-        <v>0</v>
+      <c r="V14" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W14" s="46">
+        <v>0</v>
+      </c>
+      <c r="X14" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:24">
       <c r="A15" s="46" t="s">
         <v>1447</v>
       </c>
@@ -36237,23 +36481,26 @@
       <c r="R15" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S15" s="46">
+      <c r="S15" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T15" s="46">
         <v>-1</v>
       </c>
-      <c r="T15" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U15" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V15" s="46">
-        <v>0</v>
+      <c r="V15" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W15" s="46">
+        <v>0</v>
+      </c>
+      <c r="X15" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:24">
       <c r="A16" s="46" t="s">
         <v>1448</v>
       </c>
@@ -36308,23 +36555,26 @@
       <c r="R16" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S16" s="46">
+      <c r="S16" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T16" s="46">
         <v>-1</v>
       </c>
-      <c r="T16" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U16" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V16" s="46">
-        <v>0</v>
+      <c r="V16" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W16" s="46">
+        <v>0</v>
+      </c>
+      <c r="X16" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="17" spans="1:23">
+    <row r="17" spans="1:24">
       <c r="A17" s="46" t="s">
         <v>1450</v>
       </c>
@@ -36379,23 +36629,26 @@
       <c r="R17" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S17" s="46">
+      <c r="S17" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T17" s="46">
         <v>-1</v>
       </c>
-      <c r="T17" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U17" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V17" s="46">
-        <v>0</v>
+      <c r="V17" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W17" s="46">
+        <v>0</v>
+      </c>
+      <c r="X17" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="18" spans="1:23">
+    <row r="18" spans="1:24">
       <c r="A18" s="46" t="s">
         <v>1451</v>
       </c>
@@ -36450,23 +36703,26 @@
       <c r="R18" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S18" s="46">
+      <c r="S18" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T18" s="46">
         <v>-1</v>
       </c>
-      <c r="T18" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U18" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V18" s="46">
-        <v>0</v>
+      <c r="V18" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W18" s="46">
+        <v>0</v>
+      </c>
+      <c r="X18" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="19" spans="1:23">
+    <row r="19" spans="1:24">
       <c r="A19" s="46" t="s">
         <v>1452</v>
       </c>
@@ -36521,23 +36777,26 @@
       <c r="R19" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S19" s="46">
+      <c r="S19" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T19" s="46">
         <v>-1</v>
       </c>
-      <c r="T19" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U19" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V19" s="46">
-        <v>0</v>
+      <c r="V19" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W19" s="46">
+        <v>0</v>
+      </c>
+      <c r="X19" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="20" spans="1:23">
+    <row r="20" spans="1:24">
       <c r="A20" s="46" t="s">
         <v>1458</v>
       </c>
@@ -36592,23 +36851,26 @@
       <c r="R20" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S20" s="46">
+      <c r="S20" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T20" s="46">
         <v>-1</v>
       </c>
-      <c r="T20" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U20" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V20" s="46">
-        <v>0</v>
+      <c r="V20" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W20" s="46">
+        <v>0</v>
+      </c>
+      <c r="X20" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="21" spans="1:23">
+    <row r="21" spans="1:24">
       <c r="A21" s="46" t="s">
         <v>1459</v>
       </c>
@@ -36663,23 +36925,26 @@
       <c r="R21" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S21" s="46">
+      <c r="S21" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T21" s="46">
         <v>-1</v>
       </c>
-      <c r="T21" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U21" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V21" s="46">
-        <v>0</v>
+      <c r="V21" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W21" s="46">
+        <v>0</v>
+      </c>
+      <c r="X21" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="22" spans="1:23">
+    <row r="22" spans="1:24">
       <c r="A22" s="46" t="s">
         <v>1460</v>
       </c>
@@ -36734,23 +36999,26 @@
       <c r="R22" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S22" s="46">
+      <c r="S22" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T22" s="46">
         <v>-1</v>
       </c>
-      <c r="T22" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U22" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V22" s="46">
-        <v>0</v>
+      <c r="V22" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W22" s="46">
+        <v>0</v>
+      </c>
+      <c r="X22" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="23" spans="1:23">
+    <row r="23" spans="1:24">
       <c r="A23" s="46" t="s">
         <v>1470</v>
       </c>
@@ -36805,23 +37073,26 @@
       <c r="R23" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S23" s="46">
+      <c r="S23" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T23" s="46">
         <v>-1</v>
       </c>
-      <c r="T23" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U23" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V23" s="46">
-        <v>0</v>
+      <c r="V23" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W23" s="46">
+        <v>0</v>
+      </c>
+      <c r="X23" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="24" spans="1:23">
+    <row r="24" spans="1:24">
       <c r="A24" s="46" t="s">
         <v>1471</v>
       </c>
@@ -36876,23 +37147,26 @@
       <c r="R24" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S24" s="46">
+      <c r="S24" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T24" s="46">
         <v>-1</v>
       </c>
-      <c r="T24" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U24" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V24" s="46">
-        <v>0</v>
+      <c r="V24" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W24" s="46">
+        <v>0</v>
+      </c>
+      <c r="X24" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="25" spans="1:23">
+    <row r="25" spans="1:24">
       <c r="A25" s="46" t="s">
         <v>1472</v>
       </c>
@@ -36947,23 +37221,26 @@
       <c r="R25" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S25" s="46">
+      <c r="S25" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T25" s="46">
         <v>-1</v>
       </c>
-      <c r="T25" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U25" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V25" s="46">
-        <v>0</v>
+      <c r="V25" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W25" s="46">
+        <v>0</v>
+      </c>
+      <c r="X25" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="26" spans="1:23">
+    <row r="26" spans="1:24">
       <c r="A26" s="46"/>
       <c r="B26" s="46"/>
       <c r="C26" s="46"/>
@@ -36987,8 +37264,9 @@
       <c r="U26" s="46"/>
       <c r="V26" s="46"/>
       <c r="W26" s="46"/>
-    </row>
-    <row r="27" spans="1:23">
+      <c r="X26" s="46"/>
+    </row>
+    <row r="27" spans="1:24">
       <c r="A27" s="46" t="s">
         <v>1555</v>
       </c>
@@ -37043,23 +37321,26 @@
       <c r="R27" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S27" s="46">
+      <c r="S27" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T27" s="46">
         <v>-1</v>
       </c>
-      <c r="T27" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U27" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V27" s="46">
-        <v>0</v>
+      <c r="V27" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W27" s="46">
+        <v>0</v>
+      </c>
+      <c r="X27" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="28" spans="1:23">
+    <row r="28" spans="1:24">
       <c r="A28" s="46" t="s">
         <v>1566</v>
       </c>
@@ -37114,23 +37395,26 @@
       <c r="R28" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S28" s="46">
+      <c r="S28" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T28" s="46">
         <v>-1</v>
       </c>
-      <c r="T28" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U28" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V28" s="46">
-        <v>0</v>
+      <c r="V28" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W28" s="46">
+        <v>0</v>
+      </c>
+      <c r="X28" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="31" spans="1:23">
+    <row r="31" spans="1:24">
       <c r="A31" s="46" t="s">
         <v>1542</v>
       </c>
@@ -37185,23 +37469,26 @@
       <c r="R31" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S31" s="46">
+      <c r="S31" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T31" s="46">
         <v>-1</v>
       </c>
-      <c r="T31" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U31" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V31" s="46">
-        <v>0</v>
+      <c r="V31" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W31" s="46">
+        <v>0</v>
+      </c>
+      <c r="X31" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="32" spans="1:23">
+    <row r="32" spans="1:24">
       <c r="A32" s="46" t="s">
         <v>1541</v>
       </c>
@@ -37256,23 +37543,26 @@
       <c r="R32" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S32" s="46">
+      <c r="S32" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T32" s="46">
         <v>-1</v>
       </c>
-      <c r="T32" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U32" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V32" s="46">
-        <v>0</v>
+      <c r="V32" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W32" s="46">
+        <v>0</v>
+      </c>
+      <c r="X32" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="35" spans="1:23">
+    <row r="35" spans="1:24">
       <c r="A35" s="46" t="s">
         <v>1543</v>
       </c>
@@ -37327,23 +37617,26 @@
       <c r="R35" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S35" s="46">
+      <c r="S35" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T35" s="46">
         <v>-1</v>
       </c>
-      <c r="T35" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U35" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V35" s="46">
-        <v>0</v>
+      <c r="V35" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W35" s="46">
+        <v>0</v>
+      </c>
+      <c r="X35" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="36" spans="1:23">
+    <row r="36" spans="1:24">
       <c r="A36" s="46" t="s">
         <v>1544</v>
       </c>
@@ -37398,23 +37691,26 @@
       <c r="R36" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S36" s="46">
+      <c r="S36" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T36" s="46">
         <v>-1</v>
       </c>
-      <c r="T36" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U36" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V36" s="46">
-        <v>0</v>
+      <c r="V36" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W36" s="46">
+        <v>0</v>
+      </c>
+      <c r="X36" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="39" spans="1:23">
+    <row r="39" spans="1:24">
       <c r="A39" s="46" t="s">
         <v>1545</v>
       </c>
@@ -37469,23 +37765,26 @@
       <c r="R39" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S39" s="46">
+      <c r="S39" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T39" s="46">
         <v>-1</v>
       </c>
-      <c r="T39" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U39" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V39" s="46">
-        <v>0</v>
+      <c r="V39" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W39" s="46">
+        <v>0</v>
+      </c>
+      <c r="X39" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="40" spans="1:23">
+    <row r="40" spans="1:24">
       <c r="A40" s="46" t="s">
         <v>1546</v>
       </c>
@@ -37540,23 +37839,26 @@
       <c r="R40" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S40" s="46">
+      <c r="S40" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T40" s="46">
         <v>-1</v>
       </c>
-      <c r="T40" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U40" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V40" s="46">
-        <v>0</v>
+      <c r="V40" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W40" s="46">
+        <v>0</v>
+      </c>
+      <c r="X40" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="45" spans="1:23">
+    <row r="45" spans="1:24">
       <c r="A45" s="46" t="s">
         <v>1571</v>
       </c>
@@ -37611,23 +37913,26 @@
       <c r="R45" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S45" s="46">
+      <c r="S45" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T45" s="46">
         <v>-1</v>
       </c>
-      <c r="T45" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U45" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V45" s="46">
-        <v>0</v>
+      <c r="V45" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W45" s="46">
+        <v>0</v>
+      </c>
+      <c r="X45" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="46" spans="1:23">
+    <row r="46" spans="1:24">
       <c r="A46" s="46" t="s">
         <v>1572</v>
       </c>
@@ -37682,23 +37987,26 @@
       <c r="R46" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S46" s="46">
+      <c r="S46" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T46" s="46">
         <v>-1</v>
       </c>
-      <c r="T46" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U46" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V46" s="46">
-        <v>0</v>
+      <c r="V46" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W46" s="46">
+        <v>0</v>
+      </c>
+      <c r="X46" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="47" spans="1:23">
+    <row r="47" spans="1:24">
       <c r="A47" s="46" t="s">
         <v>1573</v>
       </c>
@@ -37753,23 +38061,26 @@
       <c r="R47" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S47" s="46">
+      <c r="S47" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T47" s="46">
         <v>-1</v>
       </c>
-      <c r="T47" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U47" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V47" s="46">
-        <v>0</v>
+      <c r="V47" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W47" s="46">
+        <v>0</v>
+      </c>
+      <c r="X47" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="48" spans="1:23">
+    <row r="48" spans="1:24">
       <c r="A48" s="46" t="s">
         <v>1589</v>
       </c>
@@ -37824,23 +38135,26 @@
       <c r="R48" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S48" s="46">
+      <c r="S48" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T48" s="46">
         <v>-1</v>
       </c>
-      <c r="T48" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U48" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V48" s="46">
-        <v>0</v>
+      <c r="V48" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W48" s="46">
+        <v>0</v>
+      </c>
+      <c r="X48" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="49" spans="1:23">
+    <row r="49" spans="1:24">
       <c r="A49" s="46" t="s">
         <v>1574</v>
       </c>
@@ -37895,23 +38209,26 @@
       <c r="R49" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S49" s="46">
+      <c r="S49" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T49" s="46">
         <v>-1</v>
       </c>
-      <c r="T49" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U49" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V49" s="46">
-        <v>0</v>
+      <c r="V49" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W49" s="46">
+        <v>0</v>
+      </c>
+      <c r="X49" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="50" spans="1:23">
+    <row r="50" spans="1:24">
       <c r="A50" s="46" t="s">
         <v>1575</v>
       </c>
@@ -37966,23 +38283,26 @@
       <c r="R50" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S50" s="46">
+      <c r="S50" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T50" s="46">
         <v>-1</v>
       </c>
-      <c r="T50" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U50" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V50" s="46">
-        <v>0</v>
+      <c r="V50" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W50" s="46">
+        <v>0</v>
+      </c>
+      <c r="X50" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="51" spans="1:23">
+    <row r="51" spans="1:24">
       <c r="A51" s="46" t="s">
         <v>1576</v>
       </c>
@@ -38037,23 +38357,26 @@
       <c r="R51" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S51" s="46">
+      <c r="S51" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T51" s="46">
         <v>-1</v>
       </c>
-      <c r="T51" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U51" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V51" s="46">
-        <v>0</v>
+      <c r="V51" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W51" s="46">
+        <v>0</v>
+      </c>
+      <c r="X51" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="52" spans="1:23">
+    <row r="52" spans="1:24">
       <c r="A52" s="46" t="s">
         <v>1590</v>
       </c>
@@ -38108,23 +38431,26 @@
       <c r="R52" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S52" s="46">
+      <c r="S52" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T52" s="46">
         <v>-1</v>
       </c>
-      <c r="T52" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U52" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V52" s="46">
-        <v>0</v>
+      <c r="V52" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W52" s="46">
+        <v>0</v>
+      </c>
+      <c r="X52" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="53" spans="1:23">
+    <row r="53" spans="1:24">
       <c r="A53" s="46" t="s">
         <v>1577</v>
       </c>
@@ -38179,23 +38505,26 @@
       <c r="R53" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S53" s="46">
+      <c r="S53" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T53" s="46">
         <v>-1</v>
       </c>
-      <c r="T53" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U53" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V53" s="46">
-        <v>0</v>
+      <c r="V53" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W53" s="46">
+        <v>0</v>
+      </c>
+      <c r="X53" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="54" spans="1:23">
+    <row r="54" spans="1:24">
       <c r="A54" s="46" t="s">
         <v>1578</v>
       </c>
@@ -38250,23 +38579,26 @@
       <c r="R54" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S54" s="46">
+      <c r="S54" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T54" s="46">
         <v>-1</v>
       </c>
-      <c r="T54" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U54" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V54" s="46">
-        <v>0</v>
+      <c r="V54" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W54" s="46">
+        <v>0</v>
+      </c>
+      <c r="X54" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="55" spans="1:23">
+    <row r="55" spans="1:24">
       <c r="A55" s="46" t="s">
         <v>1579</v>
       </c>
@@ -38321,23 +38653,26 @@
       <c r="R55" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S55" s="46">
+      <c r="S55" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T55" s="46">
         <v>-1</v>
       </c>
-      <c r="T55" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U55" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V55" s="46">
-        <v>0</v>
+      <c r="V55" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W55" s="46">
+        <v>0</v>
+      </c>
+      <c r="X55" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="56" spans="1:23">
+    <row r="56" spans="1:24">
       <c r="A56" s="46" t="s">
         <v>1591</v>
       </c>
@@ -38392,23 +38727,26 @@
       <c r="R56" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S56" s="46">
+      <c r="S56" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T56" s="46">
         <v>-1</v>
       </c>
-      <c r="T56" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U56" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V56" s="46">
-        <v>0</v>
+      <c r="V56" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W56" s="46">
+        <v>0</v>
+      </c>
+      <c r="X56" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="57" spans="1:23">
+    <row r="57" spans="1:24">
       <c r="A57" s="46" t="s">
         <v>1580</v>
       </c>
@@ -38463,23 +38801,26 @@
       <c r="R57" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S57" s="46">
+      <c r="S57" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T57" s="46">
         <v>-1</v>
       </c>
-      <c r="T57" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U57" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V57" s="46">
-        <v>0</v>
+      <c r="V57" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W57" s="46">
+        <v>0</v>
+      </c>
+      <c r="X57" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="58" spans="1:23">
+    <row r="58" spans="1:24">
       <c r="A58" s="46" t="s">
         <v>1581</v>
       </c>
@@ -38534,23 +38875,26 @@
       <c r="R58" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S58" s="46">
+      <c r="S58" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T58" s="46">
         <v>-1</v>
       </c>
-      <c r="T58" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U58" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V58" s="46">
-        <v>0</v>
+      <c r="V58" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W58" s="46">
+        <v>0</v>
+      </c>
+      <c r="X58" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="59" spans="1:23">
+    <row r="59" spans="1:24">
       <c r="A59" s="46" t="s">
         <v>1582</v>
       </c>
@@ -38605,23 +38949,26 @@
       <c r="R59" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S59" s="46">
+      <c r="S59" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T59" s="46">
         <v>-1</v>
       </c>
-      <c r="T59" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U59" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V59" s="46">
-        <v>0</v>
+      <c r="V59" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W59" s="46">
+        <v>0</v>
+      </c>
+      <c r="X59" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="60" spans="1:23">
+    <row r="60" spans="1:24">
       <c r="A60" s="46" t="s">
         <v>1592</v>
       </c>
@@ -38676,23 +39023,26 @@
       <c r="R60" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S60" s="46">
+      <c r="S60" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T60" s="46">
         <v>-1</v>
       </c>
-      <c r="T60" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U60" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V60" s="46">
-        <v>0</v>
+      <c r="V60" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W60" s="46">
+        <v>0</v>
+      </c>
+      <c r="X60" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="61" spans="1:23">
+    <row r="61" spans="1:24">
       <c r="A61" s="46" t="s">
         <v>1583</v>
       </c>
@@ -38747,23 +39097,26 @@
       <c r="R61" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S61" s="46">
+      <c r="S61" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T61" s="46">
         <v>-1</v>
       </c>
-      <c r="T61" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U61" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V61" s="46">
-        <v>0</v>
+      <c r="V61" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W61" s="46">
+        <v>0</v>
+      </c>
+      <c r="X61" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="62" spans="1:23">
+    <row r="62" spans="1:24">
       <c r="A62" s="46" t="s">
         <v>1584</v>
       </c>
@@ -38818,23 +39171,26 @@
       <c r="R62" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S62" s="46">
+      <c r="S62" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T62" s="46">
         <v>-1</v>
       </c>
-      <c r="T62" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U62" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V62" s="46">
-        <v>0</v>
+      <c r="V62" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W62" s="46">
+        <v>0</v>
+      </c>
+      <c r="X62" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="63" spans="1:23">
+    <row r="63" spans="1:24">
       <c r="A63" s="46" t="s">
         <v>1585</v>
       </c>
@@ -38889,23 +39245,26 @@
       <c r="R63" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S63" s="46">
+      <c r="S63" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T63" s="46">
         <v>-1</v>
       </c>
-      <c r="T63" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U63" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V63" s="46">
-        <v>0</v>
+      <c r="V63" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W63" s="46">
+        <v>0</v>
+      </c>
+      <c r="X63" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="64" spans="1:23">
+    <row r="64" spans="1:24">
       <c r="A64" s="46" t="s">
         <v>1593</v>
       </c>
@@ -38960,23 +39319,26 @@
       <c r="R64" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S64" s="46">
+      <c r="S64" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T64" s="46">
         <v>-1</v>
       </c>
-      <c r="T64" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U64" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V64" s="46">
-        <v>0</v>
+      <c r="V64" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W64" s="46">
+        <v>0</v>
+      </c>
+      <c r="X64" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="66" spans="1:23">
+    <row r="66" spans="1:24">
       <c r="A66" s="46" t="s">
         <v>1659</v>
       </c>
@@ -39031,23 +39393,26 @@
       <c r="R66" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S66" s="46">
+      <c r="S66" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T66" s="46">
         <v>-1</v>
       </c>
-      <c r="T66" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U66" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V66" s="46">
-        <v>0</v>
+      <c r="V66" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W66" s="46">
+        <v>0</v>
+      </c>
+      <c r="X66" s="46">
         <v>-1</v>
       </c>
     </row>
-    <row r="68" spans="1:23">
+    <row r="68" spans="1:24">
       <c r="A68" s="46" t="s">
         <v>1710</v>
       </c>
@@ -39102,23 +39467,26 @@
       <c r="R68" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S68" s="46">
+      <c r="S68" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T68" s="46">
         <v>-1</v>
       </c>
-      <c r="T68" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U68" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="V68" s="46" t="s">
         <v>1720</v>
       </c>
-      <c r="V68" s="46">
-        <v>1</v>
-      </c>
       <c r="W68" s="46">
+        <v>1</v>
+      </c>
+      <c r="X68" s="46">
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:23">
+    <row r="70" spans="1:24">
       <c r="A70" s="46" t="s">
         <v>1712</v>
       </c>
@@ -39173,23 +39541,26 @@
       <c r="R70" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S70" s="46">
+      <c r="S70" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T70" s="46">
         <v>-1</v>
       </c>
-      <c r="T70" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U70" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V70" s="46">
-        <v>1</v>
+      <c r="V70" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W70" s="46">
+        <v>1</v>
+      </c>
+      <c r="X70" s="46">
         <v>10</v>
       </c>
     </row>
-    <row r="71" spans="1:23">
+    <row r="71" spans="1:24">
       <c r="A71" s="46" t="s">
         <v>1713</v>
       </c>
@@ -39244,23 +39615,26 @@
       <c r="R71" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S71" s="46">
+      <c r="S71" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T71" s="46">
         <v>-1</v>
       </c>
-      <c r="T71" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U71" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V71" s="46">
-        <v>1</v>
+      <c r="V71" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W71" s="46">
+        <v>1</v>
+      </c>
+      <c r="X71" s="46">
         <v>10</v>
       </c>
     </row>
-    <row r="72" spans="1:23">
+    <row r="72" spans="1:24">
       <c r="A72" s="46" t="s">
         <v>1714</v>
       </c>
@@ -39315,23 +39689,26 @@
       <c r="R72" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S72" s="46">
+      <c r="S72" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T72" s="46">
         <v>-1</v>
       </c>
-      <c r="T72" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U72" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V72" s="46">
-        <v>1</v>
+      <c r="V72" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W72" s="46">
+        <v>1</v>
+      </c>
+      <c r="X72" s="46">
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:23">
+    <row r="73" spans="1:24">
       <c r="A73" s="46" t="s">
         <v>1715</v>
       </c>
@@ -39386,20 +39763,171 @@
       <c r="R73" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="S73" s="46">
+      <c r="S73" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="T73" s="46">
         <v>-1</v>
       </c>
-      <c r="T73" s="46" t="s">
-        <v>36</v>
-      </c>
       <c r="U73" s="46" t="s">
         <v>36</v>
       </c>
-      <c r="V73" s="46">
-        <v>1</v>
+      <c r="V73" s="46" t="s">
+        <v>36</v>
       </c>
       <c r="W73" s="46">
+        <v>1</v>
+      </c>
+      <c r="X73" s="46">
         <v>10</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24">
+      <c r="A75" s="46" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B75" s="46" t="s">
+        <v>1567</v>
+      </c>
+      <c r="C75" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="D75" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="E75" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F75" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G75" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="H75" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="I75" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="J75" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="K75" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="L75" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="M75" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="N75" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="O75" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="P75" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q75" s="46" t="s">
+        <v>1740</v>
+      </c>
+      <c r="R75" s="46" t="s">
+        <v>1742</v>
+      </c>
+      <c r="S75" s="46">
+        <v>1</v>
+      </c>
+      <c r="T75" s="46">
+        <v>-1</v>
+      </c>
+      <c r="U75" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="V75" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="W75" s="46">
+        <v>1</v>
+      </c>
+      <c r="X75" s="46">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24">
+      <c r="A76" s="46" t="s">
+        <v>1741</v>
+      </c>
+      <c r="B76" s="46" t="s">
+        <v>1201</v>
+      </c>
+      <c r="C76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="D76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="E76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="H76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="I76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="J76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="K76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="L76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="M76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="N76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="O76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="P76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q76" s="46" t="s">
+        <v>1740</v>
+      </c>
+      <c r="R76" s="46" t="s">
+        <v>1742</v>
+      </c>
+      <c r="S76" s="46">
+        <v>10</v>
+      </c>
+      <c r="T76" s="46">
+        <v>-1</v>
+      </c>
+      <c r="U76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="V76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="W76" s="46">
+        <v>1</v>
+      </c>
+      <c r="X76" s="46">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -41453,7 +41981,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4267B9-6C50-42DE-8EEA-ACDE778B1226}">
-  <dimension ref="A1:U24"/>
+  <dimension ref="A1:U25"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="15.26953125" customWidth="1"/>
@@ -43021,6 +43549,71 @@
       </c>
       <c r="U24" t="s">
         <v>1666</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21">
+      <c r="A25" s="44" t="s">
+        <v>1739</v>
+      </c>
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25">
+        <v>0</v>
+      </c>
+      <c r="E25">
+        <v>0</v>
+      </c>
+      <c r="F25">
+        <v>0</v>
+      </c>
+      <c r="G25">
+        <v>0</v>
+      </c>
+      <c r="H25">
+        <v>0</v>
+      </c>
+      <c r="I25">
+        <v>0</v>
+      </c>
+      <c r="J25">
+        <v>0</v>
+      </c>
+      <c r="K25">
+        <v>0</v>
+      </c>
+      <c r="L25">
+        <v>0</v>
+      </c>
+      <c r="M25">
+        <v>0</v>
+      </c>
+      <c r="N25">
+        <v>10</v>
+      </c>
+      <c r="O25" s="44" t="s">
+        <v>1376</v>
+      </c>
+      <c r="P25">
+        <v>0</v>
+      </c>
+      <c r="Q25">
+        <v>1</v>
+      </c>
+      <c r="R25" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="S25" t="s">
+        <v>36</v>
+      </c>
+      <c r="T25">
+        <v>11</v>
+      </c>
+      <c r="U25" t="s">
+        <v>1567</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{580A8A56-B507-4566-9E08-7665C983E5AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9F4B21-F3C1-4CE5-821E-D58AD52623F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="14" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="4" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -31696,7 +31696,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>1477</v>
+        <v>1380</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -31719,7 +31719,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>1493</v>
+        <v>1379</v>
       </c>
       <c r="G46">
         <v>0</v>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9F4B21-F3C1-4CE5-821E-D58AD52623F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60B5506D-076B-456C-9963-0004605A91C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="4" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="14" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7461" uniqueCount="1745">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7533" uniqueCount="1750">
   <si>
     <t>NAME</t>
   </si>
@@ -5419,6 +5419,21 @@
   </si>
   <si>
     <t>EVENT_NUM</t>
+  </si>
+  <si>
+    <t>mon_draw1</t>
+  </si>
+  <si>
+    <t>foxy</t>
+  </si>
+  <si>
+    <t>panda</t>
+  </si>
+  <si>
+    <t>bandit</t>
+  </si>
+  <si>
+    <t>goblin</t>
   </si>
 </sst>
 </file>
@@ -9190,136 +9205,576 @@
       </c>
     </row>
     <row r="23" spans="1:47" ht="12.5">
-      <c r="A23" s="48"/>
-      <c r="B23" s="48"/>
-      <c r="C23" s="48"/>
-      <c r="D23" s="48"/>
-      <c r="E23" s="48"/>
-      <c r="F23" s="48"/>
-      <c r="G23" s="48"/>
-      <c r="H23" s="48"/>
-      <c r="I23" s="48"/>
-      <c r="J23" s="48"/>
-      <c r="K23" s="48"/>
-      <c r="L23" s="48"/>
-      <c r="M23" s="48"/>
-      <c r="N23" s="48"/>
-      <c r="O23" s="48"/>
-      <c r="P23" s="48"/>
-      <c r="Q23" s="48"/>
-      <c r="R23" s="48"/>
-      <c r="S23" s="48"/>
-      <c r="T23" s="48"/>
-      <c r="U23" s="48"/>
-      <c r="V23" s="48"/>
-      <c r="W23" s="48"/>
-      <c r="X23" s="48"/>
-      <c r="Y23" s="40"/>
-      <c r="Z23" s="7"/>
-      <c r="AA23" s="7"/>
-      <c r="AE23" s="28"/>
-      <c r="AG23" s="28"/>
-      <c r="AH23" s="28"/>
-      <c r="AI23" s="46"/>
+      <c r="A23" s="47" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B23" s="48">
+        <v>1</v>
+      </c>
+      <c r="C23" s="48">
+        <v>2</v>
+      </c>
+      <c r="D23" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="F23" s="48">
+        <v>0</v>
+      </c>
+      <c r="G23" s="48">
+        <v>100</v>
+      </c>
+      <c r="H23" s="48">
+        <v>45</v>
+      </c>
+      <c r="I23" s="48">
+        <v>45</v>
+      </c>
+      <c r="J23" s="48">
+        <v>0</v>
+      </c>
+      <c r="K23" s="48">
+        <v>1</v>
+      </c>
+      <c r="L23" s="48">
+        <v>0</v>
+      </c>
+      <c r="M23" s="48">
+        <v>0</v>
+      </c>
+      <c r="N23" s="48">
+        <v>0</v>
+      </c>
+      <c r="O23" s="48">
+        <v>0</v>
+      </c>
+      <c r="P23" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q23" s="48">
+        <v>30</v>
+      </c>
+      <c r="R23" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="S23" s="40" t="s">
+        <v>1510</v>
+      </c>
+      <c r="T23" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="U23" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="V23" s="40">
+        <v>40</v>
+      </c>
+      <c r="W23" s="7">
+        <v>80</v>
+      </c>
+      <c r="X23" s="42">
+        <v>1</v>
+      </c>
+      <c r="Y23" s="40">
+        <v>45</v>
+      </c>
+      <c r="Z23" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA23" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB23" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC23" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD23" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE23">
+        <v>1</v>
+      </c>
+      <c r="AF23">
+        <v>1</v>
+      </c>
+      <c r="AG23">
+        <v>6</v>
+      </c>
+      <c r="AH23">
+        <v>3</v>
+      </c>
+      <c r="AI23" s="46" t="s">
+        <v>1519</v>
+      </c>
+      <c r="AJ23">
+        <v>0</v>
+      </c>
+      <c r="AK23">
+        <v>0</v>
+      </c>
+      <c r="AL23">
+        <v>0</v>
+      </c>
+      <c r="AM23">
+        <v>0</v>
+      </c>
+      <c r="AN23">
+        <v>-1</v>
+      </c>
+      <c r="AO23">
+        <v>0</v>
+      </c>
+      <c r="AP23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS23" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT23">
+        <v>0</v>
+      </c>
+      <c r="AU23">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:47" ht="12.5">
-      <c r="A24" s="48"/>
-      <c r="B24" s="48"/>
-      <c r="C24" s="48"/>
-      <c r="D24" s="48"/>
-      <c r="E24" s="48"/>
-      <c r="F24" s="48"/>
-      <c r="G24" s="48"/>
-      <c r="H24" s="48"/>
-      <c r="I24" s="48"/>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48"/>
-      <c r="L24" s="48"/>
-      <c r="M24" s="48"/>
-      <c r="N24" s="48"/>
-      <c r="O24" s="48"/>
-      <c r="P24" s="48"/>
-      <c r="Q24" s="48"/>
-      <c r="R24" s="48"/>
-      <c r="S24" s="48"/>
-      <c r="T24" s="48"/>
-      <c r="U24" s="48"/>
-      <c r="V24" s="48"/>
-      <c r="W24" s="48"/>
-      <c r="X24" s="48"/>
-      <c r="Y24" s="40"/>
-      <c r="Z24" s="7"/>
-      <c r="AA24" s="7"/>
-      <c r="AE24" s="28"/>
-      <c r="AG24" s="28"/>
-      <c r="AH24" s="28"/>
-      <c r="AI24" s="46"/>
+      <c r="A24" s="47" t="s">
+        <v>1747</v>
+      </c>
+      <c r="B24" s="48">
+        <v>1</v>
+      </c>
+      <c r="C24" s="48">
+        <v>2</v>
+      </c>
+      <c r="D24" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="48">
+        <v>0</v>
+      </c>
+      <c r="G24" s="48">
+        <v>100</v>
+      </c>
+      <c r="H24" s="48">
+        <v>45</v>
+      </c>
+      <c r="I24" s="48">
+        <v>45</v>
+      </c>
+      <c r="J24" s="48">
+        <v>0</v>
+      </c>
+      <c r="K24" s="48">
+        <v>1</v>
+      </c>
+      <c r="L24" s="48">
+        <v>0</v>
+      </c>
+      <c r="M24" s="48">
+        <v>0</v>
+      </c>
+      <c r="N24" s="48">
+        <v>0</v>
+      </c>
+      <c r="O24" s="48">
+        <v>0</v>
+      </c>
+      <c r="P24" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q24" s="48">
+        <v>30</v>
+      </c>
+      <c r="R24" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="S24" s="40" t="s">
+        <v>1510</v>
+      </c>
+      <c r="T24" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="U24" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="V24" s="40">
+        <v>40</v>
+      </c>
+      <c r="W24" s="7">
+        <v>80</v>
+      </c>
+      <c r="X24" s="42">
+        <v>1</v>
+      </c>
+      <c r="Y24" s="40">
+        <v>45</v>
+      </c>
+      <c r="Z24" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA24" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB24" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC24" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD24" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE24">
+        <v>1</v>
+      </c>
+      <c r="AF24">
+        <v>1</v>
+      </c>
+      <c r="AG24">
+        <v>6</v>
+      </c>
+      <c r="AH24">
+        <v>3</v>
+      </c>
+      <c r="AI24" s="46" t="s">
+        <v>1519</v>
+      </c>
+      <c r="AJ24">
+        <v>0</v>
+      </c>
+      <c r="AK24">
+        <v>0</v>
+      </c>
+      <c r="AL24">
+        <v>0</v>
+      </c>
+      <c r="AM24">
+        <v>0</v>
+      </c>
+      <c r="AN24">
+        <v>-1</v>
+      </c>
+      <c r="AO24">
+        <v>0</v>
+      </c>
+      <c r="AP24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS24" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT24">
+        <v>0</v>
+      </c>
+      <c r="AU24">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:47" ht="12.5">
-      <c r="A25" s="48"/>
-      <c r="B25" s="48"/>
-      <c r="C25" s="48"/>
-      <c r="D25" s="48"/>
-      <c r="E25" s="48"/>
-      <c r="F25" s="48"/>
-      <c r="G25" s="48"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="48"/>
-      <c r="J25" s="48"/>
-      <c r="K25" s="48"/>
-      <c r="L25" s="48"/>
-      <c r="M25" s="48"/>
-      <c r="N25" s="48"/>
-      <c r="O25" s="48"/>
-      <c r="P25" s="48"/>
-      <c r="Q25" s="48"/>
-      <c r="R25" s="48"/>
-      <c r="S25" s="48"/>
-      <c r="T25" s="48"/>
-      <c r="U25" s="48"/>
-      <c r="V25" s="48"/>
-      <c r="W25" s="48"/>
-      <c r="X25" s="48"/>
-      <c r="Y25" s="40"/>
-      <c r="Z25" s="7"/>
-      <c r="AA25" s="7"/>
-      <c r="AE25" s="28"/>
-      <c r="AG25" s="28"/>
-      <c r="AH25" s="28"/>
-      <c r="AI25" s="46"/>
+      <c r="A25" s="47" t="s">
+        <v>1749</v>
+      </c>
+      <c r="B25" s="48">
+        <v>1</v>
+      </c>
+      <c r="C25" s="48">
+        <v>2</v>
+      </c>
+      <c r="D25" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E25" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="F25" s="48">
+        <v>0</v>
+      </c>
+      <c r="G25" s="48">
+        <v>100</v>
+      </c>
+      <c r="H25" s="48">
+        <v>45</v>
+      </c>
+      <c r="I25" s="48">
+        <v>45</v>
+      </c>
+      <c r="J25" s="48">
+        <v>0</v>
+      </c>
+      <c r="K25" s="48">
+        <v>1</v>
+      </c>
+      <c r="L25" s="48">
+        <v>0</v>
+      </c>
+      <c r="M25" s="48">
+        <v>0</v>
+      </c>
+      <c r="N25" s="48">
+        <v>0</v>
+      </c>
+      <c r="O25" s="48">
+        <v>0</v>
+      </c>
+      <c r="P25" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q25" s="48">
+        <v>30</v>
+      </c>
+      <c r="R25" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="S25" s="40" t="s">
+        <v>1510</v>
+      </c>
+      <c r="T25" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="U25" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="V25" s="40">
+        <v>40</v>
+      </c>
+      <c r="W25" s="7">
+        <v>80</v>
+      </c>
+      <c r="X25" s="42">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="40">
+        <v>45</v>
+      </c>
+      <c r="Z25" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA25" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB25" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC25" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD25" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE25">
+        <v>1</v>
+      </c>
+      <c r="AF25">
+        <v>1</v>
+      </c>
+      <c r="AG25">
+        <v>6</v>
+      </c>
+      <c r="AH25">
+        <v>3</v>
+      </c>
+      <c r="AI25" s="46" t="s">
+        <v>1519</v>
+      </c>
+      <c r="AJ25">
+        <v>0</v>
+      </c>
+      <c r="AK25">
+        <v>0</v>
+      </c>
+      <c r="AL25">
+        <v>0</v>
+      </c>
+      <c r="AM25">
+        <v>0</v>
+      </c>
+      <c r="AN25">
+        <v>-1</v>
+      </c>
+      <c r="AO25">
+        <v>0</v>
+      </c>
+      <c r="AP25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS25" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT25">
+        <v>0</v>
+      </c>
+      <c r="AU25">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:47" ht="12.5">
-      <c r="A26" s="48"/>
-      <c r="B26" s="48"/>
-      <c r="C26" s="48"/>
-      <c r="D26" s="48"/>
-      <c r="E26" s="48"/>
-      <c r="F26" s="48"/>
-      <c r="G26" s="48"/>
-      <c r="H26" s="48"/>
-      <c r="I26" s="48"/>
-      <c r="J26" s="48"/>
-      <c r="K26" s="48"/>
-      <c r="L26" s="48"/>
-      <c r="M26" s="48"/>
-      <c r="N26" s="48"/>
-      <c r="O26" s="48"/>
-      <c r="P26" s="48"/>
-      <c r="Q26" s="48"/>
-      <c r="R26" s="48"/>
-      <c r="S26" s="48"/>
-      <c r="T26" s="48"/>
-      <c r="U26" s="48"/>
-      <c r="V26" s="48"/>
-      <c r="W26" s="48"/>
-      <c r="X26" s="48"/>
-      <c r="Y26" s="40"/>
-      <c r="Z26" s="7"/>
-      <c r="AA26" s="7"/>
-      <c r="AE26" s="28"/>
-      <c r="AG26" s="28"/>
-      <c r="AH26" s="28"/>
-      <c r="AI26" s="46"/>
+      <c r="A26" s="47" t="s">
+        <v>1748</v>
+      </c>
+      <c r="B26" s="48">
+        <v>1</v>
+      </c>
+      <c r="C26" s="48">
+        <v>2</v>
+      </c>
+      <c r="D26" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E26" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="F26" s="48">
+        <v>0</v>
+      </c>
+      <c r="G26" s="48">
+        <v>100</v>
+      </c>
+      <c r="H26" s="48">
+        <v>45</v>
+      </c>
+      <c r="I26" s="48">
+        <v>45</v>
+      </c>
+      <c r="J26" s="48">
+        <v>0</v>
+      </c>
+      <c r="K26" s="48">
+        <v>1</v>
+      </c>
+      <c r="L26" s="48">
+        <v>0</v>
+      </c>
+      <c r="M26" s="48">
+        <v>0</v>
+      </c>
+      <c r="N26" s="48">
+        <v>0</v>
+      </c>
+      <c r="O26" s="48">
+        <v>0</v>
+      </c>
+      <c r="P26" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="Q26" s="48">
+        <v>30</v>
+      </c>
+      <c r="R26" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="S26" s="40" t="s">
+        <v>1510</v>
+      </c>
+      <c r="T26" s="40" t="s">
+        <v>35</v>
+      </c>
+      <c r="U26" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="V26" s="40">
+        <v>40</v>
+      </c>
+      <c r="W26" s="7">
+        <v>80</v>
+      </c>
+      <c r="X26" s="42">
+        <v>1</v>
+      </c>
+      <c r="Y26" s="40">
+        <v>45</v>
+      </c>
+      <c r="Z26" s="7">
+        <v>0</v>
+      </c>
+      <c r="AA26" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="s">
+        <v>37</v>
+      </c>
+      <c r="AC26" t="s">
+        <v>38</v>
+      </c>
+      <c r="AD26" t="s">
+        <v>39</v>
+      </c>
+      <c r="AE26">
+        <v>1</v>
+      </c>
+      <c r="AF26">
+        <v>1</v>
+      </c>
+      <c r="AG26">
+        <v>6</v>
+      </c>
+      <c r="AH26">
+        <v>3</v>
+      </c>
+      <c r="AI26" s="46" t="s">
+        <v>1519</v>
+      </c>
+      <c r="AJ26">
+        <v>0</v>
+      </c>
+      <c r="AK26">
+        <v>0</v>
+      </c>
+      <c r="AL26">
+        <v>0</v>
+      </c>
+      <c r="AM26">
+        <v>0</v>
+      </c>
+      <c r="AN26">
+        <v>-1</v>
+      </c>
+      <c r="AO26">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AQ26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS26" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT26">
+        <v>0</v>
+      </c>
+      <c r="AU26">
+        <v>0</v>
+      </c>
     </row>
     <row r="27" spans="1:47" ht="12.5">
       <c r="A27" s="48"/>
@@ -31004,9 +31459,10 @@
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1200-000000000000}">
-  <dimension ref="A1:G51"/>
+  <dimension ref="A1:G56"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
+    <col min="1" max="1" width="11" customWidth="1"/>
     <col min="3" max="3" width="10.36328125" customWidth="1"/>
     <col min="4" max="4" width="10.1796875" customWidth="1"/>
     <col min="5" max="6" width="10.81640625" customWidth="1"/>
@@ -31814,6 +32270,98 @@
         <v>1235</v>
       </c>
       <c r="G51">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7">
+      <c r="A53" t="s">
+        <v>1745</v>
+      </c>
+      <c r="B53">
+        <v>0</v>
+      </c>
+      <c r="C53">
+        <v>25</v>
+      </c>
+      <c r="D53">
+        <v>1</v>
+      </c>
+      <c r="E53">
+        <v>1</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1749</v>
+      </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" t="s">
+        <v>36</v>
+      </c>
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <v>25</v>
+      </c>
+      <c r="D54">
+        <v>1</v>
+      </c>
+      <c r="E54">
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>1746</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" t="s">
+        <v>36</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>25</v>
+      </c>
+      <c r="D55">
+        <v>1</v>
+      </c>
+      <c r="E55">
+        <v>1</v>
+      </c>
+      <c r="F55" t="s">
+        <v>1747</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7">
+      <c r="A56" t="s">
+        <v>36</v>
+      </c>
+      <c r="B56">
+        <v>0</v>
+      </c>
+      <c r="C56">
+        <v>25</v>
+      </c>
+      <c r="D56">
+        <v>1</v>
+      </c>
+      <c r="E56">
+        <v>1</v>
+      </c>
+      <c r="F56" t="s">
+        <v>1748</v>
+      </c>
+      <c r="G56">
         <v>0</v>
       </c>
     </row>
@@ -39835,7 +40383,7 @@
         <v>1740</v>
       </c>
       <c r="R75" s="46" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
       <c r="S75" s="46">
         <v>1</v>
@@ -39909,7 +40457,7 @@
         <v>1740</v>
       </c>
       <c r="R76" s="46" t="s">
-        <v>1742</v>
+        <v>1745</v>
       </c>
       <c r="S76" s="46">
         <v>10</v>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F139F1C0-22E5-4678-A392-CD59DE825195}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A671746F-2330-4AA6-96B6-568CDC002519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7550" uniqueCount="1750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7543" uniqueCount="1750">
   <si>
     <t>NAME</t>
   </si>
@@ -41354,8 +41354,8 @@
       <c r="F19" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="G19" s="51" t="s">
-        <v>36</v>
+      <c r="G19" s="51">
+        <v>1</v>
       </c>
       <c r="H19" s="51" t="s">
         <v>36</v>
@@ -41406,8 +41406,8 @@
       <c r="F20" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="G20" s="51" t="s">
-        <v>36</v>
+      <c r="G20" s="51">
+        <v>1</v>
       </c>
       <c r="H20" s="51" t="s">
         <v>36</v>
@@ -41458,8 +41458,8 @@
       <c r="F21" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="G21" s="51" t="s">
-        <v>36</v>
+      <c r="G21" s="51">
+        <v>1</v>
       </c>
       <c r="H21" s="51" t="s">
         <v>36</v>
@@ -41510,11 +41510,11 @@
       <c r="F22" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="G22" s="51" t="s">
-        <v>36</v>
+      <c r="G22" s="51">
+        <v>1</v>
       </c>
       <c r="H22" s="51" t="s">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="I22" s="51" t="s">
         <v>36</v>
@@ -41562,8 +41562,8 @@
       <c r="F23" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="G23" s="51" t="s">
-        <v>36</v>
+      <c r="G23" s="51">
+        <v>1</v>
       </c>
       <c r="H23" s="51" t="s">
         <v>36</v>
@@ -41600,8 +41600,8 @@
       <c r="F24" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="G24" s="51" t="s">
-        <v>36</v>
+      <c r="G24" s="51">
+        <v>1</v>
       </c>
       <c r="H24" s="51" t="s">
         <v>36</v>
@@ -41638,8 +41638,8 @@
       <c r="F25" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="G25" s="51" t="s">
-        <v>36</v>
+      <c r="G25" s="51">
+        <v>1</v>
       </c>
       <c r="H25" s="51" t="s">
         <v>36</v>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A671746F-2330-4AA6-96B6-568CDC002519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E6D212-4E50-4A23-A02D-25F7A2F199D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7543" uniqueCount="1750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7572" uniqueCount="1750">
   <si>
     <t>NAME</t>
   </si>
@@ -10001,38 +10001,150 @@
       </c>
     </row>
     <row r="28" spans="1:48" ht="12.5">
-      <c r="A28" s="48"/>
-      <c r="B28" s="48"/>
-      <c r="C28" s="48"/>
-      <c r="D28" s="48"/>
-      <c r="E28" s="48"/>
-      <c r="F28" s="48"/>
-      <c r="G28" s="48"/>
-      <c r="H28" s="48"/>
-      <c r="I28" s="48"/>
-      <c r="J28" s="48"/>
-      <c r="K28" s="48"/>
-      <c r="L28" s="48"/>
-      <c r="M28" s="48"/>
-      <c r="N28" s="48"/>
-      <c r="O28" s="48"/>
-      <c r="P28" s="48"/>
-      <c r="Q28" s="48"/>
-      <c r="R28" s="48"/>
-      <c r="S28" s="48"/>
-      <c r="T28" s="48"/>
-      <c r="U28" s="48"/>
-      <c r="V28" s="48"/>
-      <c r="W28" s="48"/>
-      <c r="X28" s="48"/>
-      <c r="Y28" s="48"/>
-      <c r="Z28" s="40"/>
-      <c r="AA28" s="7"/>
-      <c r="AB28" s="7"/>
-      <c r="AF28" s="28"/>
-      <c r="AH28" s="28"/>
-      <c r="AI28" s="28"/>
-      <c r="AJ28" s="46"/>
+      <c r="A28" s="47" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B28" s="48">
+        <v>1</v>
+      </c>
+      <c r="C28" s="48">
+        <v>2</v>
+      </c>
+      <c r="D28" s="48" t="s">
+        <v>30</v>
+      </c>
+      <c r="E28" s="48" t="s">
+        <v>31</v>
+      </c>
+      <c r="F28" s="48">
+        <v>0</v>
+      </c>
+      <c r="G28" s="48">
+        <v>10000</v>
+      </c>
+      <c r="H28" s="48">
+        <v>45</v>
+      </c>
+      <c r="I28" s="48">
+        <v>100</v>
+      </c>
+      <c r="J28" s="48">
+        <v>0</v>
+      </c>
+      <c r="K28" s="48">
+        <v>11</v>
+      </c>
+      <c r="L28" s="48">
+        <v>1</v>
+      </c>
+      <c r="M28" s="48">
+        <v>0</v>
+      </c>
+      <c r="N28" s="48">
+        <v>0</v>
+      </c>
+      <c r="O28" s="48">
+        <v>0</v>
+      </c>
+      <c r="P28" s="48">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="R28" s="48">
+        <v>30</v>
+      </c>
+      <c r="S28" s="40" t="s">
+        <v>33</v>
+      </c>
+      <c r="T28" s="40" t="s">
+        <v>1603</v>
+      </c>
+      <c r="U28" s="40" t="s">
+        <v>42</v>
+      </c>
+      <c r="V28" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="W28" s="40">
+        <v>40</v>
+      </c>
+      <c r="X28" s="7">
+        <v>80</v>
+      </c>
+      <c r="Y28" s="42">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="40">
+        <v>45</v>
+      </c>
+      <c r="AA28" s="7">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="7">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="s">
+        <v>37</v>
+      </c>
+      <c r="AD28" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE28" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF28">
+        <v>1</v>
+      </c>
+      <c r="AG28">
+        <v>1</v>
+      </c>
+      <c r="AH28">
+        <v>6</v>
+      </c>
+      <c r="AI28">
+        <v>3</v>
+      </c>
+      <c r="AJ28" s="46" t="s">
+        <v>1519</v>
+      </c>
+      <c r="AK28">
+        <v>0</v>
+      </c>
+      <c r="AL28">
+        <v>0</v>
+      </c>
+      <c r="AM28">
+        <v>0</v>
+      </c>
+      <c r="AN28">
+        <v>0</v>
+      </c>
+      <c r="AO28">
+        <v>-1</v>
+      </c>
+      <c r="AP28">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AS28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AT28" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU28">
+        <v>0</v>
+      </c>
+      <c r="AV28">
+        <v>0</v>
+      </c>
     </row>
     <row r="29" spans="1:48" ht="12.5">
       <c r="A29" s="48"/>
@@ -40592,7 +40704,7 @@
         <v>1740</v>
       </c>
       <c r="R75" s="46" t="s">
-        <v>1745</v>
+        <v>1742</v>
       </c>
       <c r="S75" s="46">
         <v>1</v>
@@ -40666,7 +40778,7 @@
         <v>1740</v>
       </c>
       <c r="R76" s="46" t="s">
-        <v>1745</v>
+        <v>1742</v>
       </c>
       <c r="S76" s="46">
         <v>10</v>
@@ -44380,7 +44492,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6EE0150-8FFB-4453-BBB2-90368188C9E0}">
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AZ34"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="17.26953125" customWidth="1"/>
@@ -44413,17 +44525,17 @@
     <col min="38" max="38" width="9.54296875" customWidth="1"/>
     <col min="39" max="39" width="9.36328125" customWidth="1"/>
     <col min="40" max="40" width="11.453125" customWidth="1"/>
-    <col min="41" max="41" width="14" customWidth="1"/>
-    <col min="42" max="42" width="7.453125" customWidth="1"/>
-    <col min="43" max="43" width="9" customWidth="1"/>
-    <col min="44" max="44" width="8.26953125" customWidth="1"/>
-    <col min="45" max="45" width="8.7265625" customWidth="1"/>
+    <col min="41" max="41" width="13.453125" customWidth="1"/>
+    <col min="42" max="42" width="6.453125" customWidth="1"/>
+    <col min="43" max="43" width="7.6328125" customWidth="1"/>
+    <col min="44" max="44" width="6.6328125" customWidth="1"/>
+    <col min="45" max="45" width="7" customWidth="1"/>
     <col min="46" max="46" width="7.81640625" customWidth="1"/>
     <col min="48" max="48" width="7" customWidth="1"/>
     <col min="49" max="51" width="7.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:51" ht="13">
+    <row r="1" spans="1:52" ht="13">
       <c r="A1" s="43" t="s">
         <v>0</v>
       </c>
@@ -44577,8 +44689,11 @@
       <c r="AY1" s="43" t="s">
         <v>1704</v>
       </c>
-    </row>
-    <row r="2" spans="1:51">
+      <c r="AZ1" s="43" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:52">
       <c r="A2" s="44" t="s">
         <v>35</v>
       </c>
@@ -44732,8 +44847,11 @@
       <c r="AY2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:51">
+      <c r="AZ2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:52">
       <c r="A3" s="44" t="s">
         <v>42</v>
       </c>
@@ -44887,8 +45005,11 @@
       <c r="AY3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:51">
+      <c r="AZ3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:52">
       <c r="A4" s="44" t="s">
         <v>1379</v>
       </c>
@@ -45042,8 +45163,11 @@
       <c r="AY4">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:51">
+      <c r="AZ4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:52">
       <c r="A5" s="44" t="s">
         <v>1380</v>
       </c>
@@ -45197,8 +45321,11 @@
       <c r="AY5">
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:51">
+      <c r="AZ5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:52">
       <c r="A6" s="44" t="s">
         <v>1477</v>
       </c>
@@ -45352,8 +45479,11 @@
       <c r="AY6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:51">
+      <c r="AZ6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:52">
       <c r="A7" s="44" t="s">
         <v>1491</v>
       </c>
@@ -45507,8 +45637,11 @@
       <c r="AY7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:51">
+      <c r="AZ7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:52">
       <c r="A8" s="44" t="s">
         <v>1438</v>
       </c>
@@ -45662,8 +45795,11 @@
       <c r="AY8">
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:51">
+      <c r="AZ8">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:52">
       <c r="A9" s="44" t="s">
         <v>1441</v>
       </c>
@@ -45817,8 +45953,11 @@
       <c r="AY9">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:51">
+      <c r="AZ9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:52">
       <c r="A10" s="44" t="s">
         <v>1455</v>
       </c>
@@ -45972,8 +46111,11 @@
       <c r="AY10">
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:51">
+      <c r="AZ10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:52">
       <c r="A11" s="44" t="s">
         <v>1532</v>
       </c>
@@ -46127,8 +46269,11 @@
       <c r="AY11">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:51">
+      <c r="AZ11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:52">
       <c r="A12" s="44" t="s">
         <v>1456</v>
       </c>
@@ -46282,8 +46427,11 @@
       <c r="AY12">
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:51">
+      <c r="AZ12">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:52">
       <c r="A13" s="44" t="s">
         <v>1457</v>
       </c>
@@ -46437,8 +46585,11 @@
       <c r="AY13">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:51">
+      <c r="AZ13">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:52">
       <c r="A14" s="44" t="s">
         <v>1493</v>
       </c>
@@ -46592,8 +46743,11 @@
       <c r="AY14">
         <v>0</v>
       </c>
-    </row>
-    <row r="15" spans="1:51">
+      <c r="AZ14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:52">
       <c r="A15" s="44" t="s">
         <v>1497</v>
       </c>
@@ -46747,8 +46901,11 @@
       <c r="AY15">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:51">
+      <c r="AZ15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:52">
       <c r="A16" s="44" t="s">
         <v>1498</v>
       </c>
@@ -46902,8 +47059,11 @@
       <c r="AY16">
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="1:51">
+      <c r="AZ16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:52">
       <c r="A17" s="44" t="s">
         <v>1502</v>
       </c>
@@ -47057,8 +47217,11 @@
       <c r="AY17">
         <v>0</v>
       </c>
-    </row>
-    <row r="18" spans="1:51">
+      <c r="AZ17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:52">
       <c r="A18" s="44" t="s">
         <v>1509</v>
       </c>
@@ -47212,8 +47375,11 @@
       <c r="AY18">
         <v>0</v>
       </c>
-    </row>
-    <row r="19" spans="1:51">
+      <c r="AZ18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:52">
       <c r="A19" s="44" t="s">
         <v>1510</v>
       </c>
@@ -47367,8 +47533,11 @@
       <c r="AY19">
         <v>0</v>
       </c>
-    </row>
-    <row r="20" spans="1:51">
+      <c r="AZ19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:52">
       <c r="A20" s="44" t="s">
         <v>1439</v>
       </c>
@@ -47522,8 +47691,11 @@
       <c r="AY20">
         <v>0</v>
       </c>
-    </row>
-    <row r="21" spans="1:51">
+      <c r="AZ20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:52">
       <c r="A21" s="44" t="s">
         <v>1559</v>
       </c>
@@ -47677,8 +47849,11 @@
       <c r="AY21">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:51">
+      <c r="AZ21">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:52">
       <c r="A22" s="44" t="s">
         <v>1595</v>
       </c>
@@ -47832,8 +48007,11 @@
       <c r="AY22">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="1:51">
+      <c r="AZ22">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:52">
       <c r="A23" s="44" t="s">
         <v>935</v>
       </c>
@@ -47987,8 +48165,11 @@
       <c r="AY23">
         <v>0</v>
       </c>
-    </row>
-    <row r="24" spans="1:51">
+      <c r="AZ23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:52">
       <c r="A24" s="44" t="s">
         <v>1601</v>
       </c>
@@ -48142,8 +48323,11 @@
       <c r="AY24">
         <v>0</v>
       </c>
-    </row>
-    <row r="25" spans="1:51">
+      <c r="AZ24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:52">
       <c r="A25" s="44" t="s">
         <v>1610</v>
       </c>
@@ -48297,8 +48481,11 @@
       <c r="AY25">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="1:51">
+      <c r="AZ25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:52">
       <c r="A26" s="44" t="s">
         <v>1619</v>
       </c>
@@ -48452,8 +48639,11 @@
       <c r="AY26">
         <v>0</v>
       </c>
-    </row>
-    <row r="27" spans="1:51">
+      <c r="AZ26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:52">
       <c r="A27" s="44" t="s">
         <v>1623</v>
       </c>
@@ -48607,8 +48797,11 @@
       <c r="AY27">
         <v>0</v>
       </c>
-    </row>
-    <row r="28" spans="1:51">
+      <c r="AZ27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:52">
       <c r="A28" s="44" t="s">
         <v>1624</v>
       </c>
@@ -48762,8 +48955,11 @@
       <c r="AY28">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="1:51">
+      <c r="AZ28">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:52">
       <c r="A29" s="44" t="s">
         <v>1628</v>
       </c>
@@ -48917,8 +49113,11 @@
       <c r="AY29">
         <v>0</v>
       </c>
-    </row>
-    <row r="30" spans="1:51">
+      <c r="AZ29">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:52">
       <c r="A30" s="44" t="s">
         <v>1632</v>
       </c>
@@ -49072,8 +49271,11 @@
       <c r="AY30">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="1:51">
+      <c r="AZ30">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:52">
       <c r="A31" s="44" t="s">
         <v>1655</v>
       </c>
@@ -49227,8 +49429,11 @@
       <c r="AY31">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="1:51">
+      <c r="AZ31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:52">
       <c r="A32" s="44" t="s">
         <v>1586</v>
       </c>
@@ -49382,8 +49587,11 @@
       <c r="AY32">
         <v>0</v>
       </c>
-    </row>
-    <row r="33" spans="1:51">
+      <c r="AZ32">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:52">
       <c r="A33" s="44" t="s">
         <v>1695</v>
       </c>
@@ -49535,6 +49743,167 @@
         <v>0</v>
       </c>
       <c r="AY33">
+        <v>0</v>
+      </c>
+      <c r="AZ33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:52">
+      <c r="A34" s="44" t="s">
+        <v>1738</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34">
+        <v>0</v>
+      </c>
+      <c r="D34">
+        <v>0</v>
+      </c>
+      <c r="E34">
+        <v>0</v>
+      </c>
+      <c r="F34">
+        <v>0</v>
+      </c>
+      <c r="G34">
+        <v>0</v>
+      </c>
+      <c r="H34">
+        <v>0</v>
+      </c>
+      <c r="I34">
+        <v>0</v>
+      </c>
+      <c r="J34">
+        <v>0</v>
+      </c>
+      <c r="K34">
+        <v>0</v>
+      </c>
+      <c r="L34">
+        <v>0</v>
+      </c>
+      <c r="M34">
+        <v>0</v>
+      </c>
+      <c r="N34">
+        <v>0</v>
+      </c>
+      <c r="O34">
+        <v>0</v>
+      </c>
+      <c r="P34">
+        <v>0</v>
+      </c>
+      <c r="Q34">
+        <v>0</v>
+      </c>
+      <c r="R34">
+        <v>0</v>
+      </c>
+      <c r="S34">
+        <v>3</v>
+      </c>
+      <c r="T34">
+        <v>0</v>
+      </c>
+      <c r="U34">
+        <v>0</v>
+      </c>
+      <c r="V34">
+        <v>0</v>
+      </c>
+      <c r="W34">
+        <v>0</v>
+      </c>
+      <c r="X34">
+        <v>1</v>
+      </c>
+      <c r="Y34">
+        <v>0</v>
+      </c>
+      <c r="Z34">
+        <v>-1</v>
+      </c>
+      <c r="AA34">
+        <v>0</v>
+      </c>
+      <c r="AB34">
+        <v>10</v>
+      </c>
+      <c r="AC34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AD34" s="44" t="s">
+        <v>1371</v>
+      </c>
+      <c r="AE34" s="44" t="s">
+        <v>1478</v>
+      </c>
+      <c r="AF34" s="44" t="s">
+        <v>1478</v>
+      </c>
+      <c r="AG34" s="44">
+        <v>0</v>
+      </c>
+      <c r="AH34" s="44" t="s">
+        <v>1482</v>
+      </c>
+      <c r="AI34" s="44">
+        <v>1</v>
+      </c>
+      <c r="AJ34" s="44" t="s">
+        <v>36</v>
+      </c>
+      <c r="AK34" s="44">
+        <v>0</v>
+      </c>
+      <c r="AL34">
+        <v>0</v>
+      </c>
+      <c r="AM34">
+        <v>0</v>
+      </c>
+      <c r="AN34">
+        <v>1</v>
+      </c>
+      <c r="AO34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP34">
+        <v>0</v>
+      </c>
+      <c r="AQ34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AR34">
+        <v>0</v>
+      </c>
+      <c r="AS34">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AU34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AV34" t="s">
+        <v>36</v>
+      </c>
+      <c r="AW34">
+        <v>0</v>
+      </c>
+      <c r="AX34">
+        <v>0</v>
+      </c>
+      <c r="AY34">
+        <v>0</v>
+      </c>
+      <c r="AZ34">
         <v>0</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48E6D212-4E50-4A23-A02D-25F7A2F199D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D661EB2-3630-4E9E-A0BA-405645FB6718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="17" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -40704,7 +40704,7 @@
         <v>1740</v>
       </c>
       <c r="R75" s="46" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="S75" s="46">
         <v>1</v>
@@ -40778,7 +40778,7 @@
         <v>1740</v>
       </c>
       <c r="R76" s="46" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="S76" s="46">
         <v>10</v>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D661EB2-3630-4E9E-A0BA-405645FB6718}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFE1133-BC29-4B9F-9616-75B066A0C26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="17" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40704,7 +40704,7 @@
         <v>1740</v>
       </c>
       <c r="R75" s="46" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="S75" s="46">
         <v>1</v>
@@ -40778,7 +40778,7 @@
         <v>1740</v>
       </c>
       <c r="R76" s="46" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="S76" s="46">
         <v>10</v>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFE1133-BC29-4B9F-9616-75B066A0C26A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507F2EF7-8587-4480-ACE8-5E4EC5BB06A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="17" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7572" uniqueCount="1750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7662" uniqueCount="1757">
   <si>
     <t>NAME</t>
   </si>
@@ -5434,6 +5434,27 @@
   </si>
   <si>
     <t>goblin</t>
+  </si>
+  <si>
+    <t>sand</t>
+  </si>
+  <si>
+    <t>sphere_draw,1</t>
+  </si>
+  <si>
+    <t>sphere_draw,10</t>
+  </si>
+  <si>
+    <t>draw_mon</t>
+  </si>
+  <si>
+    <t>draw_ten_mon</t>
+  </si>
+  <si>
+    <t>draw_itm</t>
+  </si>
+  <si>
+    <t>draw_ten_itm</t>
   </si>
 </sst>
 </file>
@@ -36236,7 +36257,7 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{87945C49-375A-40BB-B037-1C50621D6D44}">
-  <dimension ref="A1:X76"/>
+  <dimension ref="A1:X80"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="17.08984375" customWidth="1"/>
@@ -40656,7 +40677,7 @@
         <v>1740</v>
       </c>
       <c r="B75" s="46" t="s">
-        <v>1567</v>
+        <v>1751</v>
       </c>
       <c r="C75" s="46" t="s">
         <v>36</v>
@@ -40730,7 +40751,7 @@
         <v>1741</v>
       </c>
       <c r="B76" s="46" t="s">
-        <v>1201</v>
+        <v>1752</v>
       </c>
       <c r="C76" s="46" t="s">
         <v>36</v>
@@ -40796,6 +40817,302 @@
         <v>1</v>
       </c>
       <c r="X76" s="46">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24">
+      <c r="A77" s="46" t="s">
+        <v>1753</v>
+      </c>
+      <c r="B77" s="46" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C77" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="D77" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="E77" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F77" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G77" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="H77" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="I77" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="J77" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="K77" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="L77" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="M77" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="N77" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="O77" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="P77" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q77" s="46" t="s">
+        <v>1753</v>
+      </c>
+      <c r="R77" s="46" t="s">
+        <v>1745</v>
+      </c>
+      <c r="S77" s="46">
+        <v>1</v>
+      </c>
+      <c r="T77" s="46">
+        <v>-1</v>
+      </c>
+      <c r="U77" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="V77" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="W77" s="46">
+        <v>1</v>
+      </c>
+      <c r="X77" s="46">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24">
+      <c r="A78" s="46" t="s">
+        <v>1754</v>
+      </c>
+      <c r="B78" s="46" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="D78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="E78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="H78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="I78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="J78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="K78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="L78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="M78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="N78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="O78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="P78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q78" s="46" t="s">
+        <v>1753</v>
+      </c>
+      <c r="R78" s="46" t="s">
+        <v>1745</v>
+      </c>
+      <c r="S78" s="46">
+        <v>10</v>
+      </c>
+      <c r="T78" s="46">
+        <v>-1</v>
+      </c>
+      <c r="U78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="V78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="W78" s="46">
+        <v>1</v>
+      </c>
+      <c r="X78" s="46">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24">
+      <c r="A79" s="46" t="s">
+        <v>1755</v>
+      </c>
+      <c r="B79" s="46" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C79" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="D79" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="E79" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F79" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G79" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="H79" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="I79" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="J79" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="K79" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="L79" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="M79" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="N79" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="O79" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="P79" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q79" s="46" t="s">
+        <v>1755</v>
+      </c>
+      <c r="R79" s="46" t="s">
+        <v>1743</v>
+      </c>
+      <c r="S79" s="46">
+        <v>1</v>
+      </c>
+      <c r="T79" s="46">
+        <v>-1</v>
+      </c>
+      <c r="U79" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="V79" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="W79" s="46">
+        <v>1</v>
+      </c>
+      <c r="X79" s="46">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24">
+      <c r="A80" s="46" t="s">
+        <v>1756</v>
+      </c>
+      <c r="B80" s="46" t="s">
+        <v>1752</v>
+      </c>
+      <c r="C80" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="D80" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="E80" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F80" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G80" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="H80" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="I80" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="J80" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="K80" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="L80" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="M80" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="N80" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="O80" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="P80" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q80" s="46" t="s">
+        <v>1755</v>
+      </c>
+      <c r="R80" s="46" t="s">
+        <v>1743</v>
+      </c>
+      <c r="S80" s="46">
+        <v>10</v>
+      </c>
+      <c r="T80" s="46">
+        <v>-1</v>
+      </c>
+      <c r="U80" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="V80" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="W80" s="46">
+        <v>1</v>
+      </c>
+      <c r="X80" s="46">
         <v>-1</v>
       </c>
     </row>
@@ -42850,7 +43167,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4267B9-6C50-42DE-8EEA-ACDE778B1226}">
-  <dimension ref="A1:U25"/>
+  <dimension ref="A1:U27"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="15.26953125" customWidth="1"/>
@@ -44483,6 +44800,136 @@
       </c>
       <c r="U25" t="s">
         <v>1567</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21">
+      <c r="A26" s="44" t="s">
+        <v>1750</v>
+      </c>
+      <c r="B26">
+        <v>0</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+      <c r="G26">
+        <v>0</v>
+      </c>
+      <c r="H26">
+        <v>0</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>0</v>
+      </c>
+      <c r="M26">
+        <v>0</v>
+      </c>
+      <c r="N26">
+        <v>10</v>
+      </c>
+      <c r="O26" s="44" t="s">
+        <v>1376</v>
+      </c>
+      <c r="P26">
+        <v>0</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+      <c r="R26" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="S26" t="s">
+        <v>36</v>
+      </c>
+      <c r="T26">
+        <v>11</v>
+      </c>
+      <c r="U26" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21">
+      <c r="A27" s="44" t="s">
+        <v>959</v>
+      </c>
+      <c r="B27">
+        <v>0</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+      <c r="G27">
+        <v>0</v>
+      </c>
+      <c r="H27">
+        <v>0</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>0</v>
+      </c>
+      <c r="L27">
+        <v>0</v>
+      </c>
+      <c r="M27">
+        <v>0</v>
+      </c>
+      <c r="N27">
+        <v>10</v>
+      </c>
+      <c r="O27" s="44" t="s">
+        <v>1376</v>
+      </c>
+      <c r="P27">
+        <v>0</v>
+      </c>
+      <c r="Q27">
+        <v>1</v>
+      </c>
+      <c r="R27" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="S27" t="s">
+        <v>36</v>
+      </c>
+      <c r="T27">
+        <v>11</v>
+      </c>
+      <c r="U27" t="s">
+        <v>1666</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{507F2EF7-8587-4480-ACE8-5E4EC5BB06A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DC96A1-F949-403A-9321-AC4D5D70857B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="17" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="9" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -5259,9 +5259,6 @@
     <t>main  size when using inv any</t>
   </si>
   <si>
-    <t>gold,10000#res1,10#res2,10#gem,100#bronze_key,1</t>
-  </si>
-  <si>
     <t>use_2d_navmesh</t>
   </si>
   <si>
@@ -5455,6 +5452,9 @@
   </si>
   <si>
     <t>draw_ten_itm</t>
+  </si>
+  <si>
+    <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1</t>
   </si>
 </sst>
 </file>
@@ -6216,13 +6216,13 @@
         <v>1630</v>
       </c>
       <c r="AT1" s="6" t="s">
-        <v>1709</v>
+        <v>1708</v>
       </c>
       <c r="AU1" s="6" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="AV1" s="6" t="s">
-        <v>1724</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="2" spans="1:48" ht="12.5">
@@ -6284,7 +6284,7 @@
         <v>33</v>
       </c>
       <c r="T2" s="40" t="s">
-        <v>1696</v>
+        <v>1695</v>
       </c>
       <c r="U2" s="40" t="s">
         <v>42</v>
@@ -8230,7 +8230,7 @@
         <v>3</v>
       </c>
       <c r="AJ15" s="46" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="AK15">
         <v>1</v>
@@ -8668,7 +8668,7 @@
         <v>3</v>
       </c>
       <c r="AJ18" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="AK18">
         <v>1</v>
@@ -8689,7 +8689,7 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="AR18" t="s">
         <v>36</v>
@@ -9136,7 +9136,7 @@
         <v>36</v>
       </c>
       <c r="AT21" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="AU21">
         <v>1</v>
@@ -9147,7 +9147,7 @@
     </row>
     <row r="22" spans="1:48" ht="12.5">
       <c r="A22" s="47" t="s">
-        <v>1725</v>
+        <v>1724</v>
       </c>
       <c r="B22" s="48">
         <v>1</v>
@@ -9252,7 +9252,7 @@
         <v>3</v>
       </c>
       <c r="AJ22" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="AK22">
         <v>1</v>
@@ -9273,7 +9273,7 @@
         <v>0</v>
       </c>
       <c r="AQ22" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="AR22" t="s">
         <v>36</v>
@@ -9293,7 +9293,7 @@
     </row>
     <row r="23" spans="1:48" ht="12.5">
       <c r="A23" s="47" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="B23" s="48">
         <v>1</v>
@@ -9439,7 +9439,7 @@
     </row>
     <row r="24" spans="1:48" ht="12.5">
       <c r="A24" s="47" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="B24" s="48">
         <v>1</v>
@@ -9585,7 +9585,7 @@
     </row>
     <row r="25" spans="1:48" ht="12.5">
       <c r="A25" s="47" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="B25" s="48">
         <v>1</v>
@@ -9731,7 +9731,7 @@
     </row>
     <row r="26" spans="1:48" ht="12.5">
       <c r="A26" s="47" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="B26" s="48">
         <v>1</v>
@@ -10023,7 +10023,7 @@
     </row>
     <row r="28" spans="1:48" ht="12.5">
       <c r="A28" s="47" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="B28" s="48">
         <v>1</v>
@@ -24518,7 +24518,7 @@
     </row>
     <row r="13" spans="1:19" ht="12.5">
       <c r="A13" s="4" t="s">
-        <v>1698</v>
+        <v>1697</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>892</v>
@@ -24598,7 +24598,7 @@
     </row>
     <row r="15" spans="1:19" ht="12.5">
       <c r="A15" s="4" t="s">
-        <v>1700</v>
+        <v>1699</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>892</v>
@@ -24625,7 +24625,7 @@
         <v>30</v>
       </c>
       <c r="J15" s="50" t="s">
-        <v>1699</v>
+        <v>1698</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>36</v>
@@ -31762,35 +31762,35 @@
     </row>
     <row r="62" spans="1:3" ht="15.75" customHeight="1">
       <c r="A62" t="s">
+        <v>1691</v>
+      </c>
+      <c r="B62">
+        <v>1</v>
+      </c>
+      <c r="C62" t="s">
         <v>1692</v>
-      </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62" t="s">
-        <v>1693</v>
       </c>
     </row>
     <row r="63" spans="1:3" ht="15.75" customHeight="1">
       <c r="A63" t="s">
+        <v>1700</v>
+      </c>
+      <c r="B63">
+        <v>1</v>
+      </c>
+      <c r="C63" t="s">
         <v>1701</v>
-      </c>
-      <c r="B63">
-        <v>1</v>
-      </c>
-      <c r="C63" t="s">
-        <v>1702</v>
       </c>
     </row>
     <row r="64" spans="1:3" ht="15.75" customHeight="1">
       <c r="A64" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B64">
+        <v>0</v>
+      </c>
+      <c r="C64" t="s">
         <v>1722</v>
-      </c>
-      <c r="B64">
-        <v>0</v>
-      </c>
-      <c r="C64" t="s">
-        <v>1723</v>
       </c>
     </row>
   </sheetData>
@@ -32364,7 +32364,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>1705</v>
+        <v>1704</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -32379,7 +32379,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>1706</v>
+        <v>1705</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -32387,7 +32387,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -32410,7 +32410,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>1727</v>
+        <v>1726</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -32425,7 +32425,7 @@
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -32433,7 +32433,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -32525,7 +32525,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -32617,7 +32617,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -32632,7 +32632,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>1749</v>
+        <v>1748</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -32655,7 +32655,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -32678,7 +32678,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -32701,7 +32701,7 @@
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>1748</v>
+        <v>1747</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -32924,7 +32924,7 @@
         <v>36</v>
       </c>
       <c r="C3" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="D3" t="s">
         <v>36</v>
@@ -32962,7 +32962,7 @@
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>1732</v>
+        <v>1731</v>
       </c>
       <c r="B4" t="s">
         <v>1182</v>
@@ -32974,7 +32974,7 @@
         <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>1733</v>
+        <v>1732</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -33012,7 +33012,7 @@
         <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="D5" t="s">
         <v>36</v>
@@ -33050,7 +33050,7 @@
     </row>
     <row r="6" spans="1:19">
       <c r="A6" t="s">
-        <v>1734</v>
+        <v>1733</v>
       </c>
       <c r="B6" t="s">
         <v>1182</v>
@@ -33062,7 +33062,7 @@
         <v>36</v>
       </c>
       <c r="E6" t="s">
-        <v>1735</v>
+        <v>1734</v>
       </c>
       <c r="F6" t="s">
         <v>36</v>
@@ -33100,7 +33100,7 @@
         <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>1731</v>
+        <v>1730</v>
       </c>
       <c r="D7" t="s">
         <v>36</v>
@@ -33997,7 +33997,7 @@
         <v>1464</v>
       </c>
       <c r="B5" t="s">
-        <v>1691</v>
+        <v>1756</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -36294,7 +36294,7 @@
         <v>1419</v>
       </c>
       <c r="E1" s="45" t="s">
-        <v>1737</v>
+        <v>1736</v>
       </c>
       <c r="F1" s="45" t="s">
         <v>1420</v>
@@ -36318,7 +36318,7 @@
         <v>1526</v>
       </c>
       <c r="M1" s="45" t="s">
-        <v>1711</v>
+        <v>1710</v>
       </c>
       <c r="N1" s="45" t="s">
         <v>1437</v>
@@ -36336,7 +36336,7 @@
         <v>1463</v>
       </c>
       <c r="S1" s="45" t="s">
-        <v>1744</v>
+        <v>1743</v>
       </c>
       <c r="T1" s="45" t="s">
         <v>1565</v>
@@ -40304,7 +40304,7 @@
     </row>
     <row r="68" spans="1:24">
       <c r="A68" s="46" t="s">
-        <v>1710</v>
+        <v>1709</v>
       </c>
       <c r="B68" s="46" t="s">
         <v>36</v>
@@ -40352,7 +40352,7 @@
         <v>36</v>
       </c>
       <c r="Q68" s="46" t="s">
-        <v>1697</v>
+        <v>1696</v>
       </c>
       <c r="R68" s="46" t="s">
         <v>36</v>
@@ -40367,7 +40367,7 @@
         <v>36</v>
       </c>
       <c r="V68" s="46" t="s">
-        <v>1720</v>
+        <v>1719</v>
       </c>
       <c r="W68" s="46">
         <v>1</v>
@@ -40378,7 +40378,7 @@
     </row>
     <row r="70" spans="1:24">
       <c r="A70" s="46" t="s">
-        <v>1712</v>
+        <v>1711</v>
       </c>
       <c r="B70" s="46" t="s">
         <v>1665</v>
@@ -40393,7 +40393,7 @@
         <v>36</v>
       </c>
       <c r="F70" s="46" t="s">
-        <v>1716</v>
+        <v>1715</v>
       </c>
       <c r="G70" s="46" t="s">
         <v>36</v>
@@ -40452,7 +40452,7 @@
     </row>
     <row r="71" spans="1:24">
       <c r="A71" s="46" t="s">
-        <v>1713</v>
+        <v>1712</v>
       </c>
       <c r="B71" s="46" t="s">
         <v>1666</v>
@@ -40467,7 +40467,7 @@
         <v>36</v>
       </c>
       <c r="F71" s="46" t="s">
-        <v>1717</v>
+        <v>1716</v>
       </c>
       <c r="G71" s="46" t="s">
         <v>36</v>
@@ -40526,7 +40526,7 @@
     </row>
     <row r="72" spans="1:24">
       <c r="A72" s="46" t="s">
-        <v>1714</v>
+        <v>1713</v>
       </c>
       <c r="B72" s="46" t="s">
         <v>1667</v>
@@ -40541,7 +40541,7 @@
         <v>36</v>
       </c>
       <c r="F72" s="46" t="s">
-        <v>1718</v>
+        <v>1717</v>
       </c>
       <c r="G72" s="46" t="s">
         <v>36</v>
@@ -40600,7 +40600,7 @@
     </row>
     <row r="73" spans="1:24">
       <c r="A73" s="46" t="s">
-        <v>1715</v>
+        <v>1714</v>
       </c>
       <c r="B73" s="46" t="s">
         <v>1668</v>
@@ -40615,7 +40615,7 @@
         <v>36</v>
       </c>
       <c r="F73" s="46" t="s">
-        <v>1719</v>
+        <v>1718</v>
       </c>
       <c r="G73" s="46" t="s">
         <v>36</v>
@@ -40674,10 +40674,10 @@
     </row>
     <row r="75" spans="1:24">
       <c r="A75" s="46" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="B75" s="46" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="C75" s="46" t="s">
         <v>36</v>
@@ -40722,10 +40722,10 @@
         <v>36</v>
       </c>
       <c r="Q75" s="46" t="s">
-        <v>1740</v>
+        <v>1739</v>
       </c>
       <c r="R75" s="46" t="s">
-        <v>1742</v>
+        <v>1741</v>
       </c>
       <c r="S75" s="46">
         <v>1</v>
@@ -40748,58 +40748,58 @@
     </row>
     <row r="76" spans="1:24">
       <c r="A76" s="46" t="s">
+        <v>1740</v>
+      </c>
+      <c r="B76" s="46" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="D76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="E76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="H76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="I76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="J76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="K76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="L76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="M76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="N76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="O76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="P76" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q76" s="46" t="s">
+        <v>1739</v>
+      </c>
+      <c r="R76" s="46" t="s">
         <v>1741</v>
-      </c>
-      <c r="B76" s="46" t="s">
-        <v>1752</v>
-      </c>
-      <c r="C76" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="D76" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="E76" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="F76" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="G76" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="H76" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="I76" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="J76" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="K76" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L76" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="M76" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="N76" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="O76" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="P76" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q76" s="46" t="s">
-        <v>1740</v>
-      </c>
-      <c r="R76" s="46" t="s">
-        <v>1742</v>
       </c>
       <c r="S76" s="46">
         <v>10</v>
@@ -40822,10 +40822,10 @@
     </row>
     <row r="77" spans="1:24">
       <c r="A77" s="46" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="B77" s="46" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="C77" s="46" t="s">
         <v>36</v>
@@ -40870,10 +40870,10 @@
         <v>36</v>
       </c>
       <c r="Q77" s="46" t="s">
-        <v>1753</v>
+        <v>1752</v>
       </c>
       <c r="R77" s="46" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="S77" s="46">
         <v>1</v>
@@ -40896,58 +40896,58 @@
     </row>
     <row r="78" spans="1:24">
       <c r="A78" s="46" t="s">
-        <v>1754</v>
+        <v>1753</v>
       </c>
       <c r="B78" s="46" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="D78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="E78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="F78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="G78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="H78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="I78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="J78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="K78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="L78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="M78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="N78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="O78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="P78" s="46" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q78" s="46" t="s">
         <v>1752</v>
       </c>
-      <c r="C78" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="D78" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="E78" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="F78" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="G78" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="H78" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="I78" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="J78" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="K78" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="L78" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="M78" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="N78" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="O78" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="P78" s="46" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q78" s="46" t="s">
-        <v>1753</v>
-      </c>
       <c r="R78" s="46" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="S78" s="46">
         <v>10</v>
@@ -40970,10 +40970,10 @@
     </row>
     <row r="79" spans="1:24">
       <c r="A79" s="46" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="B79" s="46" t="s">
-        <v>1751</v>
+        <v>1750</v>
       </c>
       <c r="C79" s="46" t="s">
         <v>36</v>
@@ -41018,10 +41018,10 @@
         <v>36</v>
       </c>
       <c r="Q79" s="46" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="R79" s="46" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="S79" s="46">
         <v>1</v>
@@ -41044,10 +41044,10 @@
     </row>
     <row r="80" spans="1:24">
       <c r="A80" s="46" t="s">
-        <v>1756</v>
+        <v>1755</v>
       </c>
       <c r="B80" s="46" t="s">
-        <v>1752</v>
+        <v>1751</v>
       </c>
       <c r="C80" s="46" t="s">
         <v>36</v>
@@ -41092,10 +41092,10 @@
         <v>36</v>
       </c>
       <c r="Q80" s="46" t="s">
-        <v>1755</v>
+        <v>1754</v>
       </c>
       <c r="R80" s="46" t="s">
-        <v>1743</v>
+        <v>1742</v>
       </c>
       <c r="S80" s="46">
         <v>10</v>
@@ -41132,7 +41132,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="49" t="s">
-        <v>1707</v>
+        <v>1706</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -41558,7 +41558,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="51" t="s">
-        <v>1736</v>
+        <v>1735</v>
       </c>
       <c r="L12" s="51">
         <v>1</v>
@@ -41632,7 +41632,7 @@
     </row>
     <row r="16" spans="1:26" ht="13">
       <c r="A16" s="49" t="s">
-        <v>1708</v>
+        <v>1707</v>
       </c>
       <c r="B16" s="48"/>
       <c r="C16" s="48"/>
@@ -44479,7 +44479,7 @@
     </row>
     <row r="21" spans="1:21">
       <c r="A21" s="44" t="s">
-        <v>1728</v>
+        <v>1727</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -44544,7 +44544,7 @@
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="44" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -44609,7 +44609,7 @@
     </row>
     <row r="23" spans="1:21">
       <c r="A23" s="44" t="s">
-        <v>1730</v>
+        <v>1729</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -44674,7 +44674,7 @@
     </row>
     <row r="24" spans="1:21">
       <c r="A24" s="44" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -44739,7 +44739,7 @@
     </row>
     <row r="25" spans="1:21">
       <c r="A25" s="44" t="s">
-        <v>1739</v>
+        <v>1738</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -44804,7 +44804,7 @@
     </row>
     <row r="26" spans="1:21">
       <c r="A26" s="44" t="s">
-        <v>1750</v>
+        <v>1749</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -45128,13 +45128,13 @@
         <v>1631</v>
       </c>
       <c r="AW1" s="43" t="s">
-        <v>1694</v>
+        <v>1693</v>
       </c>
       <c r="AX1" s="43" t="s">
+        <v>1702</v>
+      </c>
+      <c r="AY1" s="43" t="s">
         <v>1703</v>
-      </c>
-      <c r="AY1" s="43" t="s">
-        <v>1704</v>
       </c>
       <c r="AZ1" s="43" t="s">
         <v>7</v>
@@ -50040,7 +50040,7 @@
     </row>
     <row r="33" spans="1:52">
       <c r="A33" s="44" t="s">
-        <v>1695</v>
+        <v>1694</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -50198,7 +50198,7 @@
     </row>
     <row r="34" spans="1:52">
       <c r="A34" s="44" t="s">
-        <v>1738</v>
+        <v>1737</v>
       </c>
       <c r="B34">
         <v>0</v>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50DC96A1-F949-403A-9321-AC4D5D70857B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{035DFDBD-0B29-46B3-AA16-C890F967BB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="9" activeTab="22" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7662" uniqueCount="1757">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7735" uniqueCount="1763">
   <si>
     <t>NAME</t>
   </si>
@@ -5455,6 +5455,24 @@
   </si>
   <si>
     <t>gold,10000#res1,10#res2,10#gem,1000#bronze_key,1</t>
+  </si>
+  <si>
+    <t>bite</t>
+  </si>
+  <si>
+    <t>STRINGVAL</t>
+  </si>
+  <si>
+    <t>upgrade_cost</t>
+  </si>
+  <si>
+    <t>gold,{level}*100#wood,{level}</t>
+  </si>
+  <si>
+    <t>ascend_cost</t>
+  </si>
+  <si>
+    <t>gold,{level}*10#wood,{level}</t>
   </si>
 </sst>
 </file>
@@ -5711,7 +5729,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
@@ -5786,6 +5804,9 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -31207,590 +31228,805 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:C64"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr defaultColWidth="12.54296875" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="36.08984375" customWidth="1"/>
     <col min="2" max="2" width="18.453125" customWidth="1"/>
-    <col min="3" max="3" width="35.6328125" customWidth="1"/>
+    <col min="3" max="3" width="25.26953125" customWidth="1"/>
+    <col min="4" max="4" width="35.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.75" customHeight="1">
+    <row r="1" spans="1:4" ht="15.75" customHeight="1">
       <c r="A1" s="6" t="s">
         <v>83</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="C1" s="45" t="s">
+      <c r="C1" s="6" t="s">
+        <v>1758</v>
+      </c>
+      <c r="D1" s="45" t="s">
         <v>1265</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="12.5">
+    <row r="2" spans="1:4" ht="12.5">
       <c r="A2" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="24">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="12.5">
+      <c r="C2" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" ht="12.5">
       <c r="A3" s="7" t="s">
         <v>86</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="24" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" ht="12.5">
+      <c r="C3" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="12.5">
       <c r="A4" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="B4" s="7">
+      <c r="B4" s="24">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:3" ht="12.5">
+      <c r="C4" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="12.5">
       <c r="A5" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="B5" s="7">
+      <c r="B5" s="24">
         <v>0.3</v>
       </c>
-    </row>
-    <row r="6" spans="1:3" ht="12.5">
+      <c r="C5" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="12.5">
       <c r="A6" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="B6" s="7">
+      <c r="B6" s="24">
         <v>4</v>
       </c>
-    </row>
-    <row r="7" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C6" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1">
       <c r="A7" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="52">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C7" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1">
       <c r="A8" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="7">
+      <c r="B8" s="24">
         <v>300</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C8" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1">
       <c r="A9" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="B9" s="7">
+      <c r="B9" s="24">
         <v>1500</v>
       </c>
-    </row>
-    <row r="10" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C9" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1">
       <c r="A10" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="B10" s="7">
+      <c r="B10" s="24">
         <v>30</v>
       </c>
-    </row>
-    <row r="11" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C10" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1">
       <c r="A11" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B11" s="24">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C11" s="24" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1">
       <c r="A12" t="s">
         <v>95</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="52">
         <v>10</v>
       </c>
-    </row>
-    <row r="13" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C12" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="15.75" customHeight="1">
       <c r="A13" t="s">
         <v>96</v>
       </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B13" s="52">
+        <v>1</v>
+      </c>
+      <c r="C13" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="15.75" customHeight="1">
       <c r="A14" t="s">
         <v>97</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="52">
         <v>10</v>
       </c>
-    </row>
-    <row r="15" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C14" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1">
       <c r="A15" t="s">
         <v>98</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="52">
         <v>1000</v>
       </c>
-    </row>
-    <row r="16" spans="1:3" ht="15.75" customHeight="1">
+      <c r="C15" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1">
       <c r="A16" t="s">
         <v>1348</v>
       </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" ht="15.75" customHeight="1">
+      <c r="B16" s="52">
+        <v>1</v>
+      </c>
+      <c r="C16" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" ht="15.75" customHeight="1">
       <c r="A17" t="s">
         <v>99</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="52">
         <v>1000</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="15.75" customHeight="1">
+      <c r="C17" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" ht="15.75" customHeight="1">
       <c r="A18" t="s">
         <v>1338</v>
       </c>
-      <c r="B18">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" ht="15.75" customHeight="1">
+      <c r="B18" s="52">
+        <v>1</v>
+      </c>
+      <c r="C18" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="15.75" customHeight="1">
       <c r="A19" t="s">
         <v>1339</v>
       </c>
-      <c r="B19">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2" ht="15.75" customHeight="1">
+      <c r="B19" s="52">
+        <v>1</v>
+      </c>
+      <c r="C19" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="15.75" customHeight="1">
       <c r="A20" t="s">
         <v>1340</v>
       </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2" ht="15.75" customHeight="1">
+      <c r="B20" s="52">
+        <v>0</v>
+      </c>
+      <c r="C20" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" ht="15.75" customHeight="1">
       <c r="A21" t="s">
         <v>1341</v>
       </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2" ht="15.75" customHeight="1">
+      <c r="B21" s="52">
+        <v>0</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="15.75" customHeight="1">
       <c r="A22" t="s">
         <v>1342</v>
       </c>
-      <c r="B22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2" ht="15.75" customHeight="1">
+      <c r="B22" s="52">
+        <v>0</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="15.75" customHeight="1">
       <c r="A23" t="s">
         <v>1343</v>
       </c>
-      <c r="B23">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2" ht="15.75" customHeight="1">
+      <c r="B23" s="52">
+        <v>1</v>
+      </c>
+      <c r="C23" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3" ht="15.75" customHeight="1">
       <c r="A24" t="s">
         <v>1344</v>
       </c>
-      <c r="B24">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2" ht="15.75" customHeight="1">
+      <c r="B24" s="52">
+        <v>1</v>
+      </c>
+      <c r="C24" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" ht="15.75" customHeight="1">
       <c r="A25" t="s">
         <v>1345</v>
       </c>
-      <c r="B25">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2" ht="15.75" customHeight="1">
+      <c r="B25" s="52">
+        <v>1</v>
+      </c>
+      <c r="C25" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="15.75" customHeight="1">
       <c r="A26" t="s">
         <v>1346</v>
       </c>
-      <c r="B26">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2" ht="15.75" customHeight="1">
+      <c r="B26" s="52">
+        <v>1</v>
+      </c>
+      <c r="C26" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" ht="15.75" customHeight="1">
       <c r="A27" t="s">
         <v>1347</v>
       </c>
-      <c r="B27">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2" ht="15.75" customHeight="1">
+      <c r="B27" s="52">
+        <v>0</v>
+      </c>
+      <c r="C27" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" ht="15.75" customHeight="1">
       <c r="A28" t="s">
         <v>1349</v>
       </c>
-      <c r="B28">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2" ht="15.75" customHeight="1">
+      <c r="B28" s="52">
+        <v>1</v>
+      </c>
+      <c r="C28" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" ht="15.75" customHeight="1">
       <c r="A29" t="s">
         <v>1350</v>
       </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2" ht="15.75" customHeight="1">
+      <c r="B29" s="52">
+        <v>1</v>
+      </c>
+      <c r="C29" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" ht="15.75" customHeight="1">
       <c r="A30" t="s">
         <v>1351</v>
       </c>
-      <c r="B30">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2" ht="15.75" customHeight="1">
+      <c r="B30" s="52">
+        <v>1</v>
+      </c>
+      <c r="C30" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" ht="15.75" customHeight="1">
       <c r="A31" t="s">
         <v>1352</v>
       </c>
-      <c r="B31">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2" ht="15.75" customHeight="1">
+      <c r="B31" s="52">
+        <v>1</v>
+      </c>
+      <c r="C31" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="15.75" customHeight="1">
       <c r="A32" t="s">
         <v>1353</v>
       </c>
-      <c r="B32">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B32" s="52">
+        <v>1</v>
+      </c>
+      <c r="C32" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" ht="15.75" customHeight="1">
       <c r="A33" t="s">
         <v>1354</v>
       </c>
-      <c r="B33">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B33" s="52">
+        <v>0</v>
+      </c>
+      <c r="C33" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" ht="15.75" customHeight="1">
       <c r="A34" t="s">
         <v>1600</v>
       </c>
-      <c r="B34">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B34" s="52">
+        <v>0</v>
+      </c>
+      <c r="C34" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" ht="15.75" customHeight="1">
       <c r="A35" t="s">
         <v>1599</v>
       </c>
-      <c r="B35">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B35" s="52">
+        <v>0</v>
+      </c>
+      <c r="C35" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" ht="15.75" customHeight="1">
       <c r="A36" t="s">
         <v>1598</v>
       </c>
-      <c r="B36">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B36" s="52">
+        <v>1</v>
+      </c>
+      <c r="C36" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" ht="15.75" customHeight="1">
       <c r="A37" t="s">
         <v>1355</v>
       </c>
-      <c r="B37">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B37" s="52">
+        <v>1</v>
+      </c>
+      <c r="C37" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" ht="15.75" customHeight="1">
       <c r="A38" t="s">
         <v>1356</v>
       </c>
-      <c r="B38">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B38" s="52">
+        <v>0</v>
+      </c>
+      <c r="C38" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" ht="15.75" customHeight="1">
       <c r="A39" t="s">
         <v>1357</v>
       </c>
-      <c r="B39">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B39" s="52">
+        <v>1</v>
+      </c>
+      <c r="C39" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" ht="15.75" customHeight="1">
       <c r="A40" t="s">
         <v>1358</v>
       </c>
-      <c r="B40">
-        <v>1</v>
-      </c>
-      <c r="C40" t="s">
+      <c r="B40" s="52">
+        <v>1</v>
+      </c>
+      <c r="C40" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D40" t="s">
         <v>1652</v>
       </c>
     </row>
-    <row r="41" spans="1:3" ht="15.75" customHeight="1">
+    <row r="41" spans="1:4" ht="15.75" customHeight="1">
       <c r="A41" s="44" t="s">
         <v>1369</v>
       </c>
-      <c r="B41">
-        <v>1</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="B41" s="52">
+        <v>1</v>
+      </c>
+      <c r="C41" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D41" t="s">
         <v>1651</v>
       </c>
     </row>
-    <row r="42" spans="1:3" ht="15.75" customHeight="1">
+    <row r="42" spans="1:4" ht="15.75" customHeight="1">
       <c r="A42" t="s">
         <v>1386</v>
       </c>
-      <c r="B42">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B42" s="52">
+        <v>0</v>
+      </c>
+      <c r="C42" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" ht="15.75" customHeight="1">
       <c r="A43" s="46" t="s">
         <v>1412</v>
       </c>
-      <c r="B43">
-        <v>1</v>
-      </c>
-      <c r="C43" s="46" t="s">
+      <c r="B43" s="52">
+        <v>1</v>
+      </c>
+      <c r="C43" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D43" s="46" t="s">
         <v>1413</v>
       </c>
     </row>
-    <row r="44" spans="1:3" ht="15.75" customHeight="1">
+    <row r="44" spans="1:4" ht="15.75" customHeight="1">
       <c r="A44" t="s">
         <v>1476</v>
       </c>
-      <c r="B44">
+      <c r="B44" s="52">
         <v>0.2</v>
       </c>
-      <c r="C44" t="s">
+      <c r="C44" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D44" t="s">
         <v>1486</v>
       </c>
     </row>
-    <row r="45" spans="1:3" ht="15.75" customHeight="1">
+    <row r="45" spans="1:4" ht="15.75" customHeight="1">
       <c r="A45" t="s">
         <v>1485</v>
       </c>
-      <c r="B45">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B45" s="52">
+        <v>1</v>
+      </c>
+      <c r="C45" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" ht="15.75" customHeight="1">
       <c r="A46" t="s">
         <v>1494</v>
       </c>
-      <c r="B46">
-        <v>1</v>
-      </c>
-      <c r="C46" t="s">
+      <c r="B46" s="52">
+        <v>1</v>
+      </c>
+      <c r="C46" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D46" t="s">
         <v>1495</v>
       </c>
     </row>
-    <row r="47" spans="1:3" ht="15.75" customHeight="1">
+    <row r="47" spans="1:4" ht="15.75" customHeight="1">
       <c r="A47" t="s">
         <v>1506</v>
       </c>
-      <c r="B47">
+      <c r="B47" s="52">
         <v>0.6</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C47" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D47" t="s">
         <v>1507</v>
       </c>
     </row>
-    <row r="48" spans="1:3" ht="15.75" customHeight="1">
+    <row r="48" spans="1:4" ht="15.75" customHeight="1">
       <c r="A48" t="s">
         <v>1508</v>
       </c>
-      <c r="B48">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B48" s="52">
+        <v>0</v>
+      </c>
+      <c r="C48" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" ht="15.75" customHeight="1">
       <c r="A49" t="s">
         <v>1539</v>
       </c>
-      <c r="B49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="15.75" customHeight="1">
+      <c r="B49" s="52">
+        <v>1</v>
+      </c>
+      <c r="C49" s="52" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" ht="15.75" customHeight="1">
       <c r="A50" t="s">
         <v>1604</v>
       </c>
-      <c r="B50">
+      <c r="B50" s="52">
         <v>10</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C50" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D50" t="s">
         <v>1486</v>
       </c>
     </row>
-    <row r="51" spans="1:3" ht="15.75" customHeight="1">
+    <row r="51" spans="1:4" ht="15.75" customHeight="1">
       <c r="A51" t="s">
         <v>1606</v>
       </c>
-      <c r="B51">
+      <c r="B51" s="52">
         <v>4</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C51" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D51" t="s">
         <v>1650</v>
       </c>
     </row>
-    <row r="52" spans="1:3" ht="15.75" customHeight="1">
+    <row r="52" spans="1:4" ht="15.75" customHeight="1">
       <c r="A52" t="s">
         <v>1616</v>
       </c>
-      <c r="B52">
-        <v>1</v>
-      </c>
-      <c r="C52" t="s">
+      <c r="B52" s="52">
+        <v>1</v>
+      </c>
+      <c r="C52" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D52" t="s">
         <v>1647</v>
       </c>
     </row>
-    <row r="53" spans="1:3" ht="15.75" customHeight="1">
+    <row r="53" spans="1:4" ht="15.75" customHeight="1">
       <c r="A53" t="s">
         <v>1617</v>
       </c>
-      <c r="B53">
+      <c r="B53" s="52">
         <v>0.5</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C53" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D53" t="s">
         <v>1648</v>
       </c>
     </row>
-    <row r="54" spans="1:3" ht="15.75" customHeight="1">
+    <row r="54" spans="1:4" ht="15.75" customHeight="1">
       <c r="A54" t="s">
         <v>1641</v>
       </c>
-      <c r="B54">
-        <v>1</v>
-      </c>
-      <c r="C54" t="s">
+      <c r="B54" s="52">
+        <v>1</v>
+      </c>
+      <c r="C54" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D54" t="s">
         <v>1649</v>
       </c>
     </row>
-    <row r="55" spans="1:3" ht="15.75" customHeight="1">
+    <row r="55" spans="1:4" ht="15.75" customHeight="1">
       <c r="A55" t="s">
         <v>1653</v>
       </c>
-      <c r="B55">
-        <v>1</v>
-      </c>
-      <c r="C55" t="s">
+      <c r="B55" s="52">
+        <v>1</v>
+      </c>
+      <c r="C55" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D55" t="s">
         <v>1654</v>
       </c>
     </row>
-    <row r="56" spans="1:3" ht="15.75" customHeight="1">
+    <row r="56" spans="1:4" ht="15.75" customHeight="1">
       <c r="A56" t="s">
         <v>1656</v>
       </c>
-      <c r="B56">
-        <v>1</v>
-      </c>
-      <c r="C56" t="s">
+      <c r="B56" s="52">
+        <v>1</v>
+      </c>
+      <c r="C56" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D56" t="s">
         <v>1657</v>
       </c>
     </row>
-    <row r="57" spans="1:3" ht="15.75" customHeight="1">
+    <row r="57" spans="1:4" ht="15.75" customHeight="1">
       <c r="A57" t="s">
         <v>1664</v>
       </c>
-      <c r="B57">
-        <v>1</v>
-      </c>
-      <c r="C57" t="s">
+      <c r="B57" s="52">
+        <v>1</v>
+      </c>
+      <c r="C57" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D57" t="s">
         <v>1683</v>
       </c>
     </row>
-    <row r="58" spans="1:3" ht="15.75" customHeight="1">
+    <row r="58" spans="1:4" ht="15.75" customHeight="1">
       <c r="A58" t="s">
         <v>1684</v>
       </c>
-      <c r="B58">
+      <c r="B58" s="52">
         <v>3</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C58" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D58" t="s">
         <v>1686</v>
       </c>
     </row>
-    <row r="59" spans="1:3" ht="15.75" customHeight="1">
+    <row r="59" spans="1:4" ht="15.75" customHeight="1">
       <c r="A59" t="s">
         <v>1685</v>
       </c>
-      <c r="B59">
+      <c r="B59" s="52">
         <v>5</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C59" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D59" t="s">
         <v>1686</v>
       </c>
     </row>
-    <row r="60" spans="1:3" ht="15.75" customHeight="1">
+    <row r="60" spans="1:4" ht="15.75" customHeight="1">
       <c r="A60" t="s">
         <v>1687</v>
       </c>
-      <c r="B60">
+      <c r="B60" s="52">
         <v>3</v>
       </c>
-      <c r="C60" t="s">
+      <c r="C60" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D60" t="s">
         <v>1689</v>
       </c>
     </row>
-    <row r="61" spans="1:3" ht="15.75" customHeight="1">
+    <row r="61" spans="1:4" ht="15.75" customHeight="1">
       <c r="A61" t="s">
         <v>1688</v>
       </c>
-      <c r="B61">
+      <c r="B61" s="52">
         <v>5</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C61" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D61" t="s">
         <v>1690</v>
       </c>
     </row>
-    <row r="62" spans="1:3" ht="15.75" customHeight="1">
+    <row r="62" spans="1:4" ht="15.75" customHeight="1">
       <c r="A62" t="s">
         <v>1691</v>
       </c>
-      <c r="B62">
-        <v>1</v>
-      </c>
-      <c r="C62" t="s">
+      <c r="B62" s="52">
+        <v>1</v>
+      </c>
+      <c r="C62" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D62" t="s">
         <v>1692</v>
       </c>
     </row>
-    <row r="63" spans="1:3" ht="15.75" customHeight="1">
+    <row r="63" spans="1:4" ht="15.75" customHeight="1">
       <c r="A63" t="s">
         <v>1700</v>
       </c>
-      <c r="B63">
-        <v>1</v>
-      </c>
-      <c r="C63" t="s">
+      <c r="B63" s="52">
+        <v>1</v>
+      </c>
+      <c r="C63" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D63" t="s">
         <v>1701</v>
       </c>
     </row>
-    <row r="64" spans="1:3" ht="15.75" customHeight="1">
+    <row r="64" spans="1:4" ht="15.75" customHeight="1">
       <c r="A64" t="s">
         <v>1721</v>
       </c>
-      <c r="B64">
-        <v>0</v>
-      </c>
-      <c r="C64" t="s">
+      <c r="B64" s="52">
+        <v>0</v>
+      </c>
+      <c r="C64" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D64" t="s">
         <v>1722</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A65" t="s">
+        <v>1759</v>
+      </c>
+      <c r="B65" s="52">
+        <v>0</v>
+      </c>
+      <c r="C65" s="52" t="s">
+        <v>1760</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" ht="15.75" customHeight="1">
+      <c r="A66" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B66" s="52">
+        <v>0</v>
+      </c>
+      <c r="C66" s="52" t="s">
+        <v>1762</v>
       </c>
     </row>
   </sheetData>
@@ -43167,7 +43403,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4267B9-6C50-42DE-8EEA-ACDE778B1226}">
-  <dimension ref="A1:U27"/>
+  <dimension ref="A1:U28"/>
   <sheetFormatPr defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="15.26953125" customWidth="1"/>
@@ -44929,6 +45165,71 @@
         <v>11</v>
       </c>
       <c r="U27" t="s">
+        <v>1666</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21">
+      <c r="A28" s="44" t="s">
+        <v>1757</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28">
+        <v>0</v>
+      </c>
+      <c r="E28">
+        <v>0</v>
+      </c>
+      <c r="F28">
+        <v>0</v>
+      </c>
+      <c r="G28">
+        <v>0</v>
+      </c>
+      <c r="H28">
+        <v>0</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>0</v>
+      </c>
+      <c r="L28">
+        <v>0</v>
+      </c>
+      <c r="M28">
+        <v>0</v>
+      </c>
+      <c r="N28">
+        <v>10</v>
+      </c>
+      <c r="O28" s="44" t="s">
+        <v>1376</v>
+      </c>
+      <c r="P28">
+        <v>0</v>
+      </c>
+      <c r="Q28">
+        <v>1</v>
+      </c>
+      <c r="R28" s="44" t="s">
+        <v>1182</v>
+      </c>
+      <c r="S28" t="s">
+        <v>36</v>
+      </c>
+      <c r="T28">
+        <v>11</v>
+      </c>
+      <c r="U28" t="s">
         <v>1666</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{035DFDBD-0B29-46B3-AA16-C890F967BB98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E9E52B-F9B8-4C6B-A8AB-60962AAA0F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -43820,7 +43820,7 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G7">
         <v>0</v>
@@ -43885,7 +43885,7 @@
         <v>0</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G8">
         <v>0</v>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68E9E52B-F9B8-4C6B-A8AB-60962AAA0F64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1551AF7-9234-486F-A507-FF22A2870B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="6" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -33047,7 +33047,7 @@
   <cols>
     <col min="1" max="1" width="11.90625" customWidth="1"/>
     <col min="2" max="2" width="12.81640625" customWidth="1"/>
-    <col min="3" max="3" width="14.54296875" customWidth="1"/>
+    <col min="3" max="3" width="25.453125" customWidth="1"/>
     <col min="4" max="4" width="20.90625" customWidth="1"/>
     <col min="5" max="5" width="26.453125" customWidth="1"/>
     <col min="6" max="6" width="15.81640625" customWidth="1"/>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1551AF7-9234-486F-A507-FF22A2870B77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2870ABA-567D-4703-9535-B7F3FD4811B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="6" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,7 +184,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7735" uniqueCount="1763">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7567" uniqueCount="1760">
   <si>
     <t>NAME</t>
   </si>
@@ -3795,51 +3795,27 @@
     <t>daily_chest1</t>
   </si>
   <si>
-    <t>gold,400</t>
-  </si>
-  <si>
     <t>have_item,daily_point,40,&gt;=</t>
   </si>
   <si>
-    <t>gem,150</t>
-  </si>
-  <si>
     <t>daily_chest2</t>
   </si>
   <si>
-    <t>gold,401</t>
-  </si>
-  <si>
     <t>have_item,daily_point,60,&gt;=</t>
   </si>
   <si>
-    <t>gem,151</t>
-  </si>
-  <si>
     <t>daily_chest3</t>
   </si>
   <si>
-    <t>gold,402</t>
-  </si>
-  <si>
     <t>have_item,daily_point,80,&gt;=</t>
   </si>
   <si>
-    <t>gem,152</t>
-  </si>
-  <si>
     <t>daily_chest4</t>
   </si>
   <si>
-    <t>gold,403</t>
-  </si>
-  <si>
     <t>have_item,daily_point,100,&gt;=</t>
   </si>
   <si>
-    <t>gem,153</t>
-  </si>
-  <si>
     <t>TYPE</t>
   </si>
   <si>
@@ -5376,9 +5352,6 @@
     <t>weekly_point</t>
   </si>
   <si>
-    <t>gold,0</t>
-  </si>
-  <si>
     <t>task1_test</t>
   </si>
   <si>
@@ -5473,6 +5446,24 @@
   </si>
   <si>
     <t>gold,{level}*10#wood,{level}</t>
+  </si>
+  <si>
+    <t>daily_point,20#gold,0</t>
+  </si>
+  <si>
+    <t>gold,200#gem,50</t>
+  </si>
+  <si>
+    <t>gold,400#gem,150</t>
+  </si>
+  <si>
+    <t>gold,401#gem,151</t>
+  </si>
+  <si>
+    <t>gold,402#gem,152</t>
+  </si>
+  <si>
+    <t>gold,403#gem,153</t>
   </si>
 </sst>
 </file>
@@ -6129,25 +6120,25 @@
         <v>10</v>
       </c>
       <c r="J1" s="49" t="s">
-        <v>1605</v>
+        <v>1597</v>
       </c>
       <c r="K1" s="49" t="s">
-        <v>1663</v>
+        <v>1655</v>
       </c>
       <c r="L1" s="49" t="s">
         <v>11</v>
       </c>
       <c r="M1" s="49" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="N1" s="49" t="s">
-        <v>1537</v>
+        <v>1529</v>
       </c>
       <c r="O1" s="49" t="s">
-        <v>1596</v>
+        <v>1588</v>
       </c>
       <c r="P1" s="49" t="s">
-        <v>1597</v>
+        <v>1589</v>
       </c>
       <c r="Q1" s="49" t="s">
         <v>12</v>
@@ -6204,46 +6195,46 @@
         <v>29</v>
       </c>
       <c r="AI1" s="6" t="s">
-        <v>1368</v>
+        <v>1360</v>
       </c>
       <c r="AJ1" s="6" t="s">
-        <v>1410</v>
+        <v>1402</v>
       </c>
       <c r="AK1" s="6" t="s">
+        <v>1599</v>
+      </c>
+      <c r="AL1" s="6" t="s">
+        <v>1600</v>
+      </c>
+      <c r="AM1" s="6" t="s">
+        <v>1603</v>
+      </c>
+      <c r="AN1" s="6" t="s">
+        <v>1604</v>
+      </c>
+      <c r="AO1" s="6" t="s">
+        <v>1605</v>
+      </c>
+      <c r="AP1" s="6" t="s">
+        <v>1606</v>
+      </c>
+      <c r="AQ1" s="6" t="s">
         <v>1607</v>
       </c>
-      <c r="AL1" s="6" t="s">
-        <v>1608</v>
-      </c>
-      <c r="AM1" s="6" t="s">
-        <v>1611</v>
-      </c>
-      <c r="AN1" s="6" t="s">
-        <v>1612</v>
-      </c>
-      <c r="AO1" s="6" t="s">
-        <v>1613</v>
-      </c>
-      <c r="AP1" s="6" t="s">
-        <v>1614</v>
-      </c>
-      <c r="AQ1" s="6" t="s">
-        <v>1615</v>
-      </c>
       <c r="AR1" s="6" t="s">
-        <v>1626</v>
+        <v>1618</v>
       </c>
       <c r="AS1" s="6" t="s">
-        <v>1630</v>
+        <v>1622</v>
       </c>
       <c r="AT1" s="6" t="s">
-        <v>1708</v>
+        <v>1700</v>
       </c>
       <c r="AU1" s="6" t="s">
-        <v>1720</v>
+        <v>1712</v>
       </c>
       <c r="AV1" s="6" t="s">
-        <v>1723</v>
+        <v>1715</v>
       </c>
     </row>
     <row r="2" spans="1:48" ht="12.5">
@@ -6305,7 +6296,7 @@
         <v>33</v>
       </c>
       <c r="T2" s="40" t="s">
-        <v>1695</v>
+        <v>1687</v>
       </c>
       <c r="U2" s="40" t="s">
         <v>42</v>
@@ -6353,7 +6344,7 @@
         <v>3</v>
       </c>
       <c r="AJ2" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK2">
         <v>0</v>
@@ -6394,7 +6385,7 @@
     </row>
     <row r="3" spans="1:48" ht="12.5">
       <c r="A3" s="47" t="s">
-        <v>1414</v>
+        <v>1406</v>
       </c>
       <c r="B3" s="48">
         <v>1</v>
@@ -6499,7 +6490,7 @@
         <v>3</v>
       </c>
       <c r="AJ3" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK3">
         <v>0</v>
@@ -6540,7 +6531,7 @@
     </row>
     <row r="4" spans="1:48" ht="12.5">
       <c r="A4" s="47" t="s">
-        <v>1415</v>
+        <v>1407</v>
       </c>
       <c r="B4" s="48">
         <v>1</v>
@@ -6645,7 +6636,7 @@
         <v>3</v>
       </c>
       <c r="AJ4" s="46" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="AK4">
         <v>0</v>
@@ -6686,7 +6677,7 @@
     </row>
     <row r="5" spans="1:48" ht="12.5">
       <c r="A5" s="47" t="s">
-        <v>1416</v>
+        <v>1408</v>
       </c>
       <c r="B5" s="48">
         <v>1</v>
@@ -6791,7 +6782,7 @@
         <v>3</v>
       </c>
       <c r="AJ5" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -6832,7 +6823,7 @@
     </row>
     <row r="6" spans="1:48" ht="12.5">
       <c r="A6" s="47" t="s">
-        <v>1474</v>
+        <v>1466</v>
       </c>
       <c r="B6" s="48">
         <v>1</v>
@@ -6892,7 +6883,7 @@
         <v>36</v>
       </c>
       <c r="U6" s="40" t="s">
-        <v>1477</v>
+        <v>1469</v>
       </c>
       <c r="V6" s="40" t="s">
         <v>36</v>
@@ -6937,7 +6928,7 @@
         <v>3</v>
       </c>
       <c r="AJ6" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK6">
         <v>0</v>
@@ -6978,7 +6969,7 @@
     </row>
     <row r="7" spans="1:48" ht="12.5">
       <c r="A7" s="47" t="s">
-        <v>1475</v>
+        <v>1467</v>
       </c>
       <c r="B7" s="48">
         <v>1</v>
@@ -7035,7 +7026,7 @@
         <v>33</v>
       </c>
       <c r="T7" s="40" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="U7" s="40" t="s">
         <v>35</v>
@@ -7083,7 +7074,7 @@
         <v>3</v>
       </c>
       <c r="AJ7" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK7">
         <v>0</v>
@@ -7184,7 +7175,7 @@
         <v>36</v>
       </c>
       <c r="U8" s="40" t="s">
-        <v>1493</v>
+        <v>1485</v>
       </c>
       <c r="V8" s="40" t="s">
         <v>36</v>
@@ -7229,7 +7220,7 @@
         <v>3</v>
       </c>
       <c r="AJ8" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK8">
         <v>0</v>
@@ -7270,7 +7261,7 @@
     </row>
     <row r="9" spans="1:48" ht="12.5">
       <c r="A9" s="47" t="s">
-        <v>1517</v>
+        <v>1509</v>
       </c>
       <c r="B9" s="48">
         <v>1</v>
@@ -7375,7 +7366,7 @@
         <v>3</v>
       </c>
       <c r="AJ9" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK9">
         <v>0</v>
@@ -7416,7 +7407,7 @@
     </row>
     <row r="10" spans="1:48" ht="12.5">
       <c r="A10" s="47" t="s">
-        <v>1518</v>
+        <v>1510</v>
       </c>
       <c r="B10" s="48">
         <v>1</v>
@@ -7521,7 +7512,7 @@
         <v>3</v>
       </c>
       <c r="AJ10" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK10">
         <v>0</v>
@@ -7562,7 +7553,7 @@
     </row>
     <row r="11" spans="1:48" ht="12.5">
       <c r="A11" s="47" t="s">
-        <v>1529</v>
+        <v>1521</v>
       </c>
       <c r="B11" s="48">
         <v>1</v>
@@ -7667,7 +7658,7 @@
         <v>3</v>
       </c>
       <c r="AJ11" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK11">
         <v>0</v>
@@ -7708,7 +7699,7 @@
     </row>
     <row r="12" spans="1:48" ht="12.5">
       <c r="A12" s="47" t="s">
-        <v>1530</v>
+        <v>1522</v>
       </c>
       <c r="B12" s="48">
         <v>1</v>
@@ -7813,7 +7804,7 @@
         <v>3</v>
       </c>
       <c r="AJ12" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK12">
         <v>0</v>
@@ -7854,7 +7845,7 @@
     </row>
     <row r="13" spans="1:48" ht="12.5">
       <c r="A13" s="47" t="s">
-        <v>1558</v>
+        <v>1550</v>
       </c>
       <c r="B13" s="48">
         <v>1</v>
@@ -7959,7 +7950,7 @@
         <v>3</v>
       </c>
       <c r="AJ13" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK13">
         <v>0</v>
@@ -8000,7 +7991,7 @@
     </row>
     <row r="14" spans="1:48" ht="12.5">
       <c r="A14" s="47" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="B14" s="48">
         <v>1</v>
@@ -8057,7 +8048,7 @@
         <v>33</v>
       </c>
       <c r="T14" s="40" t="s">
-        <v>1603</v>
+        <v>1595</v>
       </c>
       <c r="U14" s="40" t="s">
         <v>42</v>
@@ -8105,7 +8096,7 @@
         <v>3</v>
       </c>
       <c r="AJ14" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK14">
         <v>0</v>
@@ -8146,7 +8137,7 @@
     </row>
     <row r="15" spans="1:48" ht="12.5">
       <c r="A15" s="47" t="s">
-        <v>1609</v>
+        <v>1601</v>
       </c>
       <c r="B15" s="48">
         <v>1</v>
@@ -8251,7 +8242,7 @@
         <v>3</v>
       </c>
       <c r="AJ15" s="46" t="s">
-        <v>1704</v>
+        <v>1696</v>
       </c>
       <c r="AK15">
         <v>1</v>
@@ -8349,7 +8340,7 @@
         <v>33</v>
       </c>
       <c r="T16" s="40" t="s">
-        <v>1610</v>
+        <v>1602</v>
       </c>
       <c r="U16" s="40" t="s">
         <v>35</v>
@@ -8397,7 +8388,7 @@
         <v>3</v>
       </c>
       <c r="AJ16" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK16">
         <v>1</v>
@@ -8438,7 +8429,7 @@
     </row>
     <row r="17" spans="1:48" ht="12.5">
       <c r="A17" s="47" t="s">
-        <v>1378</v>
+        <v>1370</v>
       </c>
       <c r="B17" s="48">
         <v>1</v>
@@ -8543,7 +8534,7 @@
         <v>3</v>
       </c>
       <c r="AJ17" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK17">
         <v>1</v>
@@ -8689,7 +8680,7 @@
         <v>3</v>
       </c>
       <c r="AJ18" t="s">
-        <v>1725</v>
+        <v>1717</v>
       </c>
       <c r="AK18">
         <v>1</v>
@@ -8710,7 +8701,7 @@
         <v>0</v>
       </c>
       <c r="AQ18" t="s">
-        <v>1725</v>
+        <v>1717</v>
       </c>
       <c r="AR18" t="s">
         <v>36</v>
@@ -8730,7 +8721,7 @@
     </row>
     <row r="19" spans="1:48" ht="12.5">
       <c r="A19" s="47" t="s">
-        <v>1627</v>
+        <v>1619</v>
       </c>
       <c r="B19" s="48">
         <v>1</v>
@@ -8835,7 +8826,7 @@
         <v>3</v>
       </c>
       <c r="AJ19" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK19">
         <v>1</v>
@@ -8859,7 +8850,7 @@
         <v>36</v>
       </c>
       <c r="AR19" t="s">
-        <v>1628</v>
+        <v>1620</v>
       </c>
       <c r="AS19" t="s">
         <v>36</v>
@@ -8876,7 +8867,7 @@
     </row>
     <row r="20" spans="1:48" ht="12.5">
       <c r="A20" s="47" t="s">
-        <v>1640</v>
+        <v>1632</v>
       </c>
       <c r="B20" s="48">
         <v>1</v>
@@ -8981,7 +8972,7 @@
         <v>3</v>
       </c>
       <c r="AJ20" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK20">
         <v>1</v>
@@ -9022,7 +9013,7 @@
     </row>
     <row r="21" spans="1:48" ht="12.5">
       <c r="A21" s="47" t="s">
-        <v>1266</v>
+        <v>1258</v>
       </c>
       <c r="B21" s="48">
         <v>1</v>
@@ -9127,7 +9118,7 @@
         <v>3</v>
       </c>
       <c r="AJ21" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK21">
         <v>1</v>
@@ -9157,7 +9148,7 @@
         <v>36</v>
       </c>
       <c r="AT21" t="s">
-        <v>1709</v>
+        <v>1701</v>
       </c>
       <c r="AU21">
         <v>1</v>
@@ -9168,7 +9159,7 @@
     </row>
     <row r="22" spans="1:48" ht="12.5">
       <c r="A22" s="47" t="s">
-        <v>1724</v>
+        <v>1716</v>
       </c>
       <c r="B22" s="48">
         <v>1</v>
@@ -9273,7 +9264,7 @@
         <v>3</v>
       </c>
       <c r="AJ22" t="s">
-        <v>1726</v>
+        <v>1718</v>
       </c>
       <c r="AK22">
         <v>1</v>
@@ -9294,7 +9285,7 @@
         <v>0</v>
       </c>
       <c r="AQ22" t="s">
-        <v>1726</v>
+        <v>1718</v>
       </c>
       <c r="AR22" t="s">
         <v>36</v>
@@ -9314,7 +9305,7 @@
     </row>
     <row r="23" spans="1:48" ht="12.5">
       <c r="A23" s="47" t="s">
-        <v>1745</v>
+        <v>1736</v>
       </c>
       <c r="B23" s="48">
         <v>1</v>
@@ -9371,7 +9362,7 @@
         <v>33</v>
       </c>
       <c r="T23" s="40" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="U23" s="40" t="s">
         <v>35</v>
@@ -9419,7 +9410,7 @@
         <v>3</v>
       </c>
       <c r="AJ23" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK23">
         <v>0</v>
@@ -9460,7 +9451,7 @@
     </row>
     <row r="24" spans="1:48" ht="12.5">
       <c r="A24" s="47" t="s">
-        <v>1746</v>
+        <v>1737</v>
       </c>
       <c r="B24" s="48">
         <v>1</v>
@@ -9517,7 +9508,7 @@
         <v>33</v>
       </c>
       <c r="T24" s="40" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="U24" s="40" t="s">
         <v>35</v>
@@ -9565,7 +9556,7 @@
         <v>3</v>
       </c>
       <c r="AJ24" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK24">
         <v>0</v>
@@ -9606,7 +9597,7 @@
     </row>
     <row r="25" spans="1:48" ht="12.5">
       <c r="A25" s="47" t="s">
-        <v>1748</v>
+        <v>1739</v>
       </c>
       <c r="B25" s="48">
         <v>1</v>
@@ -9663,7 +9654,7 @@
         <v>33</v>
       </c>
       <c r="T25" s="40" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="U25" s="40" t="s">
         <v>35</v>
@@ -9711,7 +9702,7 @@
         <v>3</v>
       </c>
       <c r="AJ25" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK25">
         <v>0</v>
@@ -9752,7 +9743,7 @@
     </row>
     <row r="26" spans="1:48" ht="12.5">
       <c r="A26" s="47" t="s">
-        <v>1747</v>
+        <v>1738</v>
       </c>
       <c r="B26" s="48">
         <v>1</v>
@@ -9809,7 +9800,7 @@
         <v>33</v>
       </c>
       <c r="T26" s="40" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="U26" s="40" t="s">
         <v>35</v>
@@ -9857,7 +9848,7 @@
         <v>3</v>
       </c>
       <c r="AJ26" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK26">
         <v>0</v>
@@ -9955,7 +9946,7 @@
         <v>33</v>
       </c>
       <c r="T27" s="40" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="U27" s="40" t="s">
         <v>35</v>
@@ -10003,7 +9994,7 @@
         <v>3</v>
       </c>
       <c r="AJ27" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK27">
         <v>0</v>
@@ -10044,7 +10035,7 @@
     </row>
     <row r="28" spans="1:48" ht="12.5">
       <c r="A28" s="47" t="s">
-        <v>1737</v>
+        <v>1728</v>
       </c>
       <c r="B28" s="48">
         <v>1</v>
@@ -10101,7 +10092,7 @@
         <v>33</v>
       </c>
       <c r="T28" s="40" t="s">
-        <v>1603</v>
+        <v>1595</v>
       </c>
       <c r="U28" s="40" t="s">
         <v>42</v>
@@ -10149,7 +10140,7 @@
         <v>3</v>
       </c>
       <c r="AJ28" s="46" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="AK28">
         <v>0</v>
@@ -23965,13 +23956,13 @@
         <v>881</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>1220</v>
+        <v>1212</v>
       </c>
       <c r="H1" s="6" t="s">
-        <v>1468</v>
+        <v>1460</v>
       </c>
       <c r="I1" s="6" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>882</v>
@@ -23989,7 +23980,7 @@
         <v>886</v>
       </c>
       <c r="O1" s="6" t="s">
-        <v>1538</v>
+        <v>1530</v>
       </c>
       <c r="P1" s="6" t="s">
         <v>887</v>
@@ -24033,7 +24024,7 @@
         <v>30</v>
       </c>
       <c r="J2" s="50" t="s">
-        <v>1521</v>
+        <v>1513</v>
       </c>
       <c r="K2" s="7" t="s">
         <v>36</v>
@@ -24092,7 +24083,7 @@
         <v>40</v>
       </c>
       <c r="J3" s="50" t="s">
-        <v>1417</v>
+        <v>1409</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>36</v>
@@ -24151,7 +24142,7 @@
         <v>50</v>
       </c>
       <c r="J4" s="50" t="s">
-        <v>1418</v>
+        <v>1410</v>
       </c>
       <c r="K4" s="7" t="s">
         <v>36</v>
@@ -24539,7 +24530,7 @@
     </row>
     <row r="13" spans="1:19" ht="12.5">
       <c r="A13" s="4" t="s">
-        <v>1697</v>
+        <v>1689</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>892</v>
@@ -24566,7 +24557,7 @@
         <v>30</v>
       </c>
       <c r="J13" s="50" t="s">
-        <v>1521</v>
+        <v>1513</v>
       </c>
       <c r="K13" s="7" t="s">
         <v>36</v>
@@ -24619,7 +24610,7 @@
     </row>
     <row r="15" spans="1:19" ht="12.5">
       <c r="A15" s="4" t="s">
-        <v>1699</v>
+        <v>1691</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>892</v>
@@ -24646,7 +24637,7 @@
         <v>30</v>
       </c>
       <c r="J15" s="50" t="s">
-        <v>1698</v>
+        <v>1690</v>
       </c>
       <c r="K15" s="7" t="s">
         <v>36</v>
@@ -29572,7 +29563,7 @@
         <v>1100</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1662</v>
+        <v>1654</v>
       </c>
     </row>
     <row r="2" spans="1:10">
@@ -29644,10 +29635,10 @@
         <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>1639</v>
+        <v>1631</v>
       </c>
       <c r="C4" t="s">
-        <v>1638</v>
+        <v>1630</v>
       </c>
       <c r="D4" t="s">
         <v>36</v>
@@ -29676,10 +29667,10 @@
         <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>1642</v>
+        <v>1634</v>
       </c>
       <c r="C5" t="s">
-        <v>1643</v>
+        <v>1635</v>
       </c>
       <c r="D5" t="s">
         <v>36</v>
@@ -29708,13 +29699,13 @@
         <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>1646</v>
+        <v>1638</v>
       </c>
       <c r="C6" t="s">
-        <v>1645</v>
+        <v>1637</v>
       </c>
       <c r="D6" t="s">
-        <v>1659</v>
+        <v>1651</v>
       </c>
       <c r="E6" t="s">
         <v>36</v>
@@ -29729,7 +29720,7 @@
         <v>36</v>
       </c>
       <c r="I6" t="s">
-        <v>1660</v>
+        <v>1652</v>
       </c>
       <c r="J6" t="s">
         <v>953</v>
@@ -31245,10 +31236,10 @@
         <v>84</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>1758</v>
+        <v>1749</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>1265</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="12.5">
@@ -31407,7 +31398,7 @@
     </row>
     <row r="16" spans="1:4" ht="15.75" customHeight="1">
       <c r="A16" t="s">
-        <v>1348</v>
+        <v>1340</v>
       </c>
       <c r="B16" s="52">
         <v>1</v>
@@ -31429,7 +31420,7 @@
     </row>
     <row r="18" spans="1:3" ht="15.75" customHeight="1">
       <c r="A18" t="s">
-        <v>1338</v>
+        <v>1330</v>
       </c>
       <c r="B18" s="52">
         <v>1</v>
@@ -31440,7 +31431,7 @@
     </row>
     <row r="19" spans="1:3" ht="15.75" customHeight="1">
       <c r="A19" t="s">
-        <v>1339</v>
+        <v>1331</v>
       </c>
       <c r="B19" s="52">
         <v>1</v>
@@ -31451,7 +31442,7 @@
     </row>
     <row r="20" spans="1:3" ht="15.75" customHeight="1">
       <c r="A20" t="s">
-        <v>1340</v>
+        <v>1332</v>
       </c>
       <c r="B20" s="52">
         <v>0</v>
@@ -31462,7 +31453,7 @@
     </row>
     <row r="21" spans="1:3" ht="15.75" customHeight="1">
       <c r="A21" t="s">
-        <v>1341</v>
+        <v>1333</v>
       </c>
       <c r="B21" s="52">
         <v>0</v>
@@ -31473,7 +31464,7 @@
     </row>
     <row r="22" spans="1:3" ht="15.75" customHeight="1">
       <c r="A22" t="s">
-        <v>1342</v>
+        <v>1334</v>
       </c>
       <c r="B22" s="52">
         <v>0</v>
@@ -31484,7 +31475,7 @@
     </row>
     <row r="23" spans="1:3" ht="15.75" customHeight="1">
       <c r="A23" t="s">
-        <v>1343</v>
+        <v>1335</v>
       </c>
       <c r="B23" s="52">
         <v>1</v>
@@ -31495,7 +31486,7 @@
     </row>
     <row r="24" spans="1:3" ht="15.75" customHeight="1">
       <c r="A24" t="s">
-        <v>1344</v>
+        <v>1336</v>
       </c>
       <c r="B24" s="52">
         <v>1</v>
@@ -31506,7 +31497,7 @@
     </row>
     <row r="25" spans="1:3" ht="15.75" customHeight="1">
       <c r="A25" t="s">
-        <v>1345</v>
+        <v>1337</v>
       </c>
       <c r="B25" s="52">
         <v>1</v>
@@ -31517,7 +31508,7 @@
     </row>
     <row r="26" spans="1:3" ht="15.75" customHeight="1">
       <c r="A26" t="s">
-        <v>1346</v>
+        <v>1338</v>
       </c>
       <c r="B26" s="52">
         <v>1</v>
@@ -31528,7 +31519,7 @@
     </row>
     <row r="27" spans="1:3" ht="15.75" customHeight="1">
       <c r="A27" t="s">
-        <v>1347</v>
+        <v>1339</v>
       </c>
       <c r="B27" s="52">
         <v>0</v>
@@ -31539,7 +31530,7 @@
     </row>
     <row r="28" spans="1:3" ht="15.75" customHeight="1">
       <c r="A28" t="s">
-        <v>1349</v>
+        <v>1341</v>
       </c>
       <c r="B28" s="52">
         <v>1</v>
@@ -31550,7 +31541,7 @@
     </row>
     <row r="29" spans="1:3" ht="15.75" customHeight="1">
       <c r="A29" t="s">
-        <v>1350</v>
+        <v>1342</v>
       </c>
       <c r="B29" s="52">
         <v>1</v>
@@ -31561,7 +31552,7 @@
     </row>
     <row r="30" spans="1:3" ht="15.75" customHeight="1">
       <c r="A30" t="s">
-        <v>1351</v>
+        <v>1343</v>
       </c>
       <c r="B30" s="52">
         <v>1</v>
@@ -31572,7 +31563,7 @@
     </row>
     <row r="31" spans="1:3" ht="15.75" customHeight="1">
       <c r="A31" t="s">
-        <v>1352</v>
+        <v>1344</v>
       </c>
       <c r="B31" s="52">
         <v>1</v>
@@ -31583,7 +31574,7 @@
     </row>
     <row r="32" spans="1:3" ht="15.75" customHeight="1">
       <c r="A32" t="s">
-        <v>1353</v>
+        <v>1345</v>
       </c>
       <c r="B32" s="52">
         <v>1</v>
@@ -31594,7 +31585,7 @@
     </row>
     <row r="33" spans="1:4" ht="15.75" customHeight="1">
       <c r="A33" t="s">
-        <v>1354</v>
+        <v>1346</v>
       </c>
       <c r="B33" s="52">
         <v>0</v>
@@ -31605,7 +31596,7 @@
     </row>
     <row r="34" spans="1:4" ht="15.75" customHeight="1">
       <c r="A34" t="s">
-        <v>1600</v>
+        <v>1592</v>
       </c>
       <c r="B34" s="52">
         <v>0</v>
@@ -31616,7 +31607,7 @@
     </row>
     <row r="35" spans="1:4" ht="15.75" customHeight="1">
       <c r="A35" t="s">
-        <v>1599</v>
+        <v>1591</v>
       </c>
       <c r="B35" s="52">
         <v>0</v>
@@ -31627,7 +31618,7 @@
     </row>
     <row r="36" spans="1:4" ht="15.75" customHeight="1">
       <c r="A36" t="s">
-        <v>1598</v>
+        <v>1590</v>
       </c>
       <c r="B36" s="52">
         <v>1</v>
@@ -31638,7 +31629,7 @@
     </row>
     <row r="37" spans="1:4" ht="15.75" customHeight="1">
       <c r="A37" t="s">
-        <v>1355</v>
+        <v>1347</v>
       </c>
       <c r="B37" s="52">
         <v>1</v>
@@ -31649,7 +31640,7 @@
     </row>
     <row r="38" spans="1:4" ht="15.75" customHeight="1">
       <c r="A38" t="s">
-        <v>1356</v>
+        <v>1348</v>
       </c>
       <c r="B38" s="52">
         <v>0</v>
@@ -31660,7 +31651,7 @@
     </row>
     <row r="39" spans="1:4" ht="15.75" customHeight="1">
       <c r="A39" t="s">
-        <v>1357</v>
+        <v>1349</v>
       </c>
       <c r="B39" s="52">
         <v>1</v>
@@ -31671,7 +31662,7 @@
     </row>
     <row r="40" spans="1:4" ht="15.75" customHeight="1">
       <c r="A40" t="s">
-        <v>1358</v>
+        <v>1350</v>
       </c>
       <c r="B40" s="52">
         <v>1</v>
@@ -31680,12 +31671,12 @@
         <v>36</v>
       </c>
       <c r="D40" t="s">
-        <v>1652</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="15.75" customHeight="1">
       <c r="A41" s="44" t="s">
-        <v>1369</v>
+        <v>1361</v>
       </c>
       <c r="B41" s="52">
         <v>1</v>
@@ -31694,12 +31685,12 @@
         <v>36</v>
       </c>
       <c r="D41" t="s">
-        <v>1651</v>
+        <v>1643</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="15.75" customHeight="1">
       <c r="A42" t="s">
-        <v>1386</v>
+        <v>1378</v>
       </c>
       <c r="B42" s="52">
         <v>0</v>
@@ -31710,7 +31701,7 @@
     </row>
     <row r="43" spans="1:4" ht="15.75" customHeight="1">
       <c r="A43" s="46" t="s">
-        <v>1412</v>
+        <v>1404</v>
       </c>
       <c r="B43" s="52">
         <v>1</v>
@@ -31719,12 +31710,12 @@
         <v>36</v>
       </c>
       <c r="D43" s="46" t="s">
-        <v>1413</v>
+        <v>1405</v>
       </c>
     </row>
     <row r="44" spans="1:4" ht="15.75" customHeight="1">
       <c r="A44" t="s">
-        <v>1476</v>
+        <v>1468</v>
       </c>
       <c r="B44" s="52">
         <v>0.2</v>
@@ -31733,12 +31724,12 @@
         <v>36</v>
       </c>
       <c r="D44" t="s">
-        <v>1486</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="15.75" customHeight="1">
       <c r="A45" t="s">
-        <v>1485</v>
+        <v>1477</v>
       </c>
       <c r="B45" s="52">
         <v>1</v>
@@ -31749,7 +31740,7 @@
     </row>
     <row r="46" spans="1:4" ht="15.75" customHeight="1">
       <c r="A46" t="s">
-        <v>1494</v>
+        <v>1486</v>
       </c>
       <c r="B46" s="52">
         <v>1</v>
@@ -31758,12 +31749,12 @@
         <v>36</v>
       </c>
       <c r="D46" t="s">
-        <v>1495</v>
+        <v>1487</v>
       </c>
     </row>
     <row r="47" spans="1:4" ht="15.75" customHeight="1">
       <c r="A47" t="s">
-        <v>1506</v>
+        <v>1498</v>
       </c>
       <c r="B47" s="52">
         <v>0.6</v>
@@ -31772,12 +31763,12 @@
         <v>36</v>
       </c>
       <c r="D47" t="s">
-        <v>1507</v>
+        <v>1499</v>
       </c>
     </row>
     <row r="48" spans="1:4" ht="15.75" customHeight="1">
       <c r="A48" t="s">
-        <v>1508</v>
+        <v>1500</v>
       </c>
       <c r="B48" s="52">
         <v>0</v>
@@ -31788,7 +31779,7 @@
     </row>
     <row r="49" spans="1:4" ht="15.75" customHeight="1">
       <c r="A49" t="s">
-        <v>1539</v>
+        <v>1531</v>
       </c>
       <c r="B49" s="52">
         <v>1</v>
@@ -31799,7 +31790,7 @@
     </row>
     <row r="50" spans="1:4" ht="15.75" customHeight="1">
       <c r="A50" t="s">
-        <v>1604</v>
+        <v>1596</v>
       </c>
       <c r="B50" s="52">
         <v>10</v>
@@ -31808,12 +31799,12 @@
         <v>36</v>
       </c>
       <c r="D50" t="s">
-        <v>1486</v>
+        <v>1478</v>
       </c>
     </row>
     <row r="51" spans="1:4" ht="15.75" customHeight="1">
       <c r="A51" t="s">
-        <v>1606</v>
+        <v>1598</v>
       </c>
       <c r="B51" s="52">
         <v>4</v>
@@ -31822,12 +31813,12 @@
         <v>36</v>
       </c>
       <c r="D51" t="s">
-        <v>1650</v>
+        <v>1642</v>
       </c>
     </row>
     <row r="52" spans="1:4" ht="15.75" customHeight="1">
       <c r="A52" t="s">
-        <v>1616</v>
+        <v>1608</v>
       </c>
       <c r="B52" s="52">
         <v>1</v>
@@ -31836,12 +31827,12 @@
         <v>36</v>
       </c>
       <c r="D52" t="s">
-        <v>1647</v>
+        <v>1639</v>
       </c>
     </row>
     <row r="53" spans="1:4" ht="15.75" customHeight="1">
       <c r="A53" t="s">
-        <v>1617</v>
+        <v>1609</v>
       </c>
       <c r="B53" s="52">
         <v>0.5</v>
@@ -31850,26 +31841,26 @@
         <v>36</v>
       </c>
       <c r="D53" t="s">
-        <v>1648</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="54" spans="1:4" ht="15.75" customHeight="1">
       <c r="A54" t="s">
+        <v>1633</v>
+      </c>
+      <c r="B54" s="52">
+        <v>1</v>
+      </c>
+      <c r="C54" s="52" t="s">
+        <v>36</v>
+      </c>
+      <c r="D54" t="s">
         <v>1641</v>
-      </c>
-      <c r="B54" s="52">
-        <v>1</v>
-      </c>
-      <c r="C54" s="52" t="s">
-        <v>36</v>
-      </c>
-      <c r="D54" t="s">
-        <v>1649</v>
       </c>
     </row>
     <row r="55" spans="1:4" ht="15.75" customHeight="1">
       <c r="A55" t="s">
-        <v>1653</v>
+        <v>1645</v>
       </c>
       <c r="B55" s="52">
         <v>1</v>
@@ -31878,12 +31869,12 @@
         <v>36</v>
       </c>
       <c r="D55" t="s">
-        <v>1654</v>
+        <v>1646</v>
       </c>
     </row>
     <row r="56" spans="1:4" ht="15.75" customHeight="1">
       <c r="A56" t="s">
-        <v>1656</v>
+        <v>1648</v>
       </c>
       <c r="B56" s="52">
         <v>1</v>
@@ -31892,12 +31883,12 @@
         <v>36</v>
       </c>
       <c r="D56" t="s">
-        <v>1657</v>
+        <v>1649</v>
       </c>
     </row>
     <row r="57" spans="1:4" ht="15.75" customHeight="1">
       <c r="A57" t="s">
-        <v>1664</v>
+        <v>1656</v>
       </c>
       <c r="B57" s="52">
         <v>1</v>
@@ -31906,12 +31897,12 @@
         <v>36</v>
       </c>
       <c r="D57" t="s">
-        <v>1683</v>
+        <v>1675</v>
       </c>
     </row>
     <row r="58" spans="1:4" ht="15.75" customHeight="1">
       <c r="A58" t="s">
-        <v>1684</v>
+        <v>1676</v>
       </c>
       <c r="B58" s="52">
         <v>3</v>
@@ -31920,12 +31911,12 @@
         <v>36</v>
       </c>
       <c r="D58" t="s">
-        <v>1686</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="59" spans="1:4" ht="15.75" customHeight="1">
       <c r="A59" t="s">
-        <v>1685</v>
+        <v>1677</v>
       </c>
       <c r="B59" s="52">
         <v>5</v>
@@ -31934,12 +31925,12 @@
         <v>36</v>
       </c>
       <c r="D59" t="s">
-        <v>1686</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="60" spans="1:4" ht="15.75" customHeight="1">
       <c r="A60" t="s">
-        <v>1687</v>
+        <v>1679</v>
       </c>
       <c r="B60" s="52">
         <v>3</v>
@@ -31948,12 +31939,12 @@
         <v>36</v>
       </c>
       <c r="D60" t="s">
-        <v>1689</v>
+        <v>1681</v>
       </c>
     </row>
     <row r="61" spans="1:4" ht="15.75" customHeight="1">
       <c r="A61" t="s">
-        <v>1688</v>
+        <v>1680</v>
       </c>
       <c r="B61" s="52">
         <v>5</v>
@@ -31962,12 +31953,12 @@
         <v>36</v>
       </c>
       <c r="D61" t="s">
-        <v>1690</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="62" spans="1:4" ht="15.75" customHeight="1">
       <c r="A62" t="s">
-        <v>1691</v>
+        <v>1683</v>
       </c>
       <c r="B62" s="52">
         <v>1</v>
@@ -31976,12 +31967,12 @@
         <v>36</v>
       </c>
       <c r="D62" t="s">
-        <v>1692</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="63" spans="1:4" ht="15.75" customHeight="1">
       <c r="A63" t="s">
-        <v>1700</v>
+        <v>1692</v>
       </c>
       <c r="B63" s="52">
         <v>1</v>
@@ -31990,12 +31981,12 @@
         <v>36</v>
       </c>
       <c r="D63" t="s">
-        <v>1701</v>
+        <v>1693</v>
       </c>
     </row>
     <row r="64" spans="1:4" ht="15.75" customHeight="1">
       <c r="A64" t="s">
-        <v>1721</v>
+        <v>1713</v>
       </c>
       <c r="B64" s="52">
         <v>0</v>
@@ -32004,29 +31995,29 @@
         <v>36</v>
       </c>
       <c r="D64" t="s">
-        <v>1722</v>
+        <v>1714</v>
       </c>
     </row>
     <row r="65" spans="1:3" ht="15.75" customHeight="1">
       <c r="A65" t="s">
-        <v>1759</v>
+        <v>1750</v>
       </c>
       <c r="B65" s="52">
         <v>0</v>
       </c>
       <c r="C65" s="52" t="s">
-        <v>1760</v>
+        <v>1751</v>
       </c>
     </row>
     <row r="66" spans="1:3" ht="15.75" customHeight="1">
       <c r="A66" t="s">
-        <v>1761</v>
+        <v>1752</v>
       </c>
       <c r="B66" s="52">
         <v>0</v>
       </c>
       <c r="C66" s="52" t="s">
-        <v>1762</v>
+        <v>1753</v>
       </c>
     </row>
   </sheetData>
@@ -32531,7 +32522,7 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" t="s">
-        <v>1519</v>
+        <v>1511</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -32546,7 +32537,7 @@
         <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>1515</v>
+        <v>1507</v>
       </c>
       <c r="G31">
         <v>0</v>
@@ -32554,7 +32545,7 @@
     </row>
     <row r="33" spans="1:7">
       <c r="A33" t="s">
-        <v>1520</v>
+        <v>1512</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -32569,7 +32560,7 @@
         <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>1516</v>
+        <v>1508</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -32577,7 +32568,7 @@
     </row>
     <row r="35" spans="1:7">
       <c r="A35" t="s">
-        <v>1636</v>
+        <v>1628</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -32592,7 +32583,7 @@
         <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>1633</v>
+        <v>1625</v>
       </c>
       <c r="G35">
         <v>0</v>
@@ -32600,7 +32591,7 @@
     </row>
     <row r="37" spans="1:7">
       <c r="A37" t="s">
-        <v>1704</v>
+        <v>1696</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -32615,7 +32606,7 @@
         <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>1705</v>
+        <v>1697</v>
       </c>
       <c r="G37">
         <v>0</v>
@@ -32623,7 +32614,7 @@
     </row>
     <row r="39" spans="1:7">
       <c r="A39" t="s">
-        <v>1725</v>
+        <v>1717</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -32646,7 +32637,7 @@
     </row>
     <row r="41" spans="1:7">
       <c r="A41" t="s">
-        <v>1726</v>
+        <v>1718</v>
       </c>
       <c r="B41">
         <v>0</v>
@@ -32661,7 +32652,7 @@
         <v>1</v>
       </c>
       <c r="F41" t="s">
-        <v>1727</v>
+        <v>1719</v>
       </c>
       <c r="G41">
         <v>0</v>
@@ -32669,7 +32660,7 @@
     </row>
     <row r="43" spans="1:7">
       <c r="A43" t="s">
-        <v>1741</v>
+        <v>1732</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -32730,7 +32721,7 @@
         <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>1380</v>
+        <v>1372</v>
       </c>
       <c r="G45">
         <v>0</v>
@@ -32753,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>1379</v>
+        <v>1371</v>
       </c>
       <c r="G46">
         <v>0</v>
@@ -32761,7 +32752,7 @@
     </row>
     <row r="48" spans="1:7">
       <c r="A48" t="s">
-        <v>1742</v>
+        <v>1733</v>
       </c>
       <c r="B48">
         <v>0</v>
@@ -32776,7 +32767,7 @@
         <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>1375</v>
+        <v>1367</v>
       </c>
       <c r="G48">
         <v>0</v>
@@ -32799,7 +32790,7 @@
         <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>1374</v>
+        <v>1366</v>
       </c>
       <c r="G49">
         <v>0</v>
@@ -32822,7 +32813,7 @@
         <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>1228</v>
+        <v>1220</v>
       </c>
       <c r="G50">
         <v>0</v>
@@ -32845,7 +32836,7 @@
         <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
       <c r="G51">
         <v>0</v>
@@ -32853,7 +32844,7 @@
     </row>
     <row r="53" spans="1:7">
       <c r="A53" t="s">
-        <v>1744</v>
+        <v>1735</v>
       </c>
       <c r="B53">
         <v>0</v>
@@ -32868,7 +32859,7 @@
         <v>1</v>
       </c>
       <c r="F53" t="s">
-        <v>1748</v>
+        <v>1739</v>
       </c>
       <c r="G53">
         <v>0</v>
@@ -32891,7 +32882,7 @@
         <v>1</v>
       </c>
       <c r="F54" t="s">
-        <v>1745</v>
+        <v>1736</v>
       </c>
       <c r="G54">
         <v>0</v>
@@ -32914,7 +32905,7 @@
         <v>1</v>
       </c>
       <c r="F55" t="s">
-        <v>1746</v>
+        <v>1737</v>
       </c>
       <c r="G55">
         <v>0</v>
@@ -32937,7 +32928,7 @@
         <v>1</v>
       </c>
       <c r="F56" t="s">
-        <v>1747</v>
+        <v>1738</v>
       </c>
       <c r="G56">
         <v>0</v>
@@ -33042,7 +33033,7 @@
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-1400-000000000000}">
-  <dimension ref="A1:S36"/>
+  <dimension ref="A1:S15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.5"/>
   <cols>
     <col min="1" max="1" width="11.90625" customWidth="1"/>
@@ -33116,13 +33107,13 @@
         <v>1182</v>
       </c>
       <c r="C2" t="s">
-        <v>1187</v>
+        <v>1754</v>
       </c>
       <c r="D2" t="s">
         <v>36</v>
       </c>
       <c r="E2" t="s">
-        <v>1385</v>
+        <v>1377</v>
       </c>
       <c r="F2" t="s">
         <v>36</v>
@@ -33154,19 +33145,19 @@
     </row>
     <row r="3" spans="1:19">
       <c r="A3" t="s">
-        <v>36</v>
+        <v>1722</v>
       </c>
       <c r="B3" t="s">
-        <v>36</v>
+        <v>1182</v>
       </c>
       <c r="C3" t="s">
-        <v>1730</v>
+        <v>1754</v>
       </c>
       <c r="D3" t="s">
         <v>36</v>
       </c>
       <c r="E3" t="s">
-        <v>36</v>
+        <v>1723</v>
       </c>
       <c r="F3" t="s">
         <v>36</v>
@@ -33175,10 +33166,10 @@
         <v>36</v>
       </c>
       <c r="H3" t="s">
-        <v>36</v>
+        <v>1184</v>
       </c>
       <c r="I3" t="s">
-        <v>36</v>
+        <v>1149</v>
       </c>
       <c r="J3" t="s">
         <v>36</v>
@@ -33186,31 +33177,31 @@
       <c r="K3" t="s">
         <v>36</v>
       </c>
-      <c r="L3" t="s">
-        <v>36</v>
+      <c r="L3">
+        <v>1</v>
       </c>
       <c r="M3" t="s">
         <v>36</v>
       </c>
-      <c r="N3" t="s">
-        <v>36</v>
+      <c r="N3" s="3" t="s">
+        <v>1025</v>
       </c>
     </row>
     <row r="4" spans="1:19">
       <c r="A4" t="s">
-        <v>1731</v>
+        <v>1724</v>
       </c>
       <c r="B4" t="s">
         <v>1182</v>
       </c>
       <c r="C4" t="s">
-        <v>1187</v>
+        <v>1754</v>
       </c>
       <c r="D4" t="s">
         <v>36</v>
       </c>
       <c r="E4" t="s">
-        <v>1732</v>
+        <v>1725</v>
       </c>
       <c r="F4" t="s">
         <v>36</v>
@@ -33240,109 +33231,21 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="5" spans="1:19">
-      <c r="A5" t="s">
-        <v>36</v>
-      </c>
-      <c r="B5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" t="s">
-        <v>1730</v>
-      </c>
-      <c r="D5" t="s">
-        <v>36</v>
-      </c>
-      <c r="E5" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" t="s">
-        <v>36</v>
-      </c>
-      <c r="H5" t="s">
-        <v>36</v>
-      </c>
-      <c r="I5" t="s">
-        <v>36</v>
-      </c>
-      <c r="J5" t="s">
-        <v>36</v>
-      </c>
-      <c r="K5" t="s">
-        <v>36</v>
-      </c>
-      <c r="L5" t="s">
-        <v>36</v>
-      </c>
-      <c r="M5" t="s">
-        <v>36</v>
-      </c>
-      <c r="N5" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
-      <c r="A6" t="s">
-        <v>1733</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C6" t="s">
-        <v>1187</v>
-      </c>
-      <c r="D6" t="s">
-        <v>36</v>
-      </c>
-      <c r="E6" t="s">
-        <v>1734</v>
-      </c>
-      <c r="F6" t="s">
-        <v>36</v>
-      </c>
-      <c r="G6" t="s">
-        <v>36</v>
-      </c>
-      <c r="H6" t="s">
-        <v>1184</v>
-      </c>
-      <c r="I6" t="s">
-        <v>1149</v>
-      </c>
-      <c r="J6" t="s">
-        <v>36</v>
-      </c>
-      <c r="K6" t="s">
-        <v>36</v>
-      </c>
-      <c r="L6">
-        <v>1</v>
-      </c>
-      <c r="M6" t="s">
-        <v>36</v>
-      </c>
-      <c r="N6" s="3" t="s">
-        <v>1025</v>
-      </c>
-    </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>1185</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>1186</v>
       </c>
       <c r="C7" t="s">
-        <v>1730</v>
+        <v>1187</v>
       </c>
       <c r="D7" t="s">
         <v>36</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
+        <v>1183</v>
       </c>
       <c r="F7" t="s">
         <v>36</v>
@@ -33351,10 +33254,10 @@
         <v>36</v>
       </c>
       <c r="H7" t="s">
-        <v>36</v>
+        <v>1188</v>
       </c>
       <c r="I7" t="s">
-        <v>36</v>
+        <v>1149</v>
       </c>
       <c r="J7" t="s">
         <v>36</v>
@@ -33362,31 +33265,163 @@
       <c r="K7" t="s">
         <v>36</v>
       </c>
-      <c r="L7" t="s">
-        <v>36</v>
+      <c r="L7">
+        <v>1</v>
       </c>
       <c r="M7" t="s">
         <v>36</v>
       </c>
-      <c r="N7" t="s">
-        <v>36</v>
+      <c r="N7" s="3" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
+      <c r="A8" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D8" t="s">
+        <v>36</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1191</v>
+      </c>
+      <c r="F8" t="s">
+        <v>36</v>
+      </c>
+      <c r="G8" t="s">
+        <v>36</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1192</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J8" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" t="s">
+        <v>36</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="M8" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" s="3" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
+      <c r="A9" t="s">
+        <v>1193</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D9" t="s">
+        <v>36</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1194</v>
+      </c>
+      <c r="F9" t="s">
+        <v>36</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1195</v>
+      </c>
+      <c r="I9" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J9" t="s">
+        <v>36</v>
+      </c>
+      <c r="K9" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9">
+        <v>1</v>
+      </c>
+      <c r="M9" t="s">
+        <v>36</v>
+      </c>
+      <c r="N9" s="3" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
+      <c r="A10" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1187</v>
+      </c>
+      <c r="D10" t="s">
+        <v>36</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1197</v>
+      </c>
+      <c r="F10" t="s">
+        <v>36</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I10" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J10" t="s">
+        <v>36</v>
+      </c>
+      <c r="K10" t="s">
+        <v>36</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="M10" t="s">
+        <v>36</v>
+      </c>
+      <c r="N10" s="3" t="s">
+        <v>1189</v>
       </c>
     </row>
     <row r="11" spans="1:19">
       <c r="A11" t="s">
-        <v>1185</v>
+        <v>1199</v>
       </c>
       <c r="B11" t="s">
         <v>1186</v>
       </c>
       <c r="C11" t="s">
-        <v>1187</v>
+        <v>1755</v>
       </c>
       <c r="D11" t="s">
         <v>36</v>
       </c>
       <c r="E11" t="s">
-        <v>1183</v>
+        <v>1200</v>
       </c>
       <c r="F11" t="s">
         <v>36</v>
@@ -33395,7 +33430,7 @@
         <v>36</v>
       </c>
       <c r="H11" t="s">
-        <v>1188</v>
+        <v>1198</v>
       </c>
       <c r="I11" t="s">
         <v>1149</v>
@@ -33418,19 +33453,19 @@
     </row>
     <row r="12" spans="1:19">
       <c r="A12" t="s">
-        <v>36</v>
+        <v>1202</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>1186</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>1756</v>
       </c>
       <c r="D12" t="s">
         <v>36</v>
       </c>
       <c r="E12" t="s">
-        <v>36</v>
+        <v>1203</v>
       </c>
       <c r="F12" t="s">
         <v>36</v>
@@ -33439,10 +33474,10 @@
         <v>36</v>
       </c>
       <c r="H12" t="s">
-        <v>36</v>
+        <v>1198</v>
       </c>
       <c r="I12" t="s">
-        <v>36</v>
+        <v>1149</v>
       </c>
       <c r="J12" t="s">
         <v>36</v>
@@ -33450,31 +33485,75 @@
       <c r="K12" t="s">
         <v>36</v>
       </c>
-      <c r="L12" t="s">
-        <v>36</v>
+      <c r="L12">
+        <v>1</v>
       </c>
       <c r="M12" t="s">
         <v>36</v>
       </c>
-      <c r="N12" t="s">
-        <v>36</v>
+      <c r="N12" s="3" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
+      <c r="A13" t="s">
+        <v>1204</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1757</v>
+      </c>
+      <c r="D13" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1205</v>
+      </c>
+      <c r="F13" t="s">
+        <v>36</v>
+      </c>
+      <c r="G13" t="s">
+        <v>36</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1198</v>
+      </c>
+      <c r="I13" t="s">
+        <v>1149</v>
+      </c>
+      <c r="J13" t="s">
+        <v>36</v>
+      </c>
+      <c r="K13" t="s">
+        <v>36</v>
+      </c>
+      <c r="L13">
+        <v>1</v>
+      </c>
+      <c r="M13" t="s">
+        <v>36</v>
+      </c>
+      <c r="N13" s="3" t="s">
+        <v>1189</v>
       </c>
     </row>
     <row r="14" spans="1:19">
       <c r="A14" t="s">
-        <v>1190</v>
+        <v>1206</v>
       </c>
       <c r="B14" t="s">
         <v>1186</v>
       </c>
       <c r="C14" t="s">
-        <v>1187</v>
+        <v>1758</v>
       </c>
       <c r="D14" t="s">
         <v>36</v>
       </c>
       <c r="E14" t="s">
-        <v>1191</v>
+        <v>1207</v>
       </c>
       <c r="F14" t="s">
         <v>36</v>
@@ -33483,7 +33562,7 @@
         <v>36</v>
       </c>
       <c r="H14" t="s">
-        <v>1192</v>
+        <v>1198</v>
       </c>
       <c r="I14" t="s">
         <v>1149</v>
@@ -33506,19 +33585,19 @@
     </row>
     <row r="15" spans="1:19">
       <c r="A15" t="s">
-        <v>36</v>
+        <v>1208</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>1186</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>1759</v>
       </c>
       <c r="D15" t="s">
         <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>1209</v>
       </c>
       <c r="F15" t="s">
         <v>36</v>
@@ -33527,10 +33606,10 @@
         <v>36</v>
       </c>
       <c r="H15" t="s">
-        <v>36</v>
+        <v>1198</v>
       </c>
       <c r="I15" t="s">
-        <v>36</v>
+        <v>1149</v>
       </c>
       <c r="J15" t="s">
         <v>36</v>
@@ -33538,630 +33617,14 @@
       <c r="K15" t="s">
         <v>36</v>
       </c>
-      <c r="L15" t="s">
-        <v>36</v>
+      <c r="L15">
+        <v>1</v>
       </c>
       <c r="M15" t="s">
         <v>36</v>
       </c>
-      <c r="N15" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
-      <c r="A17" t="s">
-        <v>1193</v>
-      </c>
-      <c r="B17" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C17" t="s">
-        <v>1187</v>
-      </c>
-      <c r="D17" t="s">
-        <v>36</v>
-      </c>
-      <c r="E17" t="s">
-        <v>1194</v>
-      </c>
-      <c r="F17" t="s">
-        <v>36</v>
-      </c>
-      <c r="G17" t="s">
-        <v>36</v>
-      </c>
-      <c r="H17" t="s">
-        <v>1195</v>
-      </c>
-      <c r="I17" t="s">
-        <v>1149</v>
-      </c>
-      <c r="J17" t="s">
-        <v>36</v>
-      </c>
-      <c r="K17" t="s">
-        <v>36</v>
-      </c>
-      <c r="L17">
-        <v>1</v>
-      </c>
-      <c r="M17" t="s">
-        <v>36</v>
-      </c>
-      <c r="N17" s="3" t="s">
+      <c r="N15" s="3" t="s">
         <v>1189</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
-      <c r="A18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B18" t="s">
-        <v>36</v>
-      </c>
-      <c r="C18" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" t="s">
-        <v>36</v>
-      </c>
-      <c r="E18" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" t="s">
-        <v>36</v>
-      </c>
-      <c r="G18" t="s">
-        <v>36</v>
-      </c>
-      <c r="H18" t="s">
-        <v>36</v>
-      </c>
-      <c r="I18" t="s">
-        <v>36</v>
-      </c>
-      <c r="J18" t="s">
-        <v>36</v>
-      </c>
-      <c r="K18" t="s">
-        <v>36</v>
-      </c>
-      <c r="L18" t="s">
-        <v>36</v>
-      </c>
-      <c r="M18" t="s">
-        <v>36</v>
-      </c>
-      <c r="N18" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
-      <c r="A20" t="s">
-        <v>1196</v>
-      </c>
-      <c r="B20" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C20" t="s">
-        <v>1187</v>
-      </c>
-      <c r="D20" t="s">
-        <v>36</v>
-      </c>
-      <c r="E20" t="s">
-        <v>1197</v>
-      </c>
-      <c r="F20" t="s">
-        <v>36</v>
-      </c>
-      <c r="G20" t="s">
-        <v>36</v>
-      </c>
-      <c r="H20" t="s">
-        <v>1198</v>
-      </c>
-      <c r="I20" t="s">
-        <v>1149</v>
-      </c>
-      <c r="J20" t="s">
-        <v>36</v>
-      </c>
-      <c r="K20" t="s">
-        <v>36</v>
-      </c>
-      <c r="L20">
-        <v>1</v>
-      </c>
-      <c r="M20" t="s">
-        <v>36</v>
-      </c>
-      <c r="N20" s="3" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
-      <c r="A21" t="s">
-        <v>36</v>
-      </c>
-      <c r="B21" t="s">
-        <v>36</v>
-      </c>
-      <c r="C21" t="s">
-        <v>36</v>
-      </c>
-      <c r="D21" t="s">
-        <v>36</v>
-      </c>
-      <c r="E21" t="s">
-        <v>36</v>
-      </c>
-      <c r="F21" t="s">
-        <v>36</v>
-      </c>
-      <c r="G21" t="s">
-        <v>36</v>
-      </c>
-      <c r="H21" t="s">
-        <v>36</v>
-      </c>
-      <c r="I21" t="s">
-        <v>36</v>
-      </c>
-      <c r="J21" t="s">
-        <v>36</v>
-      </c>
-      <c r="K21" t="s">
-        <v>36</v>
-      </c>
-      <c r="L21" t="s">
-        <v>36</v>
-      </c>
-      <c r="M21" t="s">
-        <v>36</v>
-      </c>
-      <c r="N21" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
-      <c r="A23" t="s">
-        <v>1199</v>
-      </c>
-      <c r="B23" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C23" t="s">
-        <v>1133</v>
-      </c>
-      <c r="D23" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" t="s">
-        <v>1200</v>
-      </c>
-      <c r="F23" t="s">
-        <v>36</v>
-      </c>
-      <c r="G23" t="s">
-        <v>36</v>
-      </c>
-      <c r="H23" t="s">
-        <v>1198</v>
-      </c>
-      <c r="I23" t="s">
-        <v>1149</v>
-      </c>
-      <c r="J23" t="s">
-        <v>36</v>
-      </c>
-      <c r="K23" t="s">
-        <v>36</v>
-      </c>
-      <c r="L23">
-        <v>1</v>
-      </c>
-      <c r="M23" t="s">
-        <v>36</v>
-      </c>
-      <c r="N23" s="3" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
-      <c r="A24" t="s">
-        <v>36</v>
-      </c>
-      <c r="B24" t="s">
-        <v>36</v>
-      </c>
-      <c r="C24" t="s">
-        <v>1201</v>
-      </c>
-      <c r="D24" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" t="s">
-        <v>36</v>
-      </c>
-      <c r="F24" t="s">
-        <v>36</v>
-      </c>
-      <c r="G24" t="s">
-        <v>36</v>
-      </c>
-      <c r="H24" t="s">
-        <v>36</v>
-      </c>
-      <c r="I24" t="s">
-        <v>36</v>
-      </c>
-      <c r="J24" t="s">
-        <v>36</v>
-      </c>
-      <c r="K24" t="s">
-        <v>36</v>
-      </c>
-      <c r="L24" t="s">
-        <v>36</v>
-      </c>
-      <c r="M24" t="s">
-        <v>36</v>
-      </c>
-      <c r="N24" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
-      <c r="A26" t="s">
-        <v>1202</v>
-      </c>
-      <c r="B26" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C26" t="s">
-        <v>1203</v>
-      </c>
-      <c r="D26" t="s">
-        <v>36</v>
-      </c>
-      <c r="E26" t="s">
-        <v>1204</v>
-      </c>
-      <c r="F26" t="s">
-        <v>36</v>
-      </c>
-      <c r="G26" t="s">
-        <v>36</v>
-      </c>
-      <c r="H26" t="s">
-        <v>1198</v>
-      </c>
-      <c r="I26" t="s">
-        <v>1149</v>
-      </c>
-      <c r="J26" t="s">
-        <v>36</v>
-      </c>
-      <c r="K26" t="s">
-        <v>36</v>
-      </c>
-      <c r="L26">
-        <v>1</v>
-      </c>
-      <c r="M26" t="s">
-        <v>36</v>
-      </c>
-      <c r="N26" s="3" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
-      <c r="A27" t="s">
-        <v>36</v>
-      </c>
-      <c r="B27" t="s">
-        <v>36</v>
-      </c>
-      <c r="C27" t="s">
-        <v>1205</v>
-      </c>
-      <c r="D27" t="s">
-        <v>36</v>
-      </c>
-      <c r="E27" t="s">
-        <v>36</v>
-      </c>
-      <c r="F27" t="s">
-        <v>36</v>
-      </c>
-      <c r="G27" t="s">
-        <v>36</v>
-      </c>
-      <c r="H27" t="s">
-        <v>36</v>
-      </c>
-      <c r="I27" t="s">
-        <v>36</v>
-      </c>
-      <c r="J27" t="s">
-        <v>36</v>
-      </c>
-      <c r="K27" t="s">
-        <v>36</v>
-      </c>
-      <c r="L27" t="s">
-        <v>36</v>
-      </c>
-      <c r="M27" t="s">
-        <v>36</v>
-      </c>
-      <c r="N27" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
-      <c r="A29" t="s">
-        <v>1206</v>
-      </c>
-      <c r="B29" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C29" t="s">
-        <v>1207</v>
-      </c>
-      <c r="D29" t="s">
-        <v>36</v>
-      </c>
-      <c r="E29" t="s">
-        <v>1208</v>
-      </c>
-      <c r="F29" t="s">
-        <v>36</v>
-      </c>
-      <c r="G29" t="s">
-        <v>36</v>
-      </c>
-      <c r="H29" t="s">
-        <v>1198</v>
-      </c>
-      <c r="I29" t="s">
-        <v>1149</v>
-      </c>
-      <c r="J29" t="s">
-        <v>36</v>
-      </c>
-      <c r="K29" t="s">
-        <v>36</v>
-      </c>
-      <c r="L29">
-        <v>1</v>
-      </c>
-      <c r="M29" t="s">
-        <v>36</v>
-      </c>
-      <c r="N29" s="3" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
-      <c r="A30" t="s">
-        <v>36</v>
-      </c>
-      <c r="B30" t="s">
-        <v>36</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1209</v>
-      </c>
-      <c r="D30" t="s">
-        <v>36</v>
-      </c>
-      <c r="E30" t="s">
-        <v>36</v>
-      </c>
-      <c r="F30" t="s">
-        <v>36</v>
-      </c>
-      <c r="G30" t="s">
-        <v>36</v>
-      </c>
-      <c r="H30" t="s">
-        <v>36</v>
-      </c>
-      <c r="I30" t="s">
-        <v>36</v>
-      </c>
-      <c r="J30" t="s">
-        <v>36</v>
-      </c>
-      <c r="K30" t="s">
-        <v>36</v>
-      </c>
-      <c r="L30" t="s">
-        <v>36</v>
-      </c>
-      <c r="M30" t="s">
-        <v>36</v>
-      </c>
-      <c r="N30" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
-      <c r="A32" t="s">
-        <v>1210</v>
-      </c>
-      <c r="B32" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C32" t="s">
-        <v>1211</v>
-      </c>
-      <c r="D32" t="s">
-        <v>36</v>
-      </c>
-      <c r="E32" t="s">
-        <v>1212</v>
-      </c>
-      <c r="F32" t="s">
-        <v>36</v>
-      </c>
-      <c r="G32" t="s">
-        <v>36</v>
-      </c>
-      <c r="H32" t="s">
-        <v>1198</v>
-      </c>
-      <c r="I32" t="s">
-        <v>1149</v>
-      </c>
-      <c r="J32" t="s">
-        <v>36</v>
-      </c>
-      <c r="K32" t="s">
-        <v>36</v>
-      </c>
-      <c r="L32">
-        <v>1</v>
-      </c>
-      <c r="M32" t="s">
-        <v>36</v>
-      </c>
-      <c r="N32" s="3" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
-      <c r="A33" t="s">
-        <v>36</v>
-      </c>
-      <c r="B33" t="s">
-        <v>36</v>
-      </c>
-      <c r="C33" t="s">
-        <v>1213</v>
-      </c>
-      <c r="D33" t="s">
-        <v>36</v>
-      </c>
-      <c r="E33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F33" t="s">
-        <v>36</v>
-      </c>
-      <c r="G33" t="s">
-        <v>36</v>
-      </c>
-      <c r="H33" t="s">
-        <v>36</v>
-      </c>
-      <c r="I33" t="s">
-        <v>36</v>
-      </c>
-      <c r="J33" t="s">
-        <v>36</v>
-      </c>
-      <c r="K33" t="s">
-        <v>36</v>
-      </c>
-      <c r="L33" t="s">
-        <v>36</v>
-      </c>
-      <c r="M33" t="s">
-        <v>36</v>
-      </c>
-      <c r="N33" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
-      <c r="A35" t="s">
-        <v>1214</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1215</v>
-      </c>
-      <c r="D35" t="s">
-        <v>36</v>
-      </c>
-      <c r="E35" t="s">
-        <v>1216</v>
-      </c>
-      <c r="F35" t="s">
-        <v>36</v>
-      </c>
-      <c r="G35" t="s">
-        <v>36</v>
-      </c>
-      <c r="H35" t="s">
-        <v>1198</v>
-      </c>
-      <c r="I35" t="s">
-        <v>1149</v>
-      </c>
-      <c r="J35" t="s">
-        <v>36</v>
-      </c>
-      <c r="K35" t="s">
-        <v>36</v>
-      </c>
-      <c r="L35">
-        <v>1</v>
-      </c>
-      <c r="M35" t="s">
-        <v>36</v>
-      </c>
-      <c r="N35" s="3" t="s">
-        <v>1189</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
-      <c r="A36" t="s">
-        <v>36</v>
-      </c>
-      <c r="B36" t="s">
-        <v>36</v>
-      </c>
-      <c r="C36" t="s">
-        <v>1217</v>
-      </c>
-      <c r="D36" t="s">
-        <v>36</v>
-      </c>
-      <c r="E36" t="s">
-        <v>36</v>
-      </c>
-      <c r="F36" t="s">
-        <v>36</v>
-      </c>
-      <c r="G36" t="s">
-        <v>36</v>
-      </c>
-      <c r="H36" t="s">
-        <v>36</v>
-      </c>
-      <c r="I36" t="s">
-        <v>36</v>
-      </c>
-      <c r="J36" t="s">
-        <v>36</v>
-      </c>
-      <c r="K36" t="s">
-        <v>36</v>
-      </c>
-      <c r="L36" t="s">
-        <v>36</v>
-      </c>
-      <c r="M36" t="s">
-        <v>36</v>
-      </c>
-      <c r="N36" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -34189,27 +33652,27 @@
         <v>1140</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1218</v>
+        <v>1210</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1219</v>
+        <v>1211</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1220</v>
+        <v>1212</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1221</v>
+        <v>1213</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1222</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="50.25" customHeight="1">
       <c r="A2" t="s">
-        <v>1223</v>
+        <v>1215</v>
       </c>
       <c r="B2" t="s">
-        <v>1224</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="20.25" customHeight="1">
@@ -34217,39 +33680,39 @@
         <v>1182</v>
       </c>
       <c r="B3" t="s">
-        <v>1225</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="24" customHeight="1">
       <c r="A4" t="s">
-        <v>1226</v>
+        <v>1218</v>
       </c>
       <c r="B4" t="s">
-        <v>1227</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="26" customHeight="1">
       <c r="A5" t="s">
-        <v>1464</v>
+        <v>1456</v>
       </c>
       <c r="B5" t="s">
-        <v>1756</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6" t="s">
-        <v>1465</v>
+        <v>1457</v>
       </c>
       <c r="B6" t="s">
-        <v>1557</v>
+        <v>1549</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" t="s">
-        <v>1549</v>
+        <v>1541</v>
       </c>
       <c r="B7" t="s">
-        <v>1542</v>
+        <v>1534</v>
       </c>
     </row>
   </sheetData>
@@ -34323,7 +33786,7 @@
         <v>1181</v>
       </c>
       <c r="B2" t="s">
-        <v>1228</v>
+        <v>1220</v>
       </c>
       <c r="C2" t="s">
         <v>896</v>
@@ -34341,10 +33804,10 @@
         <v>36</v>
       </c>
       <c r="H2" t="s">
-        <v>1229</v>
+        <v>1221</v>
       </c>
       <c r="I2" t="s">
-        <v>1230</v>
+        <v>1222</v>
       </c>
       <c r="J2" t="s">
         <v>36</v>
@@ -34367,10 +33830,10 @@
         <v>1185</v>
       </c>
       <c r="B4" t="s">
-        <v>1228</v>
+        <v>1220</v>
       </c>
       <c r="C4" t="s">
-        <v>1231</v>
+        <v>1223</v>
       </c>
       <c r="D4" t="s">
         <v>36</v>
@@ -34385,10 +33848,10 @@
         <v>36</v>
       </c>
       <c r="H4" t="s">
-        <v>1232</v>
+        <v>1224</v>
       </c>
       <c r="I4" t="s">
-        <v>1230</v>
+        <v>1222</v>
       </c>
       <c r="J4" t="s">
         <v>36</v>
@@ -34411,10 +33874,10 @@
         <v>1190</v>
       </c>
       <c r="B6" t="s">
-        <v>1228</v>
+        <v>1220</v>
       </c>
       <c r="C6" t="s">
-        <v>1233</v>
+        <v>1225</v>
       </c>
       <c r="D6" t="s">
         <v>36</v>
@@ -34429,10 +33892,10 @@
         <v>36</v>
       </c>
       <c r="H6" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
       <c r="I6" t="s">
-        <v>1230</v>
+        <v>1222</v>
       </c>
       <c r="J6" t="s">
         <v>36</v>
@@ -34455,10 +33918,10 @@
         <v>1193</v>
       </c>
       <c r="B8" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
       <c r="C8" t="s">
-        <v>1236</v>
+        <v>1228</v>
       </c>
       <c r="D8" t="s">
         <v>36</v>
@@ -34473,10 +33936,10 @@
         <v>36</v>
       </c>
       <c r="H8" t="s">
-        <v>1237</v>
+        <v>1229</v>
       </c>
       <c r="I8" t="s">
-        <v>1238</v>
+        <v>1230</v>
       </c>
       <c r="J8" t="s">
         <v>36</v>
@@ -34499,7 +33962,7 @@
         <v>1196</v>
       </c>
       <c r="B10" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
       <c r="C10" t="s">
         <v>916</v>
@@ -34517,10 +33980,10 @@
         <v>36</v>
       </c>
       <c r="H10" t="s">
-        <v>1239</v>
+        <v>1231</v>
       </c>
       <c r="I10" t="s">
-        <v>1238</v>
+        <v>1230</v>
       </c>
       <c r="J10" t="s">
         <v>36</v>
@@ -34543,7 +34006,7 @@
         <v>1199</v>
       </c>
       <c r="B12" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
       <c r="C12" t="s">
         <v>1133</v>
@@ -34561,10 +34024,10 @@
         <v>36</v>
       </c>
       <c r="H12" t="s">
-        <v>1240</v>
+        <v>1232</v>
       </c>
       <c r="I12" t="s">
-        <v>1238</v>
+        <v>1230</v>
       </c>
       <c r="J12" t="s">
         <v>36</v>
@@ -34631,16 +34094,16 @@
         <v>1202</v>
       </c>
       <c r="B15" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="C15" t="s">
-        <v>1242</v>
+        <v>1234</v>
       </c>
       <c r="D15" t="s">
         <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="F15" t="s">
         <v>36</v>
@@ -34649,7 +34112,7 @@
         <v>36</v>
       </c>
       <c r="H15" t="s">
-        <v>1243</v>
+        <v>1235</v>
       </c>
       <c r="I15" t="s">
         <v>36</v>
@@ -34672,19 +34135,19 @@
     </row>
     <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="B17" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="C17" t="s">
-        <v>1244</v>
+        <v>1236</v>
       </c>
       <c r="D17" t="s">
         <v>36</v>
       </c>
       <c r="E17" t="s">
-        <v>1208</v>
+        <v>1205</v>
       </c>
       <c r="F17" t="s">
         <v>36</v>
@@ -34693,7 +34156,7 @@
         <v>36</v>
       </c>
       <c r="H17" t="s">
-        <v>1245</v>
+        <v>1237</v>
       </c>
       <c r="I17" t="s">
         <v>36</v>
@@ -34716,19 +34179,19 @@
     </row>
     <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>1210</v>
+        <v>1206</v>
       </c>
       <c r="B19" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="C19" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
       <c r="D19" t="s">
         <v>36</v>
       </c>
       <c r="E19" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="F19" t="s">
         <v>36</v>
@@ -34737,7 +34200,7 @@
         <v>36</v>
       </c>
       <c r="H19" t="s">
-        <v>1247</v>
+        <v>1239</v>
       </c>
       <c r="I19" t="s">
         <v>36</v>
@@ -34760,19 +34223,19 @@
     </row>
     <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>1214</v>
+        <v>1208</v>
       </c>
       <c r="B21" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="C21" t="s">
-        <v>1248</v>
+        <v>1240</v>
       </c>
       <c r="D21" t="s">
         <v>36</v>
       </c>
       <c r="E21" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="F21" t="s">
         <v>36</v>
@@ -34781,7 +34244,7 @@
         <v>36</v>
       </c>
       <c r="H21" t="s">
-        <v>1247</v>
+        <v>1239</v>
       </c>
       <c r="I21" t="s">
         <v>36</v>
@@ -34804,19 +34267,19 @@
     </row>
     <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>1249</v>
+        <v>1241</v>
       </c>
       <c r="B23" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="C23" t="s">
-        <v>1250</v>
+        <v>1242</v>
       </c>
       <c r="D23" t="s">
         <v>36</v>
       </c>
       <c r="E23" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="F23" t="s">
         <v>36</v>
@@ -34825,7 +34288,7 @@
         <v>36</v>
       </c>
       <c r="H23" t="s">
-        <v>1247</v>
+        <v>1239</v>
       </c>
       <c r="I23" t="s">
         <v>36</v>
@@ -34848,19 +34311,19 @@
     </row>
     <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>1251</v>
+        <v>1243</v>
       </c>
       <c r="B25" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="C25" t="s">
-        <v>1252</v>
+        <v>1244</v>
       </c>
       <c r="D25" t="s">
         <v>36</v>
       </c>
       <c r="E25" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="F25" t="s">
         <v>36</v>
@@ -34869,7 +34332,7 @@
         <v>36</v>
       </c>
       <c r="H25" t="s">
-        <v>1247</v>
+        <v>1239</v>
       </c>
       <c r="I25" t="s">
         <v>36</v>
@@ -34892,19 +34355,19 @@
     </row>
     <row r="27" spans="1:14">
       <c r="A27" t="s">
-        <v>1253</v>
+        <v>1245</v>
       </c>
       <c r="B27" t="s">
-        <v>1241</v>
+        <v>1233</v>
       </c>
       <c r="C27" t="s">
-        <v>1254</v>
+        <v>1246</v>
       </c>
       <c r="D27" t="s">
         <v>36</v>
       </c>
       <c r="E27" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="F27" t="s">
         <v>36</v>
@@ -34913,7 +34376,7 @@
         <v>36</v>
       </c>
       <c r="H27" t="s">
-        <v>1247</v>
+        <v>1239</v>
       </c>
       <c r="I27" t="s">
         <v>36</v>
@@ -34967,60 +34430,60 @@
         <v>3</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1255</v>
+        <v>1247</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1256</v>
+        <v>1248</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1257</v>
+        <v>1249</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1258</v>
+        <v>1250</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1259</v>
+        <v>1251</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1260</v>
+        <v>1252</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1261</v>
+        <v>1253</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>1409</v>
+        <v>1401</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>1262</v>
+        <v>1254</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>172</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>1263</v>
+        <v>1255</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>1264</v>
+        <v>1256</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>1265</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="2" spans="1:15">
       <c r="A2" t="s">
-        <v>1266</v>
+        <v>1258</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="D2">
         <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>1268</v>
+        <v>1260</v>
       </c>
       <c r="F2">
         <v>12</v>
@@ -35029,10 +34492,10 @@
         <v>910</v>
       </c>
       <c r="H2" t="s">
-        <v>1269</v>
+        <v>1261</v>
       </c>
       <c r="I2" t="s">
-        <v>1270</v>
+        <v>1262</v>
       </c>
       <c r="J2" t="s">
         <v>1149</v>
@@ -35073,10 +34536,10 @@
         <v>917</v>
       </c>
       <c r="H3" t="s">
-        <v>1271</v>
+        <v>1263</v>
       </c>
       <c r="I3" t="s">
-        <v>1272</v>
+        <v>1264</v>
       </c>
       <c r="J3" t="s">
         <v>1151</v>
@@ -35096,7 +34559,7 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>1266</v>
+        <v>1258</v>
       </c>
       <c r="B5">
         <v>2</v>
@@ -35117,10 +34580,10 @@
         <v>1120</v>
       </c>
       <c r="H5" t="s">
-        <v>1273</v>
+        <v>1265</v>
       </c>
       <c r="I5" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="J5" t="s">
         <v>1149</v>
@@ -35140,19 +34603,19 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>1275</v>
+        <v>1267</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>1267</v>
+        <v>1259</v>
       </c>
       <c r="D7">
         <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>1268</v>
+        <v>1260</v>
       </c>
       <c r="F7">
         <v>12</v>
@@ -35161,10 +34624,10 @@
         <v>910</v>
       </c>
       <c r="H7" t="s">
-        <v>1269</v>
+        <v>1261</v>
       </c>
       <c r="I7" t="s">
-        <v>1276</v>
+        <v>1268</v>
       </c>
       <c r="J7" t="s">
         <v>1149</v>
@@ -35205,10 +34668,10 @@
         <v>917</v>
       </c>
       <c r="H8" t="s">
-        <v>1271</v>
+        <v>1263</v>
       </c>
       <c r="I8" t="s">
-        <v>1276</v>
+        <v>1268</v>
       </c>
       <c r="J8" t="s">
         <v>1151</v>
@@ -35228,7 +34691,7 @@
     </row>
     <row r="10" spans="1:15">
       <c r="A10" t="s">
-        <v>1275</v>
+        <v>1267</v>
       </c>
       <c r="B10">
         <v>2</v>
@@ -35249,13 +34712,13 @@
         <v>1120</v>
       </c>
       <c r="H10" t="s">
-        <v>1273</v>
+        <v>1265</v>
       </c>
       <c r="I10" t="s">
-        <v>1277</v>
+        <v>1269</v>
       </c>
       <c r="J10" t="s">
-        <v>1277</v>
+        <v>1269</v>
       </c>
       <c r="K10">
         <v>5</v>
@@ -35272,7 +34735,7 @@
     </row>
     <row r="12" spans="1:15">
       <c r="A12" t="s">
-        <v>1278</v>
+        <v>1270</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -35293,13 +34756,13 @@
         <v>910</v>
       </c>
       <c r="H12" t="s">
-        <v>1279</v>
+        <v>1271</v>
       </c>
       <c r="I12" t="s">
-        <v>1280</v>
+        <v>1272</v>
       </c>
       <c r="J12" t="s">
-        <v>1280</v>
+        <v>1272</v>
       </c>
       <c r="K12">
         <v>1</v>
@@ -35311,7 +34774,7 @@
         <v>36</v>
       </c>
       <c r="N12" t="s">
-        <v>1281</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="13" spans="1:15">
@@ -35337,13 +34800,13 @@
         <v>917</v>
       </c>
       <c r="H13" t="s">
-        <v>1282</v>
+        <v>1274</v>
       </c>
       <c r="I13" t="s">
-        <v>1283</v>
+        <v>1275</v>
       </c>
       <c r="J13" t="s">
-        <v>1283</v>
+        <v>1275</v>
       </c>
       <c r="K13">
         <v>1</v>
@@ -35381,13 +34844,13 @@
         <v>910</v>
       </c>
       <c r="H15" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="I15" t="s">
-        <v>1285</v>
+        <v>1277</v>
       </c>
       <c r="J15" t="s">
-        <v>1285</v>
+        <v>1277</v>
       </c>
       <c r="K15">
         <v>0</v>
@@ -35396,15 +34859,15 @@
         <v>36</v>
       </c>
       <c r="M15" t="s">
-        <v>1286</v>
+        <v>1278</v>
       </c>
       <c r="N15" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="17" spans="1:15">
       <c r="A17" t="s">
-        <v>1288</v>
+        <v>1280</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -35425,13 +34888,13 @@
         <v>910</v>
       </c>
       <c r="H17" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="I17" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
       <c r="J17" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
       <c r="K17">
         <v>0</v>
@@ -35440,15 +34903,15 @@
         <v>36</v>
       </c>
       <c r="M17" t="s">
-        <v>1290</v>
+        <v>1282</v>
       </c>
       <c r="N17" t="s">
-        <v>1291</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="19" spans="1:15">
       <c r="A19" t="s">
-        <v>1292</v>
+        <v>1284</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -35469,13 +34932,13 @@
         <v>910</v>
       </c>
       <c r="H19" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="I19" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
       <c r="J19" t="s">
-        <v>1293</v>
+        <v>1285</v>
       </c>
       <c r="K19">
         <v>0</v>
@@ -35484,15 +34947,15 @@
         <v>36</v>
       </c>
       <c r="M19" t="s">
-        <v>1294</v>
+        <v>1286</v>
       </c>
       <c r="N19" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="21" spans="1:15">
       <c r="A21" t="s">
-        <v>1295</v>
+        <v>1287</v>
       </c>
       <c r="B21">
         <v>1</v>
@@ -35513,13 +34976,13 @@
         <v>910</v>
       </c>
       <c r="H21" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="I21" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
       <c r="J21" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
       <c r="K21">
         <v>0</v>
@@ -35528,15 +34991,15 @@
         <v>36</v>
       </c>
       <c r="M21" t="s">
-        <v>1296</v>
+        <v>1288</v>
       </c>
       <c r="N21" t="s">
-        <v>1291</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="23" spans="1:15">
       <c r="A23" t="s">
-        <v>1297</v>
+        <v>1289</v>
       </c>
       <c r="B23">
         <v>1</v>
@@ -35557,13 +35020,13 @@
         <v>910</v>
       </c>
       <c r="H23" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="I23" t="s">
-        <v>1285</v>
+        <v>1277</v>
       </c>
       <c r="J23" t="s">
-        <v>1285</v>
+        <v>1277</v>
       </c>
       <c r="K23">
         <v>0</v>
@@ -35572,15 +35035,15 @@
         <v>36</v>
       </c>
       <c r="M23" t="s">
-        <v>1286</v>
+        <v>1278</v>
       </c>
       <c r="N23" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="25" spans="1:15">
       <c r="A25" t="s">
-        <v>1298</v>
+        <v>1290</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -35601,13 +35064,13 @@
         <v>910</v>
       </c>
       <c r="H25" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="I25" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
       <c r="J25" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
       <c r="K25">
         <v>0</v>
@@ -35616,15 +35079,15 @@
         <v>36</v>
       </c>
       <c r="M25" t="s">
-        <v>1299</v>
+        <v>1291</v>
       </c>
       <c r="N25" t="s">
-        <v>1291</v>
+        <v>1283</v>
       </c>
     </row>
     <row r="27" spans="1:15">
       <c r="A27" t="s">
-        <v>1300</v>
+        <v>1292</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -35645,13 +35108,13 @@
         <v>910</v>
       </c>
       <c r="H27" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="I27" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
       <c r="J27" t="s">
-        <v>1289</v>
+        <v>1281</v>
       </c>
       <c r="K27">
         <v>0</v>
@@ -35660,18 +35123,18 @@
         <v>36</v>
       </c>
       <c r="M27" t="s">
-        <v>1301</v>
+        <v>1293</v>
       </c>
       <c r="N27" t="s">
-        <v>1291</v>
+        <v>1283</v>
       </c>
       <c r="O27" t="s">
-        <v>1302</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="29" spans="1:15">
       <c r="A29" t="s">
-        <v>1303</v>
+        <v>1295</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -35692,13 +35155,13 @@
         <v>910</v>
       </c>
       <c r="H29" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="I29" t="s">
-        <v>1304</v>
+        <v>1296</v>
       </c>
       <c r="J29" t="s">
-        <v>1304</v>
+        <v>1296</v>
       </c>
       <c r="K29">
         <v>0</v>
@@ -35707,18 +35170,18 @@
         <v>36</v>
       </c>
       <c r="M29" t="s">
-        <v>1301</v>
+        <v>1293</v>
       </c>
       <c r="N29" t="s">
-        <v>1305</v>
+        <v>1297</v>
       </c>
       <c r="O29" t="s">
-        <v>1302</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="31" spans="1:15">
       <c r="A31" t="s">
-        <v>1306</v>
+        <v>1298</v>
       </c>
       <c r="B31">
         <v>1</v>
@@ -35739,13 +35202,13 @@
         <v>910</v>
       </c>
       <c r="H31" t="s">
-        <v>1307</v>
+        <v>1299</v>
       </c>
       <c r="I31" t="s">
-        <v>1308</v>
+        <v>1300</v>
       </c>
       <c r="J31" t="s">
-        <v>1308</v>
+        <v>1300</v>
       </c>
       <c r="K31">
         <v>0</v>
@@ -35754,13 +35217,13 @@
         <v>36</v>
       </c>
       <c r="M31" t="s">
-        <v>1309</v>
+        <v>1301</v>
       </c>
       <c r="N31" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="O31" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="32" spans="1:15">
@@ -35786,13 +35249,13 @@
         <v>917</v>
       </c>
       <c r="H32" t="s">
-        <v>1307</v>
+        <v>1299</v>
       </c>
       <c r="I32" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
       <c r="J32" t="s">
-        <v>1311</v>
+        <v>1303</v>
       </c>
       <c r="K32">
         <v>0</v>
@@ -35801,18 +35264,18 @@
         <v>36</v>
       </c>
       <c r="M32" t="s">
-        <v>1312</v>
+        <v>1304</v>
       </c>
       <c r="N32" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="O32" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="34" spans="1:15">
       <c r="A34" t="s">
-        <v>1313</v>
+        <v>1305</v>
       </c>
       <c r="B34">
         <v>1</v>
@@ -35833,13 +35296,13 @@
         <v>910</v>
       </c>
       <c r="H34" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="I34" t="s">
-        <v>1314</v>
+        <v>1306</v>
       </c>
       <c r="J34" t="s">
-        <v>1314</v>
+        <v>1306</v>
       </c>
       <c r="K34">
         <v>0</v>
@@ -35851,7 +35314,7 @@
         <v>36</v>
       </c>
       <c r="N34" t="s">
-        <v>1281</v>
+        <v>1273</v>
       </c>
     </row>
     <row r="35" spans="1:15">
@@ -35877,13 +35340,13 @@
         <v>917</v>
       </c>
       <c r="H35" t="s">
-        <v>1284</v>
+        <v>1276</v>
       </c>
       <c r="I35" t="s">
-        <v>1315</v>
+        <v>1307</v>
       </c>
       <c r="J35" t="s">
-        <v>1315</v>
+        <v>1307</v>
       </c>
       <c r="K35">
         <v>0</v>
@@ -35895,15 +35358,15 @@
         <v>36</v>
       </c>
       <c r="N35" t="s">
-        <v>1316</v>
+        <v>1308</v>
       </c>
       <c r="O35" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="37" spans="1:15">
       <c r="A37" t="s">
-        <v>1317</v>
+        <v>1309</v>
       </c>
       <c r="B37">
         <v>1</v>
@@ -35924,13 +35387,13 @@
         <v>910</v>
       </c>
       <c r="H37" t="s">
-        <v>1318</v>
+        <v>1310</v>
       </c>
       <c r="I37" t="s">
-        <v>1319</v>
+        <v>1311</v>
       </c>
       <c r="J37" t="s">
-        <v>1319</v>
+        <v>1311</v>
       </c>
       <c r="K37">
         <v>0</v>
@@ -35942,10 +35405,10 @@
         <v>36</v>
       </c>
       <c r="N37" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="O37" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="38" spans="1:15">
@@ -35971,13 +35434,13 @@
         <v>917</v>
       </c>
       <c r="H38" t="s">
-        <v>1318</v>
+        <v>1310</v>
       </c>
       <c r="I38" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="J38" t="s">
-        <v>1320</v>
+        <v>1312</v>
       </c>
       <c r="K38">
         <v>0</v>
@@ -35989,10 +35452,10 @@
         <v>36</v>
       </c>
       <c r="N38" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="O38" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="39" spans="1:15">
@@ -36018,13 +35481,13 @@
         <v>1120</v>
       </c>
       <c r="H39" t="s">
-        <v>1318</v>
+        <v>1310</v>
       </c>
       <c r="I39" t="s">
-        <v>1321</v>
+        <v>1313</v>
       </c>
       <c r="J39" t="s">
-        <v>1321</v>
+        <v>1313</v>
       </c>
       <c r="K39">
         <v>0</v>
@@ -36036,10 +35499,10 @@
         <v>36</v>
       </c>
       <c r="N39" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="O39" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="40" spans="1:15">
@@ -36065,13 +35528,13 @@
         <v>1121</v>
       </c>
       <c r="H40" t="s">
-        <v>1318</v>
+        <v>1310</v>
       </c>
       <c r="I40" t="s">
-        <v>1322</v>
+        <v>1314</v>
       </c>
       <c r="J40" t="s">
-        <v>1322</v>
+        <v>1314</v>
       </c>
       <c r="K40">
         <v>0</v>
@@ -36083,10 +35546,10 @@
         <v>36</v>
       </c>
       <c r="N40" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="O40" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="41" spans="1:15">
@@ -36112,13 +35575,13 @@
         <v>1123</v>
       </c>
       <c r="H41" t="s">
-        <v>1318</v>
+        <v>1310</v>
       </c>
       <c r="I41" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
       <c r="J41" t="s">
-        <v>1246</v>
+        <v>1238</v>
       </c>
       <c r="K41">
         <v>0</v>
@@ -36130,10 +35593,10 @@
         <v>36</v>
       </c>
       <c r="N41" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="O41" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
     </row>
     <row r="42" spans="1:15">
@@ -36156,16 +35619,16 @@
         <v>36</v>
       </c>
       <c r="G42" t="s">
-        <v>1323</v>
+        <v>1315</v>
       </c>
       <c r="H42" t="s">
-        <v>1318</v>
+        <v>1310</v>
       </c>
       <c r="I42" t="s">
-        <v>1324</v>
+        <v>1316</v>
       </c>
       <c r="J42" t="s">
-        <v>1324</v>
+        <v>1316</v>
       </c>
       <c r="K42">
         <v>0</v>
@@ -36177,10 +35640,10 @@
         <v>36</v>
       </c>
       <c r="N42" t="s">
-        <v>1287</v>
+        <v>1279</v>
       </c>
       <c r="O42" t="s">
-        <v>1310</v>
+        <v>1302</v>
       </c>
     </row>
   </sheetData>
@@ -36209,25 +35672,25 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>1325</v>
+        <v>1317</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>1326</v>
+        <v>1318</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>1327</v>
+        <v>1319</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>1328</v>
+        <v>1320</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>1329</v>
+        <v>1321</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>1330</v>
+        <v>1322</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>1331</v>
+        <v>1323</v>
       </c>
     </row>
     <row r="2" spans="2:9">
@@ -36237,57 +35700,57 @@
     </row>
     <row r="3" spans="2:9">
       <c r="B3" t="s">
-        <v>1288</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="4" spans="2:9">
       <c r="B4" t="s">
-        <v>1292</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="5" spans="2:9">
       <c r="B5" t="s">
-        <v>1295</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="6" spans="2:9">
       <c r="B6" t="s">
-        <v>1297</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="7" spans="2:9">
       <c r="B7" t="s">
-        <v>1298</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="8" spans="2:9">
       <c r="B8" t="s">
-        <v>1300</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="9" spans="2:9">
       <c r="B9" t="s">
-        <v>1303</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="10" spans="2:9">
       <c r="B10" t="s">
-        <v>1313</v>
+        <v>1305</v>
       </c>
     </row>
     <row r="11" spans="2:9">
       <c r="B11" t="s">
-        <v>1332</v>
+        <v>1324</v>
       </c>
     </row>
     <row r="12" spans="2:9">
       <c r="B12" t="s">
-        <v>1333</v>
+        <v>1325</v>
       </c>
     </row>
     <row r="13" spans="2:9">
       <c r="B13" t="s">
-        <v>1334</v>
+        <v>1326</v>
       </c>
     </row>
   </sheetData>
@@ -36310,87 +35773,87 @@
         <v>0</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>1335</v>
+        <v>1327</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>1336</v>
+        <v>1328</v>
       </c>
       <c r="B2" t="s">
-        <v>1337</v>
+        <v>1329</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" s="44" t="s">
-        <v>1381</v>
+        <v>1373</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>1382</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" s="44" t="s">
-        <v>1387</v>
+        <v>1379</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>1388</v>
+        <v>1380</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" s="44" t="s">
-        <v>1389</v>
+        <v>1381</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>1390</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" s="44" t="s">
-        <v>1403</v>
+        <v>1395</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>1404</v>
+        <v>1396</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" s="44" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>1406</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" s="44" t="s">
-        <v>1523</v>
+        <v>1515</v>
       </c>
       <c r="B8" s="44" t="s">
-        <v>1553</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9" s="44" t="s">
-        <v>1524</v>
+        <v>1516</v>
       </c>
       <c r="B9" s="44" t="s">
-        <v>1552</v>
+        <v>1544</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10" s="44" t="s">
-        <v>1550</v>
+        <v>1542</v>
       </c>
       <c r="B10" s="44" t="s">
-        <v>1551</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11" t="s">
-        <v>1660</v>
+        <v>1652</v>
       </c>
       <c r="B11" t="s">
-        <v>1661</v>
+        <v>1653</v>
       </c>
     </row>
   </sheetData>
@@ -36413,40 +35876,40 @@
         <v>1102</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>1391</v>
+        <v>1383</v>
       </c>
       <c r="C1" s="43" t="s">
-        <v>1392</v>
+        <v>1384</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="44" t="s">
-        <v>1393</v>
+        <v>1385</v>
       </c>
       <c r="B2" s="44" t="s">
-        <v>1407</v>
+        <v>1399</v>
       </c>
       <c r="C2" s="44" t="s">
-        <v>1403</v>
+        <v>1395</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="44" t="s">
-        <v>1394</v>
+        <v>1386</v>
       </c>
       <c r="B3" s="44" t="s">
-        <v>1408</v>
+        <v>1400</v>
       </c>
       <c r="C3" s="44" t="s">
-        <v>1405</v>
+        <v>1397</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="44" t="s">
-        <v>1395</v>
+        <v>1387</v>
       </c>
       <c r="B4" s="44" t="s">
-        <v>1400</v>
+        <v>1392</v>
       </c>
       <c r="C4" s="44" t="s">
         <v>36</v>
@@ -36454,10 +35917,10 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="44" t="s">
-        <v>1396</v>
+        <v>1388</v>
       </c>
       <c r="B5" s="44" t="s">
-        <v>1399</v>
+        <v>1391</v>
       </c>
       <c r="C5" s="44" t="s">
         <v>36</v>
@@ -36465,10 +35928,10 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="44" t="s">
-        <v>1397</v>
+        <v>1389</v>
       </c>
       <c r="B6" s="44" t="s">
-        <v>1401</v>
+        <v>1393</v>
       </c>
       <c r="C6" s="44" t="s">
         <v>36</v>
@@ -36476,10 +35939,10 @@
     </row>
     <row r="7" spans="1:3">
       <c r="A7" s="44" t="s">
-        <v>1398</v>
+        <v>1390</v>
       </c>
       <c r="B7" s="44" t="s">
-        <v>1402</v>
+        <v>1394</v>
       </c>
       <c r="C7" s="44" t="s">
         <v>36</v>
@@ -36524,84 +35987,84 @@
         <v>1101</v>
       </c>
       <c r="C1" s="45" t="s">
-        <v>1528</v>
+        <v>1520</v>
       </c>
       <c r="D1" s="45" t="s">
-        <v>1419</v>
+        <v>1411</v>
       </c>
       <c r="E1" s="45" t="s">
-        <v>1736</v>
+        <v>1727</v>
       </c>
       <c r="F1" s="45" t="s">
-        <v>1420</v>
+        <v>1412</v>
       </c>
       <c r="G1" s="45" t="s">
-        <v>1563</v>
+        <v>1555</v>
       </c>
       <c r="H1" s="45" t="s">
-        <v>1637</v>
+        <v>1629</v>
       </c>
       <c r="I1" s="45" t="s">
         <v>83</v>
       </c>
       <c r="J1" s="45" t="s">
-        <v>1421</v>
+        <v>1413</v>
       </c>
       <c r="K1" s="45" t="s">
-        <v>1434</v>
+        <v>1426</v>
       </c>
       <c r="L1" s="45" t="s">
-        <v>1526</v>
+        <v>1518</v>
       </c>
       <c r="M1" s="45" t="s">
-        <v>1710</v>
+        <v>1702</v>
       </c>
       <c r="N1" s="45" t="s">
-        <v>1437</v>
+        <v>1429</v>
       </c>
       <c r="O1" s="45" t="s">
+        <v>1446</v>
+      </c>
+      <c r="P1" s="45" t="s">
+        <v>1546</v>
+      </c>
+      <c r="Q1" s="45" t="s">
         <v>1454</v>
       </c>
-      <c r="P1" s="45" t="s">
-        <v>1554</v>
-      </c>
-      <c r="Q1" s="45" t="s">
-        <v>1462</v>
-      </c>
       <c r="R1" s="45" t="s">
-        <v>1463</v>
+        <v>1455</v>
       </c>
       <c r="S1" s="45" t="s">
-        <v>1743</v>
+        <v>1734</v>
       </c>
       <c r="T1" s="45" t="s">
-        <v>1565</v>
+        <v>1557</v>
       </c>
       <c r="U1" s="45" t="s">
-        <v>1525</v>
+        <v>1517</v>
       </c>
       <c r="V1" s="45" t="s">
-        <v>1527</v>
+        <v>1519</v>
       </c>
       <c r="W1" s="45" t="s">
-        <v>1644</v>
+        <v>1636</v>
       </c>
       <c r="X1" s="45" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
     </row>
     <row r="2" spans="1:24">
       <c r="A2" s="46" t="s">
-        <v>1424</v>
+        <v>1416</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C2" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D2" s="46" t="s">
-        <v>1425</v>
+        <v>1417</v>
       </c>
       <c r="E2" s="46" t="s">
         <v>36</v>
@@ -36666,16 +36129,16 @@
     </row>
     <row r="3" spans="1:24">
       <c r="A3" s="46" t="s">
-        <v>1426</v>
+        <v>1418</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C3" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D3" s="46" t="s">
-        <v>1422</v>
+        <v>1414</v>
       </c>
       <c r="E3" s="46" t="s">
         <v>36</v>
@@ -36740,16 +36203,16 @@
     </row>
     <row r="4" spans="1:24">
       <c r="A4" s="46" t="s">
-        <v>1427</v>
+        <v>1419</v>
       </c>
       <c r="B4" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C4" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D4" s="46" t="s">
-        <v>1429</v>
+        <v>1421</v>
       </c>
       <c r="E4" s="46" t="s">
         <v>36</v>
@@ -36814,16 +36277,16 @@
     </row>
     <row r="5" spans="1:24">
       <c r="A5" s="46" t="s">
-        <v>1428</v>
+        <v>1420</v>
       </c>
       <c r="B5" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C5" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D5" s="46" t="s">
-        <v>1423</v>
+        <v>1415</v>
       </c>
       <c r="E5" s="46" t="s">
         <v>36</v>
@@ -36888,16 +36351,16 @@
     </row>
     <row r="6" spans="1:24">
       <c r="A6" s="46" t="s">
-        <v>1430</v>
+        <v>1422</v>
       </c>
       <c r="B6" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C6" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D6" s="46" t="s">
-        <v>1432</v>
+        <v>1424</v>
       </c>
       <c r="E6" s="46" t="s">
         <v>36</v>
@@ -36962,16 +36425,16 @@
     </row>
     <row r="7" spans="1:24">
       <c r="A7" s="46" t="s">
-        <v>1431</v>
+        <v>1423</v>
       </c>
       <c r="B7" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C7" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D7" s="46" t="s">
-        <v>1433</v>
+        <v>1425</v>
       </c>
       <c r="E7" s="46" t="s">
         <v>36</v>
@@ -37036,16 +36499,16 @@
     </row>
     <row r="8" spans="1:24">
       <c r="A8" s="46" t="s">
-        <v>1435</v>
+        <v>1427</v>
       </c>
       <c r="B8" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C8" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D8" s="46" t="s">
-        <v>1512</v>
+        <v>1504</v>
       </c>
       <c r="E8" s="46" t="s">
         <v>36</v>
@@ -37066,7 +36529,7 @@
         <v>36</v>
       </c>
       <c r="K8" s="46" t="s">
-        <v>1501</v>
+        <v>1493</v>
       </c>
       <c r="L8" s="46" t="s">
         <v>36</v>
@@ -37110,16 +36573,16 @@
     </row>
     <row r="9" spans="1:24">
       <c r="A9" s="46" t="s">
-        <v>1436</v>
+        <v>1428</v>
       </c>
       <c r="B9" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C9" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D9" s="46" t="s">
-        <v>1514</v>
+        <v>1506</v>
       </c>
       <c r="E9" s="46" t="s">
         <v>36</v>
@@ -37140,7 +36603,7 @@
         <v>36</v>
       </c>
       <c r="K9" s="46" t="s">
-        <v>1439</v>
+        <v>1431</v>
       </c>
       <c r="L9" s="46" t="s">
         <v>36</v>
@@ -37184,16 +36647,16 @@
     </row>
     <row r="10" spans="1:24">
       <c r="A10" s="46" t="s">
-        <v>1440</v>
+        <v>1432</v>
       </c>
       <c r="B10" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C10" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D10" s="46" t="s">
-        <v>1469</v>
+        <v>1461</v>
       </c>
       <c r="E10" s="46" t="s">
         <v>36</v>
@@ -37214,7 +36677,7 @@
         <v>36</v>
       </c>
       <c r="K10" s="46" t="s">
-        <v>1441</v>
+        <v>1433</v>
       </c>
       <c r="L10" s="46" t="s">
         <v>36</v>
@@ -37258,16 +36721,16 @@
     </row>
     <row r="11" spans="1:24">
       <c r="A11" s="46" t="s">
-        <v>1442</v>
+        <v>1434</v>
       </c>
       <c r="B11" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C11" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D11" s="46" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="E11" s="46" t="s">
         <v>36</v>
@@ -37332,16 +36795,16 @@
     </row>
     <row r="12" spans="1:24">
       <c r="A12" s="46" t="s">
-        <v>1443</v>
+        <v>1435</v>
       </c>
       <c r="B12" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C12" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D12" s="46" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="E12" s="46" t="s">
         <v>36</v>
@@ -37406,16 +36869,16 @@
     </row>
     <row r="13" spans="1:24">
       <c r="A13" s="46" t="s">
-        <v>1445</v>
+        <v>1437</v>
       </c>
       <c r="B13" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C13" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D13" s="46" t="s">
-        <v>1444</v>
+        <v>1436</v>
       </c>
       <c r="E13" s="46" t="s">
         <v>36</v>
@@ -37480,16 +36943,16 @@
     </row>
     <row r="14" spans="1:24">
       <c r="A14" s="46" t="s">
-        <v>1446</v>
+        <v>1438</v>
       </c>
       <c r="B14" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C14" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D14" s="46" t="s">
-        <v>1483</v>
+        <v>1475</v>
       </c>
       <c r="E14" s="46" t="s">
         <v>36</v>
@@ -37554,16 +37017,16 @@
     </row>
     <row r="15" spans="1:24">
       <c r="A15" s="46" t="s">
-        <v>1447</v>
+        <v>1439</v>
       </c>
       <c r="B15" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C15" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D15" s="46" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="E15" s="46" t="s">
         <v>36</v>
@@ -37628,16 +37091,16 @@
     </row>
     <row r="16" spans="1:24">
       <c r="A16" s="46" t="s">
-        <v>1448</v>
+        <v>1440</v>
       </c>
       <c r="B16" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C16" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D16" s="46" t="s">
-        <v>1449</v>
+        <v>1441</v>
       </c>
       <c r="E16" s="46" t="s">
         <v>36</v>
@@ -37702,16 +37165,16 @@
     </row>
     <row r="17" spans="1:24">
       <c r="A17" s="46" t="s">
-        <v>1450</v>
+        <v>1442</v>
       </c>
       <c r="B17" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C17" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D17" s="46" t="s">
-        <v>1513</v>
+        <v>1505</v>
       </c>
       <c r="E17" s="46" t="s">
         <v>36</v>
@@ -37744,7 +37207,7 @@
         <v>36</v>
       </c>
       <c r="O17" s="46" t="s">
-        <v>1456</v>
+        <v>1448</v>
       </c>
       <c r="P17" s="46" t="s">
         <v>36</v>
@@ -37776,16 +37239,16 @@
     </row>
     <row r="18" spans="1:24">
       <c r="A18" s="46" t="s">
-        <v>1451</v>
+        <v>1443</v>
       </c>
       <c r="B18" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C18" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D18" s="46" t="s">
-        <v>1505</v>
+        <v>1497</v>
       </c>
       <c r="E18" s="46" t="s">
         <v>36</v>
@@ -37818,7 +37281,7 @@
         <v>36</v>
       </c>
       <c r="O18" s="46" t="s">
-        <v>1531</v>
+        <v>1523</v>
       </c>
       <c r="P18" s="46" t="s">
         <v>36</v>
@@ -37850,16 +37313,16 @@
     </row>
     <row r="19" spans="1:24">
       <c r="A19" s="46" t="s">
-        <v>1452</v>
+        <v>1444</v>
       </c>
       <c r="B19" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C19" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D19" s="46" t="s">
-        <v>1453</v>
+        <v>1445</v>
       </c>
       <c r="E19" s="46" t="s">
         <v>36</v>
@@ -37892,7 +37355,7 @@
         <v>36</v>
       </c>
       <c r="O19" s="46" t="s">
-        <v>1457</v>
+        <v>1449</v>
       </c>
       <c r="P19" s="46" t="s">
         <v>36</v>
@@ -37924,16 +37387,16 @@
     </row>
     <row r="20" spans="1:24">
       <c r="A20" s="46" t="s">
-        <v>1458</v>
+        <v>1450</v>
       </c>
       <c r="B20" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C20" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D20" s="46" t="s">
-        <v>1461</v>
+        <v>1453</v>
       </c>
       <c r="E20" s="46" t="s">
         <v>36</v>
@@ -37954,7 +37417,7 @@
         <v>36</v>
       </c>
       <c r="K20" s="46" t="s">
-        <v>1491</v>
+        <v>1483</v>
       </c>
       <c r="L20" s="46" t="s">
         <v>36</v>
@@ -37998,16 +37461,16 @@
     </row>
     <row r="21" spans="1:24">
       <c r="A21" s="46" t="s">
-        <v>1459</v>
+        <v>1451</v>
       </c>
       <c r="B21" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C21" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D21" s="46" t="s">
-        <v>1461</v>
+        <v>1453</v>
       </c>
       <c r="E21" s="46" t="s">
         <v>36</v>
@@ -38072,16 +37535,16 @@
     </row>
     <row r="22" spans="1:24">
       <c r="A22" s="46" t="s">
-        <v>1460</v>
+        <v>1452</v>
       </c>
       <c r="B22" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C22" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D22" s="46" t="s">
-        <v>1461</v>
+        <v>1453</v>
       </c>
       <c r="E22" s="46" t="s">
         <v>36</v>
@@ -38146,16 +37609,16 @@
     </row>
     <row r="23" spans="1:24">
       <c r="A23" s="46" t="s">
-        <v>1470</v>
+        <v>1462</v>
       </c>
       <c r="B23" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C23" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D23" s="46" t="s">
-        <v>1499</v>
+        <v>1491</v>
       </c>
       <c r="E23" s="46" t="s">
         <v>36</v>
@@ -38188,7 +37651,7 @@
         <v>36</v>
       </c>
       <c r="O23" s="46" t="s">
-        <v>1498</v>
+        <v>1490</v>
       </c>
       <c r="P23" s="46" t="s">
         <v>36</v>
@@ -38220,16 +37683,16 @@
     </row>
     <row r="24" spans="1:24">
       <c r="A24" s="46" t="s">
-        <v>1471</v>
+        <v>1463</v>
       </c>
       <c r="B24" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C24" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D24" s="46" t="s">
-        <v>1473</v>
+        <v>1465</v>
       </c>
       <c r="E24" s="46" t="s">
         <v>36</v>
@@ -38294,16 +37757,16 @@
     </row>
     <row r="25" spans="1:24">
       <c r="A25" s="46" t="s">
-        <v>1472</v>
+        <v>1464</v>
       </c>
       <c r="B25" s="46" t="s">
-        <v>1522</v>
+        <v>1514</v>
       </c>
       <c r="C25" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D25" s="46" t="s">
-        <v>1473</v>
+        <v>1465</v>
       </c>
       <c r="E25" s="46" t="s">
         <v>36</v>
@@ -38394,7 +37857,7 @@
     </row>
     <row r="27" spans="1:24">
       <c r="A27" s="46" t="s">
-        <v>1555</v>
+        <v>1547</v>
       </c>
       <c r="B27" s="46" t="s">
         <v>36</v>
@@ -38409,11 +37872,11 @@
         <v>36</v>
       </c>
       <c r="F27" s="46" t="s">
+        <v>1548</v>
+      </c>
+      <c r="G27" s="46" t="s">
         <v>1556</v>
       </c>
-      <c r="G27" s="46" t="s">
-        <v>1564</v>
-      </c>
       <c r="H27" s="46" t="s">
         <v>36</v>
       </c>
@@ -38439,7 +37902,7 @@
         <v>36</v>
       </c>
       <c r="P27" s="46" t="s">
-        <v>1555</v>
+        <v>1547</v>
       </c>
       <c r="Q27" s="46" t="s">
         <v>36</v>
@@ -38468,7 +37931,7 @@
     </row>
     <row r="28" spans="1:24">
       <c r="A28" s="46" t="s">
-        <v>1566</v>
+        <v>1558</v>
       </c>
       <c r="B28" s="46" t="s">
         <v>36</v>
@@ -38483,10 +37946,10 @@
         <v>36</v>
       </c>
       <c r="F28" s="46" t="s">
-        <v>1567</v>
+        <v>1559</v>
       </c>
       <c r="G28" s="46" t="s">
-        <v>1568</v>
+        <v>1560</v>
       </c>
       <c r="H28" s="46" t="s">
         <v>36</v>
@@ -38513,7 +37976,7 @@
         <v>36</v>
       </c>
       <c r="P28" s="46" t="s">
-        <v>1566</v>
+        <v>1558</v>
       </c>
       <c r="Q28" s="46" t="s">
         <v>36</v>
@@ -38542,7 +38005,7 @@
     </row>
     <row r="31" spans="1:24">
       <c r="A31" s="46" t="s">
-        <v>1542</v>
+        <v>1534</v>
       </c>
       <c r="B31" s="46" t="s">
         <v>36</v>
@@ -38616,16 +38079,16 @@
     </row>
     <row r="32" spans="1:24">
       <c r="A32" s="46" t="s">
-        <v>1541</v>
+        <v>1533</v>
       </c>
       <c r="B32" s="46" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C32" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D32" s="46" t="s">
-        <v>1540</v>
+        <v>1532</v>
       </c>
       <c r="E32" s="46" t="s">
         <v>36</v>
@@ -38690,10 +38153,10 @@
     </row>
     <row r="35" spans="1:24">
       <c r="A35" s="46" t="s">
-        <v>1543</v>
+        <v>1535</v>
       </c>
       <c r="B35" s="46" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C35" s="46" t="s">
         <v>36</v>
@@ -38764,16 +38227,16 @@
     </row>
     <row r="36" spans="1:24">
       <c r="A36" s="46" t="s">
-        <v>1544</v>
+        <v>1536</v>
       </c>
       <c r="B36" s="46" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C36" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D36" s="46" t="s">
-        <v>1547</v>
+        <v>1539</v>
       </c>
       <c r="E36" s="46" t="s">
         <v>36</v>
@@ -38838,10 +38301,10 @@
     </row>
     <row r="39" spans="1:24">
       <c r="A39" s="46" t="s">
-        <v>1545</v>
+        <v>1537</v>
       </c>
       <c r="B39" s="46" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C39" s="46" t="s">
         <v>36</v>
@@ -38912,16 +38375,16 @@
     </row>
     <row r="40" spans="1:24">
       <c r="A40" s="46" t="s">
-        <v>1546</v>
+        <v>1538</v>
       </c>
       <c r="B40" s="46" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C40" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D40" s="46" t="s">
-        <v>1548</v>
+        <v>1540</v>
       </c>
       <c r="E40" s="46" t="s">
         <v>36</v>
@@ -38986,16 +38449,16 @@
     </row>
     <row r="45" spans="1:24">
       <c r="A45" s="46" t="s">
-        <v>1571</v>
+        <v>1563</v>
       </c>
       <c r="B45" s="46" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C45" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D45" s="46" t="s">
-        <v>1548</v>
+        <v>1540</v>
       </c>
       <c r="E45" s="46" t="s">
         <v>36</v>
@@ -39060,16 +38523,16 @@
     </row>
     <row r="46" spans="1:24">
       <c r="A46" s="46" t="s">
-        <v>1572</v>
+        <v>1564</v>
       </c>
       <c r="B46" s="46" t="s">
-        <v>1587</v>
+        <v>1579</v>
       </c>
       <c r="C46" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D46" s="46" t="s">
-        <v>1569</v>
+        <v>1561</v>
       </c>
       <c r="E46" s="46" t="s">
         <v>36</v>
@@ -39134,16 +38597,16 @@
     </row>
     <row r="47" spans="1:24">
       <c r="A47" s="46" t="s">
-        <v>1573</v>
+        <v>1565</v>
       </c>
       <c r="B47" s="46" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="C47" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D47" s="46" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
       <c r="E47" s="46" t="s">
         <v>36</v>
@@ -39208,16 +38671,16 @@
     </row>
     <row r="48" spans="1:24">
       <c r="A48" s="46" t="s">
-        <v>1589</v>
+        <v>1581</v>
       </c>
       <c r="B48" s="46" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="C48" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D48" s="46" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
       <c r="E48" s="46" t="s">
         <v>36</v>
@@ -39282,16 +38745,16 @@
     </row>
     <row r="49" spans="1:24">
       <c r="A49" s="46" t="s">
-        <v>1574</v>
+        <v>1566</v>
       </c>
       <c r="B49" s="46" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C49" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D49" s="46" t="s">
-        <v>1548</v>
+        <v>1540</v>
       </c>
       <c r="E49" s="46" t="s">
         <v>36</v>
@@ -39356,16 +38819,16 @@
     </row>
     <row r="50" spans="1:24">
       <c r="A50" s="46" t="s">
-        <v>1575</v>
+        <v>1567</v>
       </c>
       <c r="B50" s="46" t="s">
-        <v>1587</v>
+        <v>1579</v>
       </c>
       <c r="C50" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D50" s="46" t="s">
-        <v>1569</v>
+        <v>1561</v>
       </c>
       <c r="E50" s="46" t="s">
         <v>36</v>
@@ -39430,16 +38893,16 @@
     </row>
     <row r="51" spans="1:24">
       <c r="A51" s="46" t="s">
-        <v>1576</v>
+        <v>1568</v>
       </c>
       <c r="B51" s="46" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="C51" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D51" s="46" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
       <c r="E51" s="46" t="s">
         <v>36</v>
@@ -39504,16 +38967,16 @@
     </row>
     <row r="52" spans="1:24">
       <c r="A52" s="46" t="s">
-        <v>1590</v>
+        <v>1582</v>
       </c>
       <c r="B52" s="46" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="C52" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D52" s="46" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
       <c r="E52" s="46" t="s">
         <v>36</v>
@@ -39578,16 +39041,16 @@
     </row>
     <row r="53" spans="1:24">
       <c r="A53" s="46" t="s">
-        <v>1577</v>
+        <v>1569</v>
       </c>
       <c r="B53" s="46" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C53" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D53" s="46" t="s">
-        <v>1548</v>
+        <v>1540</v>
       </c>
       <c r="E53" s="46" t="s">
         <v>36</v>
@@ -39652,16 +39115,16 @@
     </row>
     <row r="54" spans="1:24">
       <c r="A54" s="46" t="s">
-        <v>1578</v>
+        <v>1570</v>
       </c>
       <c r="B54" s="46" t="s">
-        <v>1587</v>
+        <v>1579</v>
       </c>
       <c r="C54" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D54" s="46" t="s">
-        <v>1569</v>
+        <v>1561</v>
       </c>
       <c r="E54" s="46" t="s">
         <v>36</v>
@@ -39726,16 +39189,16 @@
     </row>
     <row r="55" spans="1:24">
       <c r="A55" s="46" t="s">
-        <v>1579</v>
+        <v>1571</v>
       </c>
       <c r="B55" s="46" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="C55" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D55" s="46" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
       <c r="E55" s="46" t="s">
         <v>36</v>
@@ -39800,16 +39263,16 @@
     </row>
     <row r="56" spans="1:24">
       <c r="A56" s="46" t="s">
-        <v>1591</v>
+        <v>1583</v>
       </c>
       <c r="B56" s="46" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="C56" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D56" s="46" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
       <c r="E56" s="46" t="s">
         <v>36</v>
@@ -39874,16 +39337,16 @@
     </row>
     <row r="57" spans="1:24">
       <c r="A57" s="46" t="s">
-        <v>1580</v>
+        <v>1572</v>
       </c>
       <c r="B57" s="46" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C57" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D57" s="46" t="s">
-        <v>1548</v>
+        <v>1540</v>
       </c>
       <c r="E57" s="46" t="s">
         <v>36</v>
@@ -39948,16 +39411,16 @@
     </row>
     <row r="58" spans="1:24">
       <c r="A58" s="46" t="s">
-        <v>1581</v>
+        <v>1573</v>
       </c>
       <c r="B58" s="46" t="s">
-        <v>1587</v>
+        <v>1579</v>
       </c>
       <c r="C58" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D58" s="46" t="s">
-        <v>1569</v>
+        <v>1561</v>
       </c>
       <c r="E58" s="46" t="s">
         <v>36</v>
@@ -40022,16 +39485,16 @@
     </row>
     <row r="59" spans="1:24">
       <c r="A59" s="46" t="s">
-        <v>1582</v>
+        <v>1574</v>
       </c>
       <c r="B59" s="46" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="C59" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D59" s="46" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
       <c r="E59" s="46" t="s">
         <v>36</v>
@@ -40096,16 +39559,16 @@
     </row>
     <row r="60" spans="1:24">
       <c r="A60" s="46" t="s">
-        <v>1592</v>
+        <v>1584</v>
       </c>
       <c r="B60" s="46" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="C60" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D60" s="46" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
       <c r="E60" s="46" t="s">
         <v>36</v>
@@ -40170,16 +39633,16 @@
     </row>
     <row r="61" spans="1:24">
       <c r="A61" s="46" t="s">
-        <v>1583</v>
+        <v>1575</v>
       </c>
       <c r="B61" s="46" t="s">
-        <v>1274</v>
+        <v>1266</v>
       </c>
       <c r="C61" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D61" s="46" t="s">
-        <v>1548</v>
+        <v>1540</v>
       </c>
       <c r="E61" s="46" t="s">
         <v>36</v>
@@ -40244,16 +39707,16 @@
     </row>
     <row r="62" spans="1:24">
       <c r="A62" s="46" t="s">
-        <v>1584</v>
+        <v>1576</v>
       </c>
       <c r="B62" s="46" t="s">
-        <v>1587</v>
+        <v>1579</v>
       </c>
       <c r="C62" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D62" s="46" t="s">
-        <v>1569</v>
+        <v>1561</v>
       </c>
       <c r="E62" s="46" t="s">
         <v>36</v>
@@ -40318,16 +39781,16 @@
     </row>
     <row r="63" spans="1:24">
       <c r="A63" s="46" t="s">
-        <v>1585</v>
+        <v>1577</v>
       </c>
       <c r="B63" s="46" t="s">
-        <v>1588</v>
+        <v>1580</v>
       </c>
       <c r="C63" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D63" s="46" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
       <c r="E63" s="46" t="s">
         <v>36</v>
@@ -40392,16 +39855,16 @@
     </row>
     <row r="64" spans="1:24">
       <c r="A64" s="46" t="s">
-        <v>1593</v>
+        <v>1585</v>
       </c>
       <c r="B64" s="46" t="s">
-        <v>1594</v>
+        <v>1586</v>
       </c>
       <c r="C64" s="46" t="s">
         <v>36</v>
       </c>
       <c r="D64" s="46" t="s">
-        <v>1570</v>
+        <v>1562</v>
       </c>
       <c r="E64" s="46" t="s">
         <v>36</v>
@@ -40466,7 +39929,7 @@
     </row>
     <row r="66" spans="1:24">
       <c r="A66" s="46" t="s">
-        <v>1659</v>
+        <v>1651</v>
       </c>
       <c r="B66" s="46" t="s">
         <v>36</v>
@@ -40475,17 +39938,17 @@
         <v>36</v>
       </c>
       <c r="D66" s="46" t="s">
-        <v>1658</v>
+        <v>1650</v>
       </c>
       <c r="E66" s="46" t="s">
         <v>36</v>
       </c>
       <c r="F66" s="46" t="s">
+        <v>1548</v>
+      </c>
+      <c r="G66" s="46" t="s">
         <v>1556</v>
       </c>
-      <c r="G66" s="46" t="s">
-        <v>1564</v>
-      </c>
       <c r="H66" s="46" t="s">
         <v>36</v>
       </c>
@@ -40511,7 +39974,7 @@
         <v>36</v>
       </c>
       <c r="P66" s="46" t="s">
-        <v>1555</v>
+        <v>1547</v>
       </c>
       <c r="Q66" s="46" t="s">
         <v>36</v>
@@ -40540,7 +40003,7 @@
     </row>
     <row r="68" spans="1:24">
       <c r="A68" s="46" t="s">
-        <v>1709</v>
+        <v>1701</v>
       </c>
       <c r="B68" s="46" t="s">
         <v>36</v>
@@ -40588,7 +40051,7 @@
         <v>36</v>
       </c>
       <c r="Q68" s="46" t="s">
-        <v>1696</v>
+        <v>1688</v>
       </c>
       <c r="R68" s="46" t="s">
         <v>36</v>
@@ -40603,7 +40066,7 @@
         <v>36</v>
       </c>
       <c r="V68" s="46" t="s">
-        <v>1719</v>
+        <v>1711</v>
       </c>
       <c r="W68" s="46">
         <v>1</v>
@@ -40614,10 +40077,10 @@
     </row>
     <row r="70" spans="1:24">
       <c r="A70" s="46" t="s">
-        <v>1711</v>
+        <v>1703</v>
       </c>
       <c r="B70" s="46" t="s">
-        <v>1665</v>
+        <v>1657</v>
       </c>
       <c r="C70" s="46" t="s">
         <v>36</v>
@@ -40629,7 +40092,7 @@
         <v>36</v>
       </c>
       <c r="F70" s="46" t="s">
-        <v>1715</v>
+        <v>1707</v>
       </c>
       <c r="G70" s="46" t="s">
         <v>36</v>
@@ -40688,10 +40151,10 @@
     </row>
     <row r="71" spans="1:24">
       <c r="A71" s="46" t="s">
-        <v>1712</v>
+        <v>1704</v>
       </c>
       <c r="B71" s="46" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
       <c r="C71" s="46" t="s">
         <v>36</v>
@@ -40703,7 +40166,7 @@
         <v>36</v>
       </c>
       <c r="F71" s="46" t="s">
-        <v>1716</v>
+        <v>1708</v>
       </c>
       <c r="G71" s="46" t="s">
         <v>36</v>
@@ -40762,10 +40225,10 @@
     </row>
     <row r="72" spans="1:24">
       <c r="A72" s="46" t="s">
-        <v>1713</v>
+        <v>1705</v>
       </c>
       <c r="B72" s="46" t="s">
-        <v>1667</v>
+        <v>1659</v>
       </c>
       <c r="C72" s="46" t="s">
         <v>36</v>
@@ -40777,7 +40240,7 @@
         <v>36</v>
       </c>
       <c r="F72" s="46" t="s">
-        <v>1717</v>
+        <v>1709</v>
       </c>
       <c r="G72" s="46" t="s">
         <v>36</v>
@@ -40836,10 +40299,10 @@
     </row>
     <row r="73" spans="1:24">
       <c r="A73" s="46" t="s">
-        <v>1714</v>
+        <v>1706</v>
       </c>
       <c r="B73" s="46" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
       <c r="C73" s="46" t="s">
         <v>36</v>
@@ -40851,7 +40314,7 @@
         <v>36</v>
       </c>
       <c r="F73" s="46" t="s">
-        <v>1718</v>
+        <v>1710</v>
       </c>
       <c r="G73" s="46" t="s">
         <v>36</v>
@@ -40910,10 +40373,10 @@
     </row>
     <row r="75" spans="1:24">
       <c r="A75" s="46" t="s">
-        <v>1739</v>
+        <v>1730</v>
       </c>
       <c r="B75" s="46" t="s">
-        <v>1750</v>
+        <v>1741</v>
       </c>
       <c r="C75" s="46" t="s">
         <v>36</v>
@@ -40958,10 +40421,10 @@
         <v>36</v>
       </c>
       <c r="Q75" s="46" t="s">
-        <v>1739</v>
+        <v>1730</v>
       </c>
       <c r="R75" s="46" t="s">
-        <v>1741</v>
+        <v>1732</v>
       </c>
       <c r="S75" s="46">
         <v>1</v>
@@ -40984,10 +40447,10 @@
     </row>
     <row r="76" spans="1:24">
       <c r="A76" s="46" t="s">
-        <v>1740</v>
+        <v>1731</v>
       </c>
       <c r="B76" s="46" t="s">
-        <v>1751</v>
+        <v>1742</v>
       </c>
       <c r="C76" s="46" t="s">
         <v>36</v>
@@ -41032,10 +40495,10 @@
         <v>36</v>
       </c>
       <c r="Q76" s="46" t="s">
-        <v>1739</v>
+        <v>1730</v>
       </c>
       <c r="R76" s="46" t="s">
-        <v>1741</v>
+        <v>1732</v>
       </c>
       <c r="S76" s="46">
         <v>10</v>
@@ -41058,10 +40521,10 @@
     </row>
     <row r="77" spans="1:24">
       <c r="A77" s="46" t="s">
-        <v>1752</v>
+        <v>1743</v>
       </c>
       <c r="B77" s="46" t="s">
-        <v>1750</v>
+        <v>1741</v>
       </c>
       <c r="C77" s="46" t="s">
         <v>36</v>
@@ -41106,10 +40569,10 @@
         <v>36</v>
       </c>
       <c r="Q77" s="46" t="s">
-        <v>1752</v>
+        <v>1743</v>
       </c>
       <c r="R77" s="46" t="s">
-        <v>1744</v>
+        <v>1735</v>
       </c>
       <c r="S77" s="46">
         <v>1</v>
@@ -41132,10 +40595,10 @@
     </row>
     <row r="78" spans="1:24">
       <c r="A78" s="46" t="s">
-        <v>1753</v>
+        <v>1744</v>
       </c>
       <c r="B78" s="46" t="s">
-        <v>1751</v>
+        <v>1742</v>
       </c>
       <c r="C78" s="46" t="s">
         <v>36</v>
@@ -41180,10 +40643,10 @@
         <v>36</v>
       </c>
       <c r="Q78" s="46" t="s">
-        <v>1752</v>
+        <v>1743</v>
       </c>
       <c r="R78" s="46" t="s">
-        <v>1744</v>
+        <v>1735</v>
       </c>
       <c r="S78" s="46">
         <v>10</v>
@@ -41206,10 +40669,10 @@
     </row>
     <row r="79" spans="1:24">
       <c r="A79" s="46" t="s">
-        <v>1754</v>
+        <v>1745</v>
       </c>
       <c r="B79" s="46" t="s">
-        <v>1750</v>
+        <v>1741</v>
       </c>
       <c r="C79" s="46" t="s">
         <v>36</v>
@@ -41254,10 +40717,10 @@
         <v>36</v>
       </c>
       <c r="Q79" s="46" t="s">
-        <v>1754</v>
+        <v>1745</v>
       </c>
       <c r="R79" s="46" t="s">
-        <v>1742</v>
+        <v>1733</v>
       </c>
       <c r="S79" s="46">
         <v>1</v>
@@ -41280,10 +40743,10 @@
     </row>
     <row r="80" spans="1:24">
       <c r="A80" s="46" t="s">
-        <v>1755</v>
+        <v>1746</v>
       </c>
       <c r="B80" s="46" t="s">
-        <v>1751</v>
+        <v>1742</v>
       </c>
       <c r="C80" s="46" t="s">
         <v>36</v>
@@ -41328,10 +40791,10 @@
         <v>36</v>
       </c>
       <c r="Q80" s="46" t="s">
-        <v>1754</v>
+        <v>1745</v>
       </c>
       <c r="R80" s="46" t="s">
-        <v>1742</v>
+        <v>1733</v>
       </c>
       <c r="S80" s="46">
         <v>10</v>
@@ -41368,7 +40831,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="15.75" customHeight="1">
       <c r="A1" s="49" t="s">
-        <v>1706</v>
+        <v>1698</v>
       </c>
       <c r="B1" s="48"/>
       <c r="C1" s="48"/>
@@ -41794,7 +41257,7 @@
         <v>1</v>
       </c>
       <c r="K12" s="51" t="s">
-        <v>1735</v>
+        <v>1726</v>
       </c>
       <c r="L12" s="51">
         <v>1</v>
@@ -41868,7 +41331,7 @@
     </row>
     <row r="16" spans="1:26" ht="13">
       <c r="A16" s="49" t="s">
-        <v>1707</v>
+        <v>1699</v>
       </c>
       <c r="B16" s="48"/>
       <c r="C16" s="48"/>
@@ -42185,7 +41648,7 @@
         <v>36</v>
       </c>
       <c r="J22" s="51" t="s">
-        <v>1416</v>
+        <v>1408</v>
       </c>
       <c r="K22" s="51" t="s">
         <v>36</v>
@@ -42237,7 +41700,7 @@
         <v>36</v>
       </c>
       <c r="J23" s="51" t="s">
-        <v>1416</v>
+        <v>1408</v>
       </c>
       <c r="K23" s="51" t="s">
         <v>36</v>
@@ -42351,7 +41814,7 @@
         <v>36</v>
       </c>
       <c r="J26" s="51" t="s">
-        <v>1415</v>
+        <v>1407</v>
       </c>
       <c r="K26" s="51" t="s">
         <v>36</v>
@@ -43418,7 +42881,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>1359</v>
+        <v>1351</v>
       </c>
       <c r="C1" s="43" t="s">
         <v>10</v>
@@ -43427,52 +42890,52 @@
         <v>8</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>1360</v>
+        <v>1352</v>
       </c>
       <c r="F1" s="43" t="s">
-        <v>1361</v>
+        <v>1353</v>
       </c>
       <c r="G1" s="43" t="s">
-        <v>1362</v>
+        <v>1354</v>
       </c>
       <c r="H1" s="43" t="s">
-        <v>1363</v>
+        <v>1355</v>
       </c>
       <c r="I1" s="43" t="s">
-        <v>1364</v>
+        <v>1356</v>
       </c>
       <c r="J1" s="43" t="s">
-        <v>1365</v>
+        <v>1357</v>
       </c>
       <c r="K1" s="43" t="s">
-        <v>1366</v>
+        <v>1358</v>
       </c>
       <c r="L1" s="43" t="s">
-        <v>1367</v>
+        <v>1359</v>
       </c>
       <c r="M1" s="43" t="s">
         <v>19</v>
       </c>
       <c r="N1" s="43" t="s">
-        <v>1368</v>
+        <v>1360</v>
       </c>
       <c r="O1" s="43" t="s">
         <v>815</v>
       </c>
       <c r="P1" s="43" t="s">
-        <v>1372</v>
+        <v>1364</v>
       </c>
       <c r="Q1" s="43" t="s">
-        <v>1373</v>
+        <v>1365</v>
       </c>
       <c r="R1" s="43" t="s">
         <v>7</v>
       </c>
       <c r="S1" s="43" t="s">
-        <v>1622</v>
+        <v>1614</v>
       </c>
       <c r="T1" s="43" t="s">
-        <v>1663</v>
+        <v>1655</v>
       </c>
       <c r="U1" s="43" t="s">
         <v>1101</v>
@@ -43480,7 +42943,7 @@
     </row>
     <row r="2" spans="1:21">
       <c r="A2" s="44" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -43522,7 +42985,7 @@
         <v>10</v>
       </c>
       <c r="O2" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P2">
         <v>0</v>
@@ -43540,12 +43003,12 @@
         <v>11</v>
       </c>
       <c r="U2" t="s">
-        <v>1665</v>
+        <v>1657</v>
       </c>
     </row>
     <row r="3" spans="1:21">
       <c r="A3" s="44" t="s">
-        <v>1375</v>
+        <v>1367</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -43587,7 +43050,7 @@
         <v>10</v>
       </c>
       <c r="O3" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P3">
         <v>0</v>
@@ -43605,12 +43068,12 @@
         <v>11</v>
       </c>
       <c r="U3" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="4" spans="1:21">
       <c r="A4" s="44" t="s">
-        <v>1374</v>
+        <v>1366</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -43670,12 +43133,12 @@
         <v>11</v>
       </c>
       <c r="U4" t="s">
-        <v>1667</v>
+        <v>1659</v>
       </c>
     </row>
     <row r="5" spans="1:21">
       <c r="A5" s="44" t="s">
-        <v>1228</v>
+        <v>1220</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -43717,7 +43180,7 @@
         <v>10</v>
       </c>
       <c r="O5" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P5">
         <v>0</v>
@@ -43735,12 +43198,12 @@
         <v>11</v>
       </c>
       <c r="U5" t="s">
-        <v>1668</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="6" spans="1:21">
       <c r="A6" s="44" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -43782,7 +43245,7 @@
         <v>10</v>
       </c>
       <c r="O6" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P6">
         <v>0</v>
@@ -43800,12 +43263,12 @@
         <v>11</v>
       </c>
       <c r="U6" t="s">
-        <v>1669</v>
+        <v>1661</v>
       </c>
     </row>
     <row r="7" spans="1:21">
       <c r="A7" s="44" t="s">
-        <v>1621</v>
+        <v>1613</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -43859,18 +43322,18 @@
         <v>38</v>
       </c>
       <c r="S7" t="s">
-        <v>1623</v>
+        <v>1615</v>
       </c>
       <c r="T7">
         <v>11</v>
       </c>
       <c r="U7" t="s">
-        <v>1670</v>
+        <v>1662</v>
       </c>
     </row>
     <row r="8" spans="1:21">
       <c r="A8" s="44" t="s">
-        <v>1377</v>
+        <v>1369</v>
       </c>
       <c r="B8">
         <v>0</v>
@@ -43930,12 +43393,12 @@
         <v>11</v>
       </c>
       <c r="U8" t="s">
-        <v>1671</v>
+        <v>1663</v>
       </c>
     </row>
     <row r="9" spans="1:21">
       <c r="A9" s="44" t="s">
-        <v>1378</v>
+        <v>1370</v>
       </c>
       <c r="B9">
         <v>0</v>
@@ -43977,7 +43440,7 @@
         <v>10</v>
       </c>
       <c r="O9" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P9">
         <v>0</v>
@@ -43995,7 +43458,7 @@
         <v>11</v>
       </c>
       <c r="U9" t="s">
-        <v>1672</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="10" spans="1:21">
@@ -44042,7 +43505,7 @@
         <v>10</v>
       </c>
       <c r="O10" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P10">
         <v>0</v>
@@ -44060,7 +43523,7 @@
         <v>11</v>
       </c>
       <c r="U10" t="s">
-        <v>1673</v>
+        <v>1665</v>
       </c>
     </row>
     <row r="11" spans="1:21">
@@ -44107,7 +43570,7 @@
         <v>10</v>
       </c>
       <c r="O11" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P11">
         <v>0</v>
@@ -44125,12 +43588,12 @@
         <v>11</v>
       </c>
       <c r="U11" t="s">
-        <v>1674</v>
+        <v>1666</v>
       </c>
     </row>
     <row r="12" spans="1:21">
       <c r="A12" s="44" t="s">
-        <v>1466</v>
+        <v>1458</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -44172,7 +43635,7 @@
         <v>10</v>
       </c>
       <c r="O12" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P12">
         <v>0</v>
@@ -44190,12 +43653,12 @@
         <v>11</v>
       </c>
       <c r="U12" t="s">
-        <v>1675</v>
+        <v>1667</v>
       </c>
     </row>
     <row r="13" spans="1:21">
       <c r="A13" s="44" t="s">
-        <v>1467</v>
+        <v>1459</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -44237,7 +43700,7 @@
         <v>10</v>
       </c>
       <c r="O13" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P13">
         <v>0</v>
@@ -44255,12 +43718,12 @@
         <v>11</v>
       </c>
       <c r="U13" t="s">
-        <v>1676</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="14" spans="1:21">
       <c r="A14" s="44" t="s">
-        <v>1515</v>
+        <v>1507</v>
       </c>
       <c r="B14">
         <v>0</v>
@@ -44302,7 +43765,7 @@
         <v>10</v>
       </c>
       <c r="O14" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P14">
         <v>0</v>
@@ -44320,12 +43783,12 @@
         <v>11</v>
       </c>
       <c r="U14" t="s">
-        <v>1677</v>
+        <v>1669</v>
       </c>
     </row>
     <row r="15" spans="1:21">
       <c r="A15" s="44" t="s">
-        <v>1516</v>
+        <v>1508</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -44367,7 +43830,7 @@
         <v>10</v>
       </c>
       <c r="O15" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P15">
         <v>0</v>
@@ -44385,12 +43848,12 @@
         <v>11</v>
       </c>
       <c r="U15" t="s">
-        <v>1678</v>
+        <v>1670</v>
       </c>
     </row>
     <row r="16" spans="1:21">
       <c r="A16" s="44" t="s">
-        <v>1625</v>
+        <v>1617</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -44444,18 +43907,18 @@
         <v>38</v>
       </c>
       <c r="S16" t="s">
-        <v>1624</v>
+        <v>1616</v>
       </c>
       <c r="T16">
         <v>11</v>
       </c>
       <c r="U16" t="s">
-        <v>1679</v>
+        <v>1671</v>
       </c>
     </row>
     <row r="17" spans="1:21">
       <c r="A17" s="44" t="s">
-        <v>1633</v>
+        <v>1625</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -44497,7 +43960,7 @@
         <v>10</v>
       </c>
       <c r="O17" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P17">
         <v>0</v>
@@ -44515,12 +43978,12 @@
         <v>11</v>
       </c>
       <c r="U17" t="s">
-        <v>1680</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="18" spans="1:21">
       <c r="A18" s="44" t="s">
-        <v>1634</v>
+        <v>1626</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -44562,7 +44025,7 @@
         <v>10</v>
       </c>
       <c r="O18" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P18">
         <v>0</v>
@@ -44580,12 +44043,12 @@
         <v>11</v>
       </c>
       <c r="U18" t="s">
-        <v>1681</v>
+        <v>1673</v>
       </c>
     </row>
     <row r="19" spans="1:21">
       <c r="A19" s="44" t="s">
-        <v>1635</v>
+        <v>1627</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -44627,7 +44090,7 @@
         <v>10</v>
       </c>
       <c r="O19" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P19">
         <v>0</v>
@@ -44645,7 +44108,7 @@
         <v>11</v>
       </c>
       <c r="U19" t="s">
-        <v>1682</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="20" spans="1:21">
@@ -44692,7 +44155,7 @@
         <v>10</v>
       </c>
       <c r="O20" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P20">
         <v>0</v>
@@ -44710,12 +44173,12 @@
         <v>11</v>
       </c>
       <c r="U20" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="21" spans="1:21">
       <c r="A21" s="44" t="s">
-        <v>1727</v>
+        <v>1719</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -44757,7 +44220,7 @@
         <v>10</v>
       </c>
       <c r="O21" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P21">
         <v>0</v>
@@ -44775,12 +44238,12 @@
         <v>11</v>
       </c>
       <c r="U21" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="22" spans="1:21">
       <c r="A22" s="44" t="s">
-        <v>1728</v>
+        <v>1720</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -44822,7 +44285,7 @@
         <v>10</v>
       </c>
       <c r="O22" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P22">
         <v>0</v>
@@ -44840,12 +44303,12 @@
         <v>11</v>
       </c>
       <c r="U22" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="23" spans="1:21">
       <c r="A23" s="44" t="s">
-        <v>1729</v>
+        <v>1721</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -44887,7 +44350,7 @@
         <v>10</v>
       </c>
       <c r="O23" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P23">
         <v>0</v>
@@ -44905,12 +44368,12 @@
         <v>11</v>
       </c>
       <c r="U23" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="24" spans="1:21">
       <c r="A24" s="44" t="s">
-        <v>1737</v>
+        <v>1728</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -44952,7 +44415,7 @@
         <v>10</v>
       </c>
       <c r="O24" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P24">
         <v>0</v>
@@ -44970,12 +44433,12 @@
         <v>11</v>
       </c>
       <c r="U24" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="25" spans="1:21">
       <c r="A25" s="44" t="s">
-        <v>1738</v>
+        <v>1729</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -45017,7 +44480,7 @@
         <v>10</v>
       </c>
       <c r="O25" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P25">
         <v>0</v>
@@ -45035,12 +44498,12 @@
         <v>11</v>
       </c>
       <c r="U25" t="s">
-        <v>1567</v>
+        <v>1559</v>
       </c>
     </row>
     <row r="26" spans="1:21">
       <c r="A26" s="44" t="s">
-        <v>1749</v>
+        <v>1740</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -45082,7 +44545,7 @@
         <v>10</v>
       </c>
       <c r="O26" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P26">
         <v>0</v>
@@ -45100,7 +44563,7 @@
         <v>11</v>
       </c>
       <c r="U26" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="27" spans="1:21">
@@ -45147,7 +44610,7 @@
         <v>10</v>
       </c>
       <c r="O27" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P27">
         <v>0</v>
@@ -45165,12 +44628,12 @@
         <v>11</v>
       </c>
       <c r="U27" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
     </row>
     <row r="28" spans="1:21">
       <c r="A28" s="44" t="s">
-        <v>1757</v>
+        <v>1748</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -45212,7 +44675,7 @@
         <v>10</v>
       </c>
       <c r="O28" s="44" t="s">
-        <v>1376</v>
+        <v>1368</v>
       </c>
       <c r="P28">
         <v>0</v>
@@ -45230,7 +44693,7 @@
         <v>11</v>
       </c>
       <c r="U28" t="s">
-        <v>1666</v>
+        <v>1658</v>
       </c>
     </row>
   </sheetData>
@@ -45288,7 +44751,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>1359</v>
+        <v>1351</v>
       </c>
       <c r="C1" s="43" t="s">
         <v>10</v>
@@ -45297,145 +44760,145 @@
         <v>8</v>
       </c>
       <c r="E1" s="43" t="s">
-        <v>1360</v>
+        <v>1352</v>
       </c>
       <c r="F1" s="43" t="s">
-        <v>1361</v>
+        <v>1353</v>
       </c>
       <c r="G1" s="43" t="s">
-        <v>1362</v>
+        <v>1354</v>
       </c>
       <c r="H1" s="43" t="s">
-        <v>1363</v>
+        <v>1355</v>
       </c>
       <c r="I1" s="43" t="s">
-        <v>1364</v>
+        <v>1356</v>
       </c>
       <c r="J1" s="43" t="s">
-        <v>1536</v>
+        <v>1528</v>
       </c>
       <c r="K1" s="43" t="s">
-        <v>1537</v>
+        <v>1529</v>
       </c>
       <c r="L1" s="43" t="s">
-        <v>1596</v>
+        <v>1588</v>
       </c>
       <c r="M1" s="43" t="s">
-        <v>1597</v>
+        <v>1589</v>
       </c>
       <c r="N1" s="43" t="s">
-        <v>1365</v>
+        <v>1357</v>
       </c>
       <c r="O1" s="43" t="s">
-        <v>1366</v>
+        <v>1358</v>
       </c>
       <c r="P1" s="43" t="s">
-        <v>1367</v>
+        <v>1359</v>
       </c>
       <c r="Q1" s="43" t="s">
         <v>19</v>
       </c>
       <c r="R1" s="43" t="s">
-        <v>1383</v>
+        <v>1375</v>
       </c>
       <c r="S1" s="43" t="s">
         <v>11</v>
       </c>
       <c r="T1" s="43" t="s">
+        <v>1484</v>
+      </c>
+      <c r="U1" s="43" t="s">
+        <v>1525</v>
+      </c>
+      <c r="V1" s="43" t="s">
+        <v>1526</v>
+      </c>
+      <c r="W1" s="43" t="s">
+        <v>1527</v>
+      </c>
+      <c r="X1" s="43" t="s">
+        <v>1212</v>
+      </c>
+      <c r="Y1" s="43" t="s">
         <v>1492</v>
       </c>
-      <c r="U1" s="43" t="s">
-        <v>1533</v>
-      </c>
-      <c r="V1" s="43" t="s">
-        <v>1534</v>
-      </c>
-      <c r="W1" s="43" t="s">
-        <v>1535</v>
-      </c>
-      <c r="X1" s="43" t="s">
-        <v>1220</v>
-      </c>
-      <c r="Y1" s="43" t="s">
-        <v>1500</v>
-      </c>
       <c r="Z1" s="43" t="s">
-        <v>1411</v>
+        <v>1403</v>
       </c>
       <c r="AA1" s="43" t="s">
-        <v>1504</v>
+        <v>1496</v>
       </c>
       <c r="AB1" s="43" t="s">
-        <v>1368</v>
+        <v>1360</v>
       </c>
       <c r="AC1" s="43" t="s">
+        <v>1495</v>
+      </c>
+      <c r="AD1" s="43" t="s">
+        <v>1362</v>
+      </c>
+      <c r="AE1" s="43" t="s">
+        <v>1471</v>
+      </c>
+      <c r="AF1" s="43" t="s">
+        <v>1472</v>
+      </c>
+      <c r="AG1" s="43" t="s">
+        <v>1473</v>
+      </c>
+      <c r="AH1" s="43" t="s">
+        <v>1476</v>
+      </c>
+      <c r="AI1" s="43" t="s">
         <v>1503</v>
       </c>
-      <c r="AD1" s="43" t="s">
-        <v>1370</v>
-      </c>
-      <c r="AE1" s="43" t="s">
-        <v>1479</v>
-      </c>
-      <c r="AF1" s="43" t="s">
+      <c r="AJ1" s="43" t="s">
+        <v>1488</v>
+      </c>
+      <c r="AK1" s="43" t="s">
+        <v>1594</v>
+      </c>
+      <c r="AL1" s="43" t="s">
+        <v>1364</v>
+      </c>
+      <c r="AM1" s="43" t="s">
+        <v>1365</v>
+      </c>
+      <c r="AN1" s="43" t="s">
+        <v>1376</v>
+      </c>
+      <c r="AO1" s="43" t="s">
         <v>1480</v>
       </c>
-      <c r="AG1" s="43" t="s">
-        <v>1481</v>
-      </c>
-      <c r="AH1" s="43" t="s">
-        <v>1484</v>
-      </c>
-      <c r="AI1" s="43" t="s">
-        <v>1511</v>
-      </c>
-      <c r="AJ1" s="43" t="s">
-        <v>1496</v>
-      </c>
-      <c r="AK1" s="43" t="s">
-        <v>1602</v>
-      </c>
-      <c r="AL1" s="43" t="s">
-        <v>1372</v>
-      </c>
-      <c r="AM1" s="43" t="s">
-        <v>1373</v>
-      </c>
-      <c r="AN1" s="43" t="s">
-        <v>1384</v>
-      </c>
-      <c r="AO1" s="43" t="s">
-        <v>1488</v>
-      </c>
       <c r="AP1" s="43" t="s">
-        <v>1620</v>
+        <v>1612</v>
       </c>
       <c r="AQ1" s="43" t="s">
-        <v>1561</v>
+        <v>1553</v>
       </c>
       <c r="AR1" s="43" t="s">
-        <v>1490</v>
+        <v>1482</v>
       </c>
       <c r="AS1" s="43" t="s">
+        <v>1610</v>
+      </c>
+      <c r="AT1" s="43" t="s">
         <v>1618</v>
       </c>
-      <c r="AT1" s="43" t="s">
-        <v>1626</v>
-      </c>
       <c r="AU1" s="43" t="s">
-        <v>1630</v>
+        <v>1622</v>
       </c>
       <c r="AV1" s="43" t="s">
-        <v>1631</v>
+        <v>1623</v>
       </c>
       <c r="AW1" s="43" t="s">
-        <v>1693</v>
+        <v>1685</v>
       </c>
       <c r="AX1" s="43" t="s">
-        <v>1702</v>
+        <v>1694</v>
       </c>
       <c r="AY1" s="43" t="s">
-        <v>1703</v>
+        <v>1695</v>
       </c>
       <c r="AZ1" s="43" t="s">
         <v>7</v>
@@ -45530,19 +44993,19 @@
         <v>36</v>
       </c>
       <c r="AD2" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE2" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF2" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG2" s="44">
         <v>0</v>
       </c>
       <c r="AH2" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI2" s="44">
         <v>1</v>
@@ -45688,19 +45151,19 @@
         <v>36</v>
       </c>
       <c r="AD3" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE3" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF3" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG3" s="44">
         <v>0</v>
       </c>
       <c r="AH3" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI3" s="44">
         <v>1</v>
@@ -45759,7 +45222,7 @@
     </row>
     <row r="4" spans="1:52">
       <c r="A4" s="44" t="s">
-        <v>1379</v>
+        <v>1371</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -45846,19 +45309,19 @@
         <v>36</v>
       </c>
       <c r="AD4" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE4" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF4" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG4" s="44">
         <v>0</v>
       </c>
       <c r="AH4" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI4" s="44">
         <v>1</v>
@@ -45917,7 +45380,7 @@
     </row>
     <row r="5" spans="1:52">
       <c r="A5" s="44" t="s">
-        <v>1380</v>
+        <v>1372</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -46004,19 +45467,19 @@
         <v>36</v>
       </c>
       <c r="AD5" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE5" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF5" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG5" s="44">
         <v>0</v>
       </c>
       <c r="AH5" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI5" s="44">
         <v>1</v>
@@ -46075,7 +45538,7 @@
     </row>
     <row r="6" spans="1:52">
       <c r="A6" s="44" t="s">
-        <v>1477</v>
+        <v>1469</v>
       </c>
       <c r="B6">
         <v>-1</v>
@@ -46162,19 +45625,19 @@
         <v>36</v>
       </c>
       <c r="AD6" s="44" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
       <c r="AE6" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AF6" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG6" s="44">
         <v>0</v>
       </c>
       <c r="AH6" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI6" s="44">
         <v>1</v>
@@ -46233,7 +45696,7 @@
     </row>
     <row r="7" spans="1:52">
       <c r="A7" s="44" t="s">
-        <v>1491</v>
+        <v>1483</v>
       </c>
       <c r="B7">
         <v>0</v>
@@ -46320,19 +45783,19 @@
         <v>36</v>
       </c>
       <c r="AD7" s="44" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
       <c r="AE7" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF7" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG7" s="44">
         <v>0</v>
       </c>
       <c r="AH7" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI7" s="44">
         <v>1</v>
@@ -46353,7 +45816,7 @@
         <v>60</v>
       </c>
       <c r="AO7" t="s">
-        <v>1489</v>
+        <v>1481</v>
       </c>
       <c r="AP7">
         <v>0</v>
@@ -46391,7 +45854,7 @@
     </row>
     <row r="8" spans="1:52">
       <c r="A8" s="44" t="s">
-        <v>1438</v>
+        <v>1430</v>
       </c>
       <c r="B8">
         <v>10</v>
@@ -46478,19 +45941,19 @@
         <v>36</v>
       </c>
       <c r="AD8" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE8" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF8" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG8" s="44">
         <v>0</v>
       </c>
       <c r="AH8" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI8" s="44">
         <v>1</v>
@@ -46549,7 +46012,7 @@
     </row>
     <row r="9" spans="1:52">
       <c r="A9" s="44" t="s">
-        <v>1441</v>
+        <v>1433</v>
       </c>
       <c r="B9">
         <v>1</v>
@@ -46636,19 +46099,19 @@
         <v>36</v>
       </c>
       <c r="AD9" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE9" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF9" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG9" s="44">
         <v>0</v>
       </c>
       <c r="AH9" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI9" s="44">
         <v>1</v>
@@ -46707,7 +46170,7 @@
     </row>
     <row r="10" spans="1:52">
       <c r="A10" s="44" t="s">
-        <v>1455</v>
+        <v>1447</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -46794,19 +46257,19 @@
         <v>36</v>
       </c>
       <c r="AD10" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE10" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF10" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG10" s="44">
         <v>0</v>
       </c>
       <c r="AH10" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI10" s="44">
         <v>1</v>
@@ -46865,7 +46328,7 @@
     </row>
     <row r="11" spans="1:52">
       <c r="A11" s="44" t="s">
-        <v>1532</v>
+        <v>1524</v>
       </c>
       <c r="B11">
         <v>0</v>
@@ -46952,19 +46415,19 @@
         <v>36</v>
       </c>
       <c r="AD11" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE11" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF11" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG11" s="44">
         <v>0</v>
       </c>
       <c r="AH11" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI11" s="44">
         <v>1</v>
@@ -47023,7 +46486,7 @@
     </row>
     <row r="12" spans="1:52">
       <c r="A12" s="44" t="s">
-        <v>1456</v>
+        <v>1448</v>
       </c>
       <c r="B12">
         <v>0</v>
@@ -47110,19 +46573,19 @@
         <v>36</v>
       </c>
       <c r="AD12" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE12" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF12" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG12" s="44">
         <v>0</v>
       </c>
       <c r="AH12" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI12" s="44">
         <v>1</v>
@@ -47181,7 +46644,7 @@
     </row>
     <row r="13" spans="1:52">
       <c r="A13" s="44" t="s">
-        <v>1457</v>
+        <v>1449</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -47268,19 +46731,19 @@
         <v>36</v>
       </c>
       <c r="AD13" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE13" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF13" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG13" s="44">
         <v>0</v>
       </c>
       <c r="AH13" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI13" s="44">
         <v>1</v>
@@ -47339,7 +46802,7 @@
     </row>
     <row r="14" spans="1:52">
       <c r="A14" s="44" t="s">
-        <v>1493</v>
+        <v>1485</v>
       </c>
       <c r="B14">
         <v>1</v>
@@ -47423,22 +46886,22 @@
         <v>10</v>
       </c>
       <c r="AC14" t="s">
-        <v>1502</v>
+        <v>1494</v>
       </c>
       <c r="AD14" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE14" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF14" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG14" s="44">
         <v>0</v>
       </c>
       <c r="AH14" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI14" s="44">
         <v>1</v>
@@ -47497,7 +46960,7 @@
     </row>
     <row r="15" spans="1:52">
       <c r="A15" s="44" t="s">
-        <v>1497</v>
+        <v>1489</v>
       </c>
       <c r="B15">
         <v>0</v>
@@ -47584,25 +47047,25 @@
         <v>36</v>
       </c>
       <c r="AD15" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE15" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF15" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG15" s="44">
         <v>0</v>
       </c>
       <c r="AH15" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI15" s="44">
         <v>1</v>
       </c>
       <c r="AJ15" s="44" t="s">
-        <v>1415</v>
+        <v>1407</v>
       </c>
       <c r="AK15" s="44">
         <v>0</v>
@@ -47655,7 +47118,7 @@
     </row>
     <row r="16" spans="1:52">
       <c r="A16" s="44" t="s">
-        <v>1498</v>
+        <v>1490</v>
       </c>
       <c r="B16">
         <v>0</v>
@@ -47742,25 +47205,25 @@
         <v>36</v>
       </c>
       <c r="AD16" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE16" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF16" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG16" s="44">
         <v>0</v>
       </c>
       <c r="AH16" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI16" s="44">
         <v>1</v>
       </c>
       <c r="AJ16" s="44" t="s">
-        <v>1415</v>
+        <v>1407</v>
       </c>
       <c r="AK16" s="44">
         <v>0</v>
@@ -47813,7 +47276,7 @@
     </row>
     <row r="17" spans="1:52">
       <c r="A17" s="44" t="s">
-        <v>1502</v>
+        <v>1494</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -47900,25 +47363,25 @@
         <v>36</v>
       </c>
       <c r="AD17" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE17" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF17" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG17" s="44">
         <v>0</v>
       </c>
       <c r="AH17" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI17" s="44">
         <v>1</v>
       </c>
       <c r="AJ17" s="44" t="s">
-        <v>1415</v>
+        <v>1407</v>
       </c>
       <c r="AK17" s="44">
         <v>0</v>
@@ -47971,7 +47434,7 @@
     </row>
     <row r="18" spans="1:52">
       <c r="A18" s="44" t="s">
-        <v>1509</v>
+        <v>1501</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -48058,25 +47521,25 @@
         <v>36</v>
       </c>
       <c r="AD18" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE18" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF18" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG18" s="44">
         <v>0</v>
       </c>
       <c r="AH18" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI18" s="44">
         <v>1</v>
       </c>
       <c r="AJ18" s="44" t="s">
-        <v>1415</v>
+        <v>1407</v>
       </c>
       <c r="AK18" s="44">
         <v>0</v>
@@ -48129,7 +47592,7 @@
     </row>
     <row r="19" spans="1:52">
       <c r="A19" s="44" t="s">
-        <v>1510</v>
+        <v>1502</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -48213,22 +47676,22 @@
         <v>10</v>
       </c>
       <c r="AC19" t="s">
-        <v>1509</v>
+        <v>1501</v>
       </c>
       <c r="AD19" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE19" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF19" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG19" s="44">
         <v>0</v>
       </c>
       <c r="AH19" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI19" s="44">
         <v>100</v>
@@ -48287,7 +47750,7 @@
     </row>
     <row r="20" spans="1:52">
       <c r="A20" s="44" t="s">
-        <v>1439</v>
+        <v>1431</v>
       </c>
       <c r="B20">
         <v>10</v>
@@ -48374,19 +47837,19 @@
         <v>36</v>
       </c>
       <c r="AD20" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE20" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF20" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG20" s="44">
         <v>0</v>
       </c>
       <c r="AH20" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI20" s="44">
         <v>1</v>
@@ -48445,7 +47908,7 @@
     </row>
     <row r="21" spans="1:52">
       <c r="A21" s="44" t="s">
-        <v>1559</v>
+        <v>1551</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -48532,19 +47995,19 @@
         <v>36</v>
       </c>
       <c r="AD21" s="44" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
       <c r="AE21" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF21" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG21" s="44">
         <v>0</v>
       </c>
       <c r="AH21" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI21" s="44">
         <v>1</v>
@@ -48565,13 +48028,13 @@
         <v>60</v>
       </c>
       <c r="AO21" t="s">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="AP21">
         <v>0</v>
       </c>
       <c r="AQ21" t="s">
-        <v>1562</v>
+        <v>1554</v>
       </c>
       <c r="AR21">
         <v>1</v>
@@ -48603,7 +48066,7 @@
     </row>
     <row r="22" spans="1:52">
       <c r="A22" s="44" t="s">
-        <v>1595</v>
+        <v>1587</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -48690,19 +48153,19 @@
         <v>36</v>
       </c>
       <c r="AD22" s="44" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
       <c r="AE22" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF22" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG22" s="44">
         <v>0</v>
       </c>
       <c r="AH22" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI22" s="44">
         <v>1</v>
@@ -48848,19 +48311,19 @@
         <v>36</v>
       </c>
       <c r="AD23" s="44" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
       <c r="AE23" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF23" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG23" s="44">
         <v>0</v>
       </c>
       <c r="AH23" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI23" s="44">
         <v>1</v>
@@ -48919,7 +48382,7 @@
     </row>
     <row r="24" spans="1:52">
       <c r="A24" s="44" t="s">
-        <v>1601</v>
+        <v>1593</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -49006,19 +48469,19 @@
         <v>36</v>
       </c>
       <c r="AD24" s="44" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
       <c r="AE24" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF24" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG24" s="44">
         <v>0</v>
       </c>
       <c r="AH24" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI24" s="44">
         <v>1</v>
@@ -49077,7 +48540,7 @@
     </row>
     <row r="25" spans="1:52">
       <c r="A25" s="44" t="s">
-        <v>1610</v>
+        <v>1602</v>
       </c>
       <c r="B25">
         <v>1</v>
@@ -49164,19 +48627,19 @@
         <v>36</v>
       </c>
       <c r="AD25" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE25" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF25" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG25" s="44">
         <v>0</v>
       </c>
       <c r="AH25" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI25" s="44">
         <v>1</v>
@@ -49235,7 +48698,7 @@
     </row>
     <row r="26" spans="1:52">
       <c r="A26" s="44" t="s">
-        <v>1619</v>
+        <v>1611</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -49322,19 +48785,19 @@
         <v>36</v>
       </c>
       <c r="AD26" s="44" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
       <c r="AE26" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF26" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG26" s="44">
         <v>0</v>
       </c>
       <c r="AH26" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI26" s="44">
         <v>1</v>
@@ -49355,7 +48818,7 @@
         <v>60</v>
       </c>
       <c r="AO26" t="s">
-        <v>1560</v>
+        <v>1552</v>
       </c>
       <c r="AP26">
         <v>1</v>
@@ -49393,7 +48856,7 @@
     </row>
     <row r="27" spans="1:52">
       <c r="A27" s="44" t="s">
-        <v>1623</v>
+        <v>1615</v>
       </c>
       <c r="B27">
         <v>1</v>
@@ -49480,19 +48943,19 @@
         <v>36</v>
       </c>
       <c r="AD27" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE27" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF27" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG27" s="44">
         <v>0</v>
       </c>
       <c r="AH27" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI27" s="44">
         <v>1</v>
@@ -49551,7 +49014,7 @@
     </row>
     <row r="28" spans="1:52">
       <c r="A28" s="44" t="s">
-        <v>1624</v>
+        <v>1616</v>
       </c>
       <c r="B28">
         <v>1</v>
@@ -49638,19 +49101,19 @@
         <v>36</v>
       </c>
       <c r="AD28" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE28" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF28" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG28" s="44">
         <v>0</v>
       </c>
       <c r="AH28" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI28" s="44">
         <v>1</v>
@@ -49709,7 +49172,7 @@
     </row>
     <row r="29" spans="1:52">
       <c r="A29" s="44" t="s">
-        <v>1628</v>
+        <v>1620</v>
       </c>
       <c r="B29">
         <v>1</v>
@@ -49796,19 +49259,19 @@
         <v>36</v>
       </c>
       <c r="AD29" s="44" t="s">
-        <v>1629</v>
+        <v>1621</v>
       </c>
       <c r="AE29" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF29" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG29" s="44">
         <v>0</v>
       </c>
       <c r="AH29" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI29" s="44">
         <v>1</v>
@@ -49867,7 +49330,7 @@
     </row>
     <row r="30" spans="1:52">
       <c r="A30" s="44" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="B30">
         <v>1</v>
@@ -49954,19 +49417,19 @@
         <v>36</v>
       </c>
       <c r="AD30" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE30" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF30" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG30" s="44">
         <v>0</v>
       </c>
       <c r="AH30" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI30" s="44">
         <v>1</v>
@@ -50008,7 +49471,7 @@
         <v>36</v>
       </c>
       <c r="AV30" t="s">
-        <v>1632</v>
+        <v>1624</v>
       </c>
       <c r="AW30">
         <v>0</v>
@@ -50025,7 +49488,7 @@
     </row>
     <row r="31" spans="1:52">
       <c r="A31" s="44" t="s">
-        <v>1655</v>
+        <v>1647</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -50112,19 +49575,19 @@
         <v>36</v>
       </c>
       <c r="AD31" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE31" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF31" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG31" s="44">
         <v>0</v>
       </c>
       <c r="AH31" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI31" s="44">
         <v>1</v>
@@ -50183,7 +49646,7 @@
     </row>
     <row r="32" spans="1:52">
       <c r="A32" s="44" t="s">
-        <v>1586</v>
+        <v>1578</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -50270,19 +49733,19 @@
         <v>36</v>
       </c>
       <c r="AD32" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE32" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF32" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG32" s="44">
         <v>0</v>
       </c>
       <c r="AH32" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI32" s="44">
         <v>1</v>
@@ -50341,7 +49804,7 @@
     </row>
     <row r="33" spans="1:52">
       <c r="A33" s="44" t="s">
-        <v>1694</v>
+        <v>1686</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -50428,19 +49891,19 @@
         <v>36</v>
       </c>
       <c r="AD33" s="44" t="s">
-        <v>1487</v>
+        <v>1479</v>
       </c>
       <c r="AE33" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF33" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG33" s="44">
         <v>0</v>
       </c>
       <c r="AH33" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI33" s="44">
         <v>1</v>
@@ -50499,7 +49962,7 @@
     </row>
     <row r="34" spans="1:52">
       <c r="A34" s="44" t="s">
-        <v>1737</v>
+        <v>1728</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -50586,19 +50049,19 @@
         <v>36</v>
       </c>
       <c r="AD34" s="44" t="s">
-        <v>1371</v>
+        <v>1363</v>
       </c>
       <c r="AE34" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AF34" s="44" t="s">
-        <v>1478</v>
+        <v>1470</v>
       </c>
       <c r="AG34" s="44">
         <v>0</v>
       </c>
       <c r="AH34" s="44" t="s">
-        <v>1482</v>
+        <v>1474</v>
       </c>
       <c r="AI34" s="44">
         <v>1</v>

--- a/Assets/StreamingAssets/Config_sword.xlsx
+++ b/Assets/StreamingAssets/Config_sword.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Unity Projects\AllForOne\AllForOne\Assets\StreamingAssets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2870ABA-567D-4703-9535-B7F3FD4811B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1393594D-490F-4A1C-966C-F76E41CF2D04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" firstSheet="6" activeTab="21" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" tabRatio="771" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Heroes" sheetId="1" r:id="rId1"/>
@@ -6701,7 +6701,7 @@
         <v>45</v>
       </c>
       <c r="I5" s="48">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="J5" s="48">
         <v>0</v>
@@ -33039,16 +33039,16 @@
     <col min="1" max="1" width="11.90625" customWidth="1"/>
     <col min="2" max="2" width="12.81640625" customWidth="1"/>
     <col min="3" max="3" width="25.453125" customWidth="1"/>
-    <col min="4" max="4" width="20.90625" customWidth="1"/>
+    <col min="4" max="4" width="13.54296875" customWidth="1"/>
     <col min="5" max="5" width="26.453125" customWidth="1"/>
-    <col min="6" max="6" width="15.81640625" customWidth="1"/>
-    <col min="7" max="7" width="13.08984375" customWidth="1"/>
+    <col min="6" max="6" width="20.26953125" customWidth="1"/>
+    <col min="7" max="7" width="15.453125" customWidth="1"/>
     <col min="8" max="8" width="14.36328125" customWidth="1"/>
     <col min="9" max="9" width="11.1796875" customWidth="1"/>
     <col min="10" max="10" width="11.81640625" customWidth="1"/>
     <col min="11" max="11" width="10.36328125" customWidth="1"/>
     <col min="12" max="12" width="12.81640625" customWidth="1"/>
-    <col min="13" max="13" width="14.90625" customWidth="1"/>
+    <col min="13" max="13" width="10" customWidth="1"/>
     <col min="14" max="14" width="11.90625" customWidth="1"/>
   </cols>
   <sheetData>
@@ -45118,7 +45118,7 @@
         <v>0</v>
       </c>
       <c r="S3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="T3">
         <v>0</v>
